--- a/outputs/marine_equipment/Контейнер_22т_Питер.xlsx
+++ b/outputs/marine_equipment/Контейнер_22т_Питер.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Упаковка и крепление" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Контейнер 22 т'!$A$4:$R$229</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Остается'!$A$4:$R$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Контейнер 22 т'!$A$4:$R$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Остается'!$A$4:$R$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -582,12 +582,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>22.0 т</t>
+          <t>21.7 т</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>100% от 22 т</t>
+          <t>99% от 22 т</t>
         </is>
       </c>
     </row>
@@ -616,12 +616,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2608 штук</t>
+          <t>2625 штук</t>
         </is>
       </c>
     </row>
@@ -650,12 +650,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>6.4 т</t>
+          <t>6.1 т</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>125 позиций, 1231 шт</t>
+          <t>126 позиций, 1248 шт</t>
         </is>
       </c>
     </row>
@@ -667,12 +667,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>5.5 т</t>
+          <t>5.6 т</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58 позиций</t>
+          <t>61 позиций</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.3806369554380238</v>
+        <v>0.3854850535022596</v>
       </c>
     </row>
     <row r="14">
@@ -744,19 +744,19 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>4829</v>
+        <v>4469</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.2195131205260122</v>
+        <v>0.2057399801892552</v>
       </c>
     </row>
     <row r="15">
@@ -766,19 +766,19 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1827</v>
+        <v>1778</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3677</v>
+        <v>3070</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.1671509424999646</v>
+        <v>0.1413422220107131</v>
       </c>
     </row>
     <row r="16">
@@ -800,7 +800,7 @@
         <v>2.5</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.0894318917983722</v>
+        <v>0.09057096822096943</v>
       </c>
     </row>
     <row r="17">
@@ -822,296 +822,560 @@
         <v>0.9</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.08571050609213694</v>
+        <v>0.08680218395665691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>головка вентиляционная</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>851</v>
+        <v>363</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.03868450845102547</v>
+        <v>0.0167021120867012</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>204</v>
+        <v>346</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.00925291621058312</v>
+        <v>0.01595171399680807</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>кран</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>112</v>
+        <v>259</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.00509157139078807</v>
+        <v>0.01192350339155351</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
+          <t>клапан редукционный</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>258</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.01187746669892203</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>захлопка</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>171</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0.007872274439983205</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>кран</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0.005156421734536729</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>клапан пусковой</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0.005045621512410288</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>кингстон</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B25" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C25" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D25" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E25" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="F21" s="8" t="n">
-        <v>0.004527587593092994</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="F25" s="8" t="n">
+        <v>0.004585254586095482</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>клапан пожарный</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.004189339029464747</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>стакан переборочный</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0.002398511686100146</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>клапан паровой</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0.001500796179786272</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>клапан электромагнитный</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0.001100276953892389</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>клапан без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.0006445136968407302</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>клапан предохранительный</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0.00051330912284101</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>колонка указательная</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0.0004143302336833266</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>эжектор</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0.0001841467705259229</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B22" s="9">
-        <f>SUM(B13:B21)</f>
+      <c r="B34" s="9">
+        <f>SUM(B13:B33)</f>
         <v/>
       </c>
-      <c r="C22" s="9">
-        <f>SUM(C13:C21)</f>
+      <c r="C34" s="9">
+        <f>SUM(C13:C33)</f>
         <v/>
       </c>
-      <c r="D22" s="9">
-        <f>SUM(D13:D21)</f>
+      <c r="D34" s="9">
+        <f>SUM(D13:D33)</f>
         <v/>
       </c>
-      <c r="E22" s="10">
-        <f>SUM(E13:E21)</f>
+      <c r="E34" s="10">
+        <f>SUM(E13:E33)</f>
         <v/>
       </c>
-      <c r="F22" s="11">
-        <f>SUM(F13:F21)</f>
+      <c r="F34" s="11">
+        <f>SUM(F13:F33)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Укладка снизу вверх</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Ярус</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Что кладем</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Чем перекладываем</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Вес яруса, кг</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Пол контейнера</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Сплошной настил необрезной доской 25 мм под первый ярус</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Настил кладем до погрузки, по всей площади под задвижки</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Ярус 1, на настил</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>Задвижки и клинкеты Ду200, 250, 300, 350</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>Необрезная доска 25 мм поперек, на всю ширину, шаг 300-400 мм</t>
         </is>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D39" s="16" t="n">
         <v>6419</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Ярус 2</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>Остальные клинкеты, задвижки и арматура Ду100-150</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Необрезная доска 25 мм поперек</t>
         </is>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D40" s="16" t="n">
         <v>3626</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Ярус 3</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>Ящики с мелкой арматурой до Ду80</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>Сплошной настил доской по верху ящиков, под верхний ярус</t>
         </is>
       </c>
-      <c r="D29" s="16" t="n">
-        <v>9913</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="D41" s="16" t="n">
+        <v>9636</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>Ярус 4, верх</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>Фильтры забортной воды и титановая арматура</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>Сверху ничего не кладем</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="D42" s="16" t="n">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D31" s="9">
-        <f>SUM(D27:D30)</f>
+      <c r="D43" s="9">
+        <f>SUM(D39:D42)</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>— Блок А — это то, что менеджер уже отобрала и согласовала по приложениям 2 и 3. Он едет целиком.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>— Блок Б добран со склада по цене за килограмм: бронза и титан первыми, дальше чем дороже килограмм, тем раньше. За перевозку платят за вес, поэтому дешевое и тяжелое ждет второго борта.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>— Чтобы один и тот же товар не уехал дважды, по каждому сочетанию типа и диаметра из складского учета вычтено то, что уже стоит в списке менеджера.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>— Веса блока А — замеры менеджера. В блоке Б замеров нет, там масса пересчитана от ближайшего диаметра того же типа. Перед погрузкой характерные места надо взвесить.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>— Остатки недостоверны: сверка была 16.06.2025. Количества блока Б подтверждаются только пересчетом на складе.</t>
         </is>
@@ -1128,7 +1392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R230"/>
+  <dimension ref="A1:R231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1743,7 +2007,7 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>головка вентиляционная</t>
         </is>
       </c>
       <c r="E12" s="14" t="n">
@@ -2317,7 +2581,7 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>головка вентиляционная</t>
         </is>
       </c>
       <c r="E20" s="14" t="n">
@@ -2385,7 +2649,7 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>головка вентиляционная</t>
         </is>
       </c>
       <c r="E21" s="14" t="n">
@@ -2453,7 +2717,7 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>головка вентиляционная</t>
         </is>
       </c>
       <c r="E22" s="14" t="n">
@@ -3845,7 +4109,7 @@
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="E43" s="14" t="n">
@@ -3921,7 +4185,7 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="E44" s="14" t="n">
@@ -3999,7 +4263,7 @@
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>головка вентиляционная</t>
         </is>
       </c>
       <c r="E45" s="14" t="n">
@@ -4357,7 +4621,7 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан пусковой</t>
         </is>
       </c>
       <c r="E50" s="14" t="n">
@@ -4727,7 +4991,7 @@
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан пусковой</t>
         </is>
       </c>
       <c r="E55" s="14" t="n">
@@ -4805,7 +5069,7 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>стакан переборочный</t>
         </is>
       </c>
       <c r="E56" s="14" t="n">
@@ -5009,7 +5273,7 @@
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан паровой</t>
         </is>
       </c>
       <c r="E59" s="14" t="n">
@@ -5579,7 +5843,7 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>головка вентиляционная</t>
         </is>
       </c>
       <c r="E67" s="14" t="n">
@@ -5647,7 +5911,7 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="E68" s="14" t="n"/>
@@ -5717,7 +5981,7 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="E69" s="14" t="n">
@@ -5927,7 +6191,7 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E72" s="14" t="n">
@@ -6141,7 +6405,7 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E75" s="14" t="n">
@@ -6201,7 +6465,7 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>колонка указательная</t>
         </is>
       </c>
       <c r="E76" s="14" t="n">
@@ -6425,7 +6689,7 @@
       </c>
       <c r="D79" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="E79" s="14" t="n">
@@ -6503,7 +6767,7 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="E80" s="14" t="n">
@@ -6655,7 +6919,7 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E82" s="14" t="n">
@@ -6723,7 +6987,7 @@
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E83" s="14" t="n"/>
@@ -6791,7 +7055,7 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E84" s="14" t="n">
@@ -6861,7 +7125,7 @@
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="E85" s="14" t="n">
@@ -7075,7 +7339,7 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>стакан переборочный</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
@@ -7145,7 +7409,7 @@
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>стакан переборочный</t>
         </is>
       </c>
       <c r="E89" s="14" t="n">
@@ -7285,7 +7549,7 @@
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>головка вентиляционная</t>
         </is>
       </c>
       <c r="E91" s="14" t="n">
@@ -7427,7 +7691,7 @@
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E93" s="14" t="n">
@@ -7567,7 +7831,7 @@
       </c>
       <c r="D95" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>эжектор</t>
         </is>
       </c>
       <c r="E95" s="14" t="n"/>
@@ -7781,7 +8045,7 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -8015,7 +8279,7 @@
       </c>
       <c r="D101" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>стакан переборочный</t>
         </is>
       </c>
       <c r="E101" s="14" t="n">
@@ -8463,7 +8727,7 @@
       </c>
       <c r="D107" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E107" s="14" t="n">
@@ -8603,7 +8867,7 @@
       </c>
       <c r="D109" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E109" s="14" t="n">
@@ -8901,7 +9165,7 @@
       </c>
       <c r="D113" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E113" s="14" t="n">
@@ -9005,7 +9269,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M114" s="16" t="n">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="N114" s="21" t="n">
         <v>1.176</v>
@@ -9041,19 +9305,23 @@
       </c>
       <c r="D115" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E115" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F115" s="14" t="n"/>
       <c r="G115" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
-        </is>
-      </c>
-      <c r="H115" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="H115" s="14" t="inlineStr">
+        <is>
+          <t>521-01.470-03</t>
+        </is>
+      </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -9061,29 +9329,29 @@
       </c>
       <c r="J115" s="14" t="inlineStr"/>
       <c r="K115" s="14" t="n">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="L115" s="20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="M115" s="16" t="n">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="N115" s="21" t="n">
-        <v>0.312</v>
+        <v>0.204</v>
       </c>
       <c r="O115" s="14" t="n">
-        <v>22500</v>
+        <v>6000</v>
       </c>
       <c r="P115" s="14" t="inlineStr"/>
       <c r="Q115" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R115" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -9107,19 +9375,15 @@
         </is>
       </c>
       <c r="E116" s="14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F116" s="14" t="n"/>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25 Китай</t>
-        </is>
-      </c>
-      <c r="H116" s="14" t="inlineStr">
-        <is>
-          <t>М528-03.001</t>
-        </is>
-      </c>
+          <t>Клапан штуцерный проходной Ду 20</t>
+        </is>
+      </c>
+      <c r="H116" s="19" t="inlineStr"/>
       <c r="I116" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -9127,19 +9391,19 @@
       </c>
       <c r="J116" s="14" t="inlineStr"/>
       <c r="K116" s="14" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="L116" s="20" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="M116" s="16" t="n">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="N116" s="21" t="n">
-        <v>0.186</v>
+        <v>0.2</v>
       </c>
       <c r="O116" s="14" t="n">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="P116" s="14" t="inlineStr"/>
       <c r="Q116" s="15" t="inlineStr">
@@ -9149,7 +9413,7 @@
       </c>
       <c r="R116" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9169,23 +9433,19 @@
       </c>
       <c r="D117" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E117" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F117" s="14" t="n"/>
       <c r="G117" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
-        </is>
-      </c>
-      <c r="H117" s="14" t="inlineStr">
-        <is>
-          <t>521-01.470-03</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду50</t>
+        </is>
+      </c>
+      <c r="H117" s="19" t="inlineStr"/>
       <c r="I117" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -9193,29 +9453,29 @@
       </c>
       <c r="J117" s="14" t="inlineStr"/>
       <c r="K117" s="14" t="n">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="L117" s="20" t="n">
-        <v>1.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M117" s="16" t="n">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="N117" s="21" t="n">
-        <v>0.204</v>
+        <v>0.228</v>
       </c>
       <c r="O117" s="14" t="n">
-        <v>6000</v>
+        <v>22500</v>
       </c>
       <c r="P117" s="14" t="inlineStr"/>
       <c r="Q117" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R117" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9244,10 +9504,14 @@
       <c r="F118" s="14" t="n"/>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
-        </is>
-      </c>
-      <c r="H118" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>522-01.501-02</t>
+        </is>
+      </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -9255,19 +9519,19 @@
       </c>
       <c r="J118" s="14" t="inlineStr"/>
       <c r="K118" s="14" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="L118" s="20" t="n">
         <v>1.9</v>
       </c>
       <c r="M118" s="16" t="n">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="N118" s="21" t="n">
-        <v>0.2</v>
+        <v>0.144</v>
       </c>
       <c r="O118" s="14" t="n">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="P118" s="14" t="inlineStr"/>
       <c r="Q118" s="15" t="inlineStr">
@@ -9277,7 +9541,7 @@
       </c>
       <c r="R118" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -9301,39 +9565,35 @@
         </is>
       </c>
       <c r="E119" s="14" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F119" s="14" t="n"/>
       <c r="G119" s="15" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
-        </is>
-      </c>
-      <c r="H119" s="14" t="inlineStr">
-        <is>
-          <t>521-02.013</t>
-        </is>
-      </c>
+          <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
+        </is>
+      </c>
+      <c r="H119" s="19" t="inlineStr"/>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="J119" s="14" t="inlineStr"/>
       <c r="K119" s="14" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="L119" s="20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M119" s="16" t="n">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="N119" s="21" t="n">
-        <v>0.048</v>
+        <v>0.237</v>
       </c>
       <c r="O119" s="14" t="n">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="P119" s="14" t="inlineStr"/>
       <c r="Q119" s="15" t="inlineStr">
@@ -9343,7 +9603,7 @@
       </c>
       <c r="R119" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9363,21 +9623,21 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F120" s="14" t="n"/>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
         </is>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>522-01.501-02</t>
+          <t>521-03.195</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
@@ -9385,31 +9645,35 @@
           <t>не указано</t>
         </is>
       </c>
-      <c r="J120" s="14" t="inlineStr"/>
+      <c r="J120" s="23" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="K120" s="14" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="L120" s="20" t="n">
-        <v>1.9</v>
+        <v>17</v>
       </c>
       <c r="M120" s="16" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N120" s="21" t="n">
-        <v>0.144</v>
+        <v>0.16</v>
       </c>
       <c r="O120" s="14" t="n">
-        <v>6000</v>
+        <v>27000</v>
       </c>
       <c r="P120" s="14" t="inlineStr"/>
       <c r="Q120" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R120" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9429,52 +9693,44 @@
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E121" s="14" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="F121" s="14" t="n"/>
       <c r="G121" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
-        </is>
-      </c>
-      <c r="H121" s="14" t="inlineStr">
-        <is>
-          <t>521-03.195</t>
-        </is>
-      </c>
+          <t>Клапан штущерный проходной Ду15</t>
+        </is>
+      </c>
+      <c r="H121" s="19" t="inlineStr"/>
       <c r="I121" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
       </c>
-      <c r="J121" s="23" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
-        </is>
-      </c>
+      <c r="J121" s="14" t="inlineStr"/>
       <c r="K121" s="14" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="L121" s="20" t="n">
-        <v>17</v>
+        <v>2.6</v>
       </c>
       <c r="M121" s="16" t="n">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="N121" s="21" t="n">
-        <v>0.16</v>
+        <v>0.066</v>
       </c>
       <c r="O121" s="14" t="n">
-        <v>27000</v>
+        <v>9500</v>
       </c>
       <c r="P121" s="14" t="inlineStr"/>
       <c r="Q121" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R121" s="14" t="inlineStr">
@@ -9503,15 +9759,19 @@
         </is>
       </c>
       <c r="E122" s="14" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F122" s="14" t="n"/>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>Клапан штущерный проходной Ду15</t>
-        </is>
-      </c>
-      <c r="H122" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468-07</t>
+        </is>
+      </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -9519,19 +9779,19 @@
       </c>
       <c r="J122" s="14" t="inlineStr"/>
       <c r="K122" s="14" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="L122" s="20" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="M122" s="16" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="N122" s="21" t="n">
-        <v>0.066</v>
+        <v>0.155</v>
       </c>
       <c r="O122" s="14" t="n">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="P122" s="14" t="inlineStr"/>
       <c r="Q122" s="15" t="inlineStr">
@@ -9541,7 +9801,7 @@
       </c>
       <c r="R122" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -9561,44 +9821,52 @@
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E123" s="14" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F123" s="14" t="n"/>
       <c r="G123" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
-        </is>
-      </c>
-      <c r="H123" s="19" t="inlineStr"/>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="inlineStr">
+        <is>
+          <t>522-35.4154-02</t>
+        </is>
+      </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
       </c>
-      <c r="J123" s="14" t="inlineStr"/>
+      <c r="J123" s="23" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="K123" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="L123" s="20" t="n">
-        <v>3.6</v>
+        <v>17</v>
       </c>
       <c r="M123" s="16" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="N123" s="21" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="O123" s="14" t="n">
-        <v>10000</v>
+        <v>27000</v>
       </c>
       <c r="P123" s="14" t="inlineStr"/>
       <c r="Q123" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R123" s="14" t="inlineStr">
@@ -9623,21 +9891,21 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="F124" s="14" t="n"/>
       <c r="G124" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>521-01.468-07</t>
+          <t>521-03.022</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
@@ -9647,29 +9915,29 @@
       </c>
       <c r="J124" s="14" t="inlineStr"/>
       <c r="K124" s="14" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="L124" s="20" t="n">
-        <v>3.3</v>
+        <v>20</v>
       </c>
       <c r="M124" s="16" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N124" s="21" t="n">
-        <v>0.155</v>
+        <v>0.1</v>
       </c>
       <c r="O124" s="14" t="n">
-        <v>9600</v>
+        <v>35000</v>
       </c>
       <c r="P124" s="14" t="inlineStr"/>
       <c r="Q124" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R124" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9693,43 +9961,35 @@
         </is>
       </c>
       <c r="E125" s="14" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F125" s="14" t="n"/>
       <c r="G125" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
-        </is>
-      </c>
-      <c r="H125" s="14" t="inlineStr">
-        <is>
-          <t>522-35.4154-02</t>
-        </is>
-      </c>
+          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
+        </is>
+      </c>
+      <c r="H125" s="19" t="inlineStr"/>
       <c r="I125" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
       </c>
-      <c r="J125" s="23" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
-        </is>
-      </c>
+      <c r="J125" s="14" t="inlineStr"/>
       <c r="K125" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L125" s="20" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M125" s="16" t="n">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="N125" s="21" t="n">
-        <v>0.12</v>
+        <v>0.096</v>
       </c>
       <c r="O125" s="14" t="n">
-        <v>27000</v>
+        <v>18000</v>
       </c>
       <c r="P125" s="14" t="inlineStr"/>
       <c r="Q125" s="15" t="inlineStr">
@@ -9739,7 +9999,7 @@
       </c>
       <c r="R125" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -9763,19 +10023,15 @@
         </is>
       </c>
       <c r="E126" s="14" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F126" s="14" t="n"/>
       <c r="G126" s="15" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
-        </is>
-      </c>
-      <c r="H126" s="14" t="inlineStr">
-        <is>
-          <t>521-03.022</t>
-        </is>
-      </c>
+          <t>Клапан проходной фланцевый Ду40 - БРАК</t>
+        </is>
+      </c>
+      <c r="H126" s="19" t="inlineStr"/>
       <c r="I126" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -9783,29 +10039,29 @@
       </c>
       <c r="J126" s="14" t="inlineStr"/>
       <c r="K126" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L126" s="20" t="n">
-        <v>17</v>
+        <v>5.6</v>
       </c>
       <c r="M126" s="16" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="N126" s="21" t="n">
-        <v>0.1</v>
+        <v>0.104</v>
       </c>
       <c r="O126" s="14" t="n">
-        <v>35000</v>
+        <v>12000</v>
       </c>
       <c r="P126" s="14" t="inlineStr"/>
       <c r="Q126" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R126" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -9825,19 +10081,23 @@
       </c>
       <c r="D127" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E127" s="14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F127" s="14" t="n"/>
       <c r="G127" s="15" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
-        </is>
-      </c>
-      <c r="H127" s="19" t="inlineStr"/>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
+        </is>
+      </c>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>521-03.020</t>
+        </is>
+      </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -9845,29 +10105,29 @@
       </c>
       <c r="J127" s="14" t="inlineStr"/>
       <c r="K127" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L127" s="20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="M127" s="16" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N127" s="21" t="n">
-        <v>0.096</v>
+        <v>0.056</v>
       </c>
       <c r="O127" s="14" t="n">
-        <v>18000</v>
+        <v>26000</v>
       </c>
       <c r="P127" s="14" t="inlineStr"/>
       <c r="Q127" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R127" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9887,21 +10147,21 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F128" s="14" t="n"/>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду70 Ру6,3</t>
         </is>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>521-03.020</t>
+          <t>БЕЗ ЧЕРТЕЖА</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
@@ -9911,29 +10171,29 @@
       </c>
       <c r="J128" s="14" t="inlineStr"/>
       <c r="K128" s="14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L128" s="20" t="n">
-        <v>9.1</v>
+        <v>23</v>
       </c>
       <c r="M128" s="16" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="N128" s="21" t="n">
-        <v>0.056</v>
+        <v>0.066</v>
       </c>
       <c r="O128" s="14" t="n">
-        <v>26000</v>
+        <v>40000</v>
       </c>
       <c r="P128" s="14" t="inlineStr"/>
       <c r="Q128" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R128" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -9953,43 +10213,43 @@
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>кран</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E129" s="14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F129" s="14" t="n"/>
       <c r="G129" s="15" t="inlineStr">
         <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
         </is>
       </c>
       <c r="H129" s="14" t="inlineStr">
         <is>
-          <t>528-3М129</t>
+          <t>521-02.013</t>
         </is>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="J129" s="14" t="inlineStr"/>
       <c r="K129" s="14" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="L129" s="20" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="M129" s="16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N129" s="21" t="n">
-        <v>0.066</v>
+        <v>0.048</v>
       </c>
       <c r="O129" s="14" t="n">
-        <v>9000</v>
+        <v>4500</v>
       </c>
       <c r="P129" s="14" t="inlineStr"/>
       <c r="Q129" s="15" t="inlineStr">
@@ -10019,21 +10279,21 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>кран</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F130" s="14" t="n"/>
       <c r="G130" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32 Ру100</t>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
         </is>
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>521-01.468-07</t>
+          <t>528-3М129</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
@@ -10043,19 +10303,19 @@
       </c>
       <c r="J130" s="14" t="inlineStr"/>
       <c r="K130" s="14" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L130" s="20" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="M130" s="16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N130" s="21" t="n">
-        <v>0.095</v>
+        <v>0.066</v>
       </c>
       <c r="O130" s="14" t="n">
-        <v>9600</v>
+        <v>9000</v>
       </c>
       <c r="P130" s="14" t="inlineStr"/>
       <c r="Q130" s="15" t="inlineStr">
@@ -10065,7 +10325,7 @@
       </c>
       <c r="R130" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -10085,21 +10345,21 @@
       </c>
       <c r="D131" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E131" s="14" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F131" s="14" t="n"/>
       <c r="G131" s="15" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду70 Ру6,3</t>
+          <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr">
         <is>
-          <t>БЕЗ ЧЕРТЕЖА</t>
+          <t>521-01.468-07</t>
         </is>
       </c>
       <c r="I131" s="14" t="inlineStr">
@@ -10109,29 +10369,29 @@
       </c>
       <c r="J131" s="14" t="inlineStr"/>
       <c r="K131" s="14" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L131" s="20" t="n">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="M131" s="16" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N131" s="21" t="n">
-        <v>0.066</v>
+        <v>0.095</v>
       </c>
       <c r="O131" s="14" t="n">
-        <v>40000</v>
+        <v>9600</v>
       </c>
       <c r="P131" s="14" t="inlineStr"/>
       <c r="Q131" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R131" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10485,19 +10745,23 @@
       </c>
       <c r="D137" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E137" s="14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F137" s="14" t="n"/>
       <c r="G137" s="15" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
-        </is>
-      </c>
-      <c r="H137" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="H137" s="14" t="inlineStr">
+        <is>
+          <t>522-01.498-02</t>
+        </is>
+      </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -10505,19 +10769,19 @@
       </c>
       <c r="J137" s="14" t="inlineStr"/>
       <c r="K137" s="14" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L137" s="20" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="M137" s="16" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N137" s="21" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="O137" s="14" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="P137" s="14" t="inlineStr"/>
       <c r="Q137" s="15" t="inlineStr">
@@ -10527,7 +10791,7 @@
       </c>
       <c r="R137" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10811,7 @@
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10556,10 +10820,14 @@
       <c r="F138" s="14" t="n"/>
       <c r="G138" s="15" t="inlineStr">
         <is>
-          <t>Захлопка Ду50Ру6 - БРАК</t>
-        </is>
-      </c>
-      <c r="H138" s="19" t="inlineStr"/>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+        </is>
+      </c>
+      <c r="H138" s="14" t="inlineStr">
+        <is>
+          <t>595-03.011</t>
+        </is>
+      </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -10570,16 +10838,16 @@
         <v>3</v>
       </c>
       <c r="L138" s="20" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M138" s="16" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="N138" s="21" t="n">
         <v>0.036</v>
       </c>
       <c r="O138" s="14" t="n">
-        <v>17500</v>
+        <v>25000</v>
       </c>
       <c r="P138" s="14" t="inlineStr"/>
       <c r="Q138" s="15" t="inlineStr">
@@ -10589,7 +10857,7 @@
       </c>
       <c r="R138" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10877,7 @@
       </c>
       <c r="D139" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E139" s="14" t="n">
@@ -10618,12 +10886,12 @@
       <c r="F139" s="14" t="n"/>
       <c r="G139" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr">
         <is>
-          <t>522-01.498-02</t>
+          <t>521-3М.324</t>
         </is>
       </c>
       <c r="I139" s="14" t="inlineStr">
@@ -10633,19 +10901,19 @@
       </c>
       <c r="J139" s="14" t="inlineStr"/>
       <c r="K139" s="14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L139" s="20" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="M139" s="16" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N139" s="21" t="n">
-        <v>0.032</v>
+        <v>0.016</v>
       </c>
       <c r="O139" s="14" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="P139" s="14" t="inlineStr"/>
       <c r="Q139" s="15" t="inlineStr">
@@ -10655,7 +10923,7 @@
       </c>
       <c r="R139" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10943,7 @@
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10684,14 +10952,10 @@
       <c r="F140" s="14" t="n"/>
       <c r="G140" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
-        </is>
-      </c>
-      <c r="H140" s="14" t="inlineStr">
-        <is>
-          <t>521-01.180</t>
-        </is>
-      </c>
+          <t>Клапан штуцерный угловой Ду32</t>
+        </is>
+      </c>
+      <c r="H140" s="19" t="inlineStr"/>
       <c r="I140" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -10699,19 +10963,19 @@
       </c>
       <c r="J140" s="14" t="inlineStr"/>
       <c r="K140" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L140" s="20" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="M140" s="16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N140" s="21" t="n">
-        <v>0.025</v>
+        <v>0.04</v>
       </c>
       <c r="O140" s="14" t="n">
-        <v>14000</v>
+        <v>9600</v>
       </c>
       <c r="P140" s="14" t="inlineStr"/>
       <c r="Q140" s="15" t="inlineStr">
@@ -10741,16 +11005,16 @@
       </c>
       <c r="D141" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E141" s="14" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F141" s="14" t="n"/>
       <c r="G141" s="15" t="inlineStr">
         <is>
-          <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
+          <t>Клапан штуцерный угловой Ду15</t>
         </is>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
@@ -10761,19 +11025,19 @@
       </c>
       <c r="J141" s="14" t="inlineStr"/>
       <c r="K141" s="14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L141" s="20" t="n">
-        <v>9.1</v>
+        <v>2.6</v>
       </c>
       <c r="M141" s="16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N141" s="21" t="n">
-        <v>0.024</v>
+        <v>0.015</v>
       </c>
       <c r="O141" s="14" t="n">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="P141" s="14" t="inlineStr"/>
       <c r="Q141" s="15" t="inlineStr">
@@ -10783,7 +11047,7 @@
       </c>
       <c r="R141" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -10803,7 +11067,7 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10812,12 +11076,12 @@
       <c r="F142" s="14" t="n"/>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>521-3М.324</t>
+          <t>521-01.470-02</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
@@ -10827,19 +11091,19 @@
       </c>
       <c r="J142" s="14" t="inlineStr"/>
       <c r="K142" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L142" s="20" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="M142" s="16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N142" s="21" t="n">
-        <v>0.016</v>
+        <v>0.026</v>
       </c>
       <c r="O142" s="14" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="P142" s="14" t="inlineStr"/>
       <c r="Q142" s="15" t="inlineStr">
@@ -10849,7 +11113,7 @@
       </c>
       <c r="R142" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10873,15 +11137,19 @@
         </is>
       </c>
       <c r="E143" s="14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F143" s="14" t="n"/>
       <c r="G143" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32</t>
-        </is>
-      </c>
-      <c r="H143" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="H143" s="14" t="inlineStr">
+        <is>
+          <t>521-01474-03</t>
+        </is>
+      </c>
       <c r="I143" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -10889,19 +11157,19 @@
       </c>
       <c r="J143" s="14" t="inlineStr"/>
       <c r="K143" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L143" s="20" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="M143" s="16" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N143" s="21" t="n">
-        <v>0.04</v>
+        <v>0.022</v>
       </c>
       <c r="O143" s="14" t="n">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="P143" s="14" t="inlineStr"/>
       <c r="Q143" s="15" t="inlineStr">
@@ -10911,7 +11179,7 @@
       </c>
       <c r="R143" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10935,15 +11203,19 @@
         </is>
       </c>
       <c r="E144" s="14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F144" s="14" t="n"/>
       <c r="G144" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15</t>
-        </is>
-      </c>
-      <c r="H144" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr">
+        <is>
+          <t>521 3м 623</t>
+        </is>
+      </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -10951,19 +11223,19 @@
       </c>
       <c r="J144" s="14" t="inlineStr"/>
       <c r="K144" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L144" s="20" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="M144" s="16" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N144" s="21" t="n">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="O144" s="14" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="P144" s="14" t="inlineStr"/>
       <c r="Q144" s="15" t="inlineStr">
@@ -10973,7 +11245,7 @@
       </c>
       <c r="R144" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10993,21 +11265,21 @@
       </c>
       <c r="D145" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E145" s="14" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F145" s="14" t="n"/>
       <c r="G145" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду65 Ру6,3</t>
         </is>
       </c>
       <c r="H145" s="14" t="inlineStr">
         <is>
-          <t>521-01.470-02</t>
+          <t>521-03-022</t>
         </is>
       </c>
       <c r="I145" s="14" t="inlineStr">
@@ -11017,29 +11289,29 @@
       </c>
       <c r="J145" s="14" t="inlineStr"/>
       <c r="K145" s="14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L145" s="20" t="n">
-        <v>1.9</v>
+        <v>20</v>
       </c>
       <c r="M145" s="16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N145" s="21" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="O145" s="14" t="n">
-        <v>6000</v>
+        <v>35000</v>
       </c>
       <c r="P145" s="14" t="inlineStr"/>
       <c r="Q145" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R145" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11059,21 +11331,21 @@
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F146" s="14" t="n"/>
       <c r="G146" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>521-01474-03</t>
+          <t>без чертежа</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
@@ -11083,24 +11355,24 @@
       </c>
       <c r="J146" s="14" t="inlineStr"/>
       <c r="K146" s="14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L146" s="20" t="n">
-        <v>1.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M146" s="16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N146" s="21" t="n">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="O146" s="14" t="n">
-        <v>6000</v>
+        <v>25000</v>
       </c>
       <c r="P146" s="14" t="inlineStr"/>
       <c r="Q146" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R146" s="14" t="inlineStr">
@@ -11129,17 +11401,17 @@
         </is>
       </c>
       <c r="E147" s="14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F147" s="14" t="n"/>
       <c r="G147" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="H147" s="14" t="inlineStr">
         <is>
-          <t>521 3м 623</t>
+          <t>521-01.468</t>
         </is>
       </c>
       <c r="I147" s="14" t="inlineStr">
@@ -11149,16 +11421,16 @@
       </c>
       <c r="J147" s="14" t="inlineStr"/>
       <c r="K147" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L147" s="20" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="M147" s="16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N147" s="21" t="n">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="O147" s="14" t="n">
         <v>6000</v>
@@ -11191,19 +11463,23 @@
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F148" s="14" t="n"/>
       <c r="G148" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
-        </is>
-      </c>
-      <c r="H148" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="H148" s="14" t="inlineStr">
+        <is>
+          <t>522-01500-05</t>
+        </is>
+      </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -11211,29 +11487,29 @@
       </c>
       <c r="J148" s="14" t="inlineStr"/>
       <c r="K148" s="14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L148" s="20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="M148" s="16" t="n">
         <v>18</v>
       </c>
       <c r="N148" s="21" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="O148" s="14" t="n">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="P148" s="14" t="inlineStr"/>
       <c r="Q148" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R148" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -11262,14 +11538,10 @@
       <c r="F149" s="14" t="n"/>
       <c r="G149" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
-        </is>
-      </c>
-      <c r="H149" s="14" t="inlineStr">
-        <is>
-          <t>522-35.445-19</t>
-        </is>
-      </c>
+          <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
+        </is>
+      </c>
+      <c r="H149" s="19" t="inlineStr"/>
       <c r="I149" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -11277,16 +11549,16 @@
       </c>
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L149" s="20" t="n">
-        <v>9.1</v>
+        <v>5.6</v>
       </c>
       <c r="M149" s="16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N149" s="21" t="n">
-        <v>0.016</v>
+        <v>0.024</v>
       </c>
       <c r="O149" s="14" t="n">
         <v>18000</v>
@@ -11299,7 +11571,7 @@
       </c>
       <c r="R149" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -11323,17 +11595,17 @@
         </is>
       </c>
       <c r="E150" s="14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F150" s="14" t="n"/>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr">
         <is>
-          <t>521-01.468</t>
+          <t>521-01.469-03</t>
         </is>
       </c>
       <c r="I150" s="14" t="inlineStr">
@@ -11346,16 +11618,16 @@
         <v>7</v>
       </c>
       <c r="L150" s="20" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M150" s="16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N150" s="21" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="O150" s="14" t="n">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="P150" s="14" t="inlineStr"/>
       <c r="Q150" s="15" t="inlineStr">
@@ -11365,7 +11637,7 @@
       </c>
       <c r="R150" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11389,17 +11661,17 @@
         </is>
       </c>
       <c r="E151" s="14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F151" s="14" t="n"/>
       <c r="G151" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="H151" s="14" t="inlineStr">
         <is>
-          <t>522-01500-05</t>
+          <t>521-01.464-01</t>
         </is>
       </c>
       <c r="I151" s="14" t="inlineStr">
@@ -11409,16 +11681,16 @@
       </c>
       <c r="J151" s="14" t="inlineStr"/>
       <c r="K151" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L151" s="20" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="M151" s="16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N151" s="21" t="n">
-        <v>0.018</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O151" s="14" t="n">
         <v>6000</v>
@@ -11451,21 +11723,21 @@
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F152" s="14" t="n"/>
       <c r="G152" s="15" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду65 Ру6,3</t>
+          <t>Клапан штуцерный угловой Ду25 Ру100</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr">
         <is>
-          <t>521-03-022</t>
+          <t>521-01.468-06</t>
         </is>
       </c>
       <c r="I152" s="14" t="inlineStr">
@@ -11475,29 +11747,29 @@
       </c>
       <c r="J152" s="14" t="inlineStr"/>
       <c r="K152" s="14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L152" s="20" t="n">
-        <v>17</v>
+        <v>1.8</v>
       </c>
       <c r="M152" s="16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N152" s="21" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="O152" s="14" t="n">
-        <v>35000</v>
+        <v>7500</v>
       </c>
       <c r="P152" s="14" t="inlineStr"/>
       <c r="Q152" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R152" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -11521,17 +11793,17 @@
         </is>
       </c>
       <c r="E153" s="14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F153" s="14" t="n"/>
       <c r="G153" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
         </is>
       </c>
       <c r="H153" s="14" t="inlineStr">
         <is>
-          <t>521-01.464-01</t>
+          <t>521-35.2754</t>
         </is>
       </c>
       <c r="I153" s="14" t="inlineStr">
@@ -11544,16 +11816,16 @@
         <v>6</v>
       </c>
       <c r="L153" s="20" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M153" s="16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N153" s="21" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="O153" s="14" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="P153" s="14" t="inlineStr"/>
       <c r="Q153" s="15" t="inlineStr">
@@ -11563,7 +11835,7 @@
       </c>
       <c r="R153" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11587,17 +11859,17 @@
         </is>
       </c>
       <c r="E154" s="14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F154" s="14" t="n"/>
       <c r="G154" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr">
         <is>
-          <t>521-01464-03</t>
+          <t>522-03,149</t>
         </is>
       </c>
       <c r="I154" s="14" t="inlineStr">
@@ -11607,19 +11879,19 @@
       </c>
       <c r="J154" s="14" t="inlineStr"/>
       <c r="K154" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L154" s="20" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M154" s="16" t="n">
         <v>14</v>
       </c>
       <c r="N154" s="21" t="n">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="O154" s="14" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="P154" s="14" t="inlineStr"/>
       <c r="Q154" s="15" t="inlineStr">
@@ -11629,7 +11901,7 @@
       </c>
       <c r="R154" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11652,16 +11924,18 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="E155" s="14" t="n"/>
+      <c r="E155" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="F155" s="14" t="n"/>
       <c r="G155" s="15" t="inlineStr">
         <is>
-          <t>Клапан для манометра штуцерный сальниковый</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="H155" s="14" t="inlineStr">
         <is>
-          <t>521-34.3404-03</t>
+          <t>521-01464-03</t>
         </is>
       </c>
       <c r="I155" s="14" t="inlineStr">
@@ -11671,16 +11945,16 @@
       </c>
       <c r="J155" s="14" t="inlineStr"/>
       <c r="K155" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L155" s="20" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="M155" s="16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N155" s="21" t="n">
-        <v>0.1</v>
+        <v>0.014</v>
       </c>
       <c r="O155" s="14" t="n">
         <v>6000</v>
@@ -11713,21 +11987,19 @@
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="E156" s="14" t="n">
-        <v>32</v>
-      </c>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="n"/>
       <c r="F156" s="14" t="n"/>
       <c r="G156" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
+          <t>Клапан для манометра штуцерный сальниковый</t>
         </is>
       </c>
       <c r="H156" s="14" t="inlineStr">
         <is>
-          <t>УН522-3М38</t>
+          <t>521-34.3404-03</t>
         </is>
       </c>
       <c r="I156" s="14" t="inlineStr">
@@ -11737,19 +12009,19 @@
       </c>
       <c r="J156" s="14" t="inlineStr"/>
       <c r="K156" s="14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L156" s="20" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="M156" s="16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N156" s="21" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="O156" s="14" t="n">
-        <v>14000</v>
+        <v>6000</v>
       </c>
       <c r="P156" s="14" t="inlineStr"/>
       <c r="Q156" s="15" t="inlineStr">
@@ -11759,7 +12031,7 @@
       </c>
       <c r="R156" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -11783,17 +12055,17 @@
         </is>
       </c>
       <c r="E157" s="14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F157" s="14" t="n"/>
       <c r="G157" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
       <c r="H157" s="14" t="inlineStr">
         <is>
-          <t>521-03.387</t>
+          <t>522-01-493</t>
         </is>
       </c>
       <c r="I157" s="14" t="inlineStr">
@@ -11803,19 +12075,19 @@
       </c>
       <c r="J157" s="14" t="inlineStr"/>
       <c r="K157" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L157" s="20" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M157" s="16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N157" s="21" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="O157" s="14" t="n">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="P157" s="14" t="inlineStr"/>
       <c r="Q157" s="15" t="inlineStr">
@@ -11845,19 +12117,21 @@
       </c>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="E158" s="14" t="n"/>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E158" s="14" t="n">
+        <v>40</v>
+      </c>
       <c r="F158" s="14" t="n"/>
       <c r="G158" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr">
         <is>
-          <t>521-ц22п</t>
+          <t>522-35.445-19</t>
         </is>
       </c>
       <c r="I158" s="14" t="inlineStr">
@@ -11867,19 +12141,19 @@
       </c>
       <c r="J158" s="14" t="inlineStr"/>
       <c r="K158" s="14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L158" s="20" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="M158" s="16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N158" s="21" t="n">
-        <v>0.08</v>
+        <v>0.016</v>
       </c>
       <c r="O158" s="14" t="n">
-        <v>4000</v>
+        <v>18000</v>
       </c>
       <c r="P158" s="14" t="inlineStr"/>
       <c r="Q158" s="15" t="inlineStr">
@@ -11913,19 +12187,15 @@
         </is>
       </c>
       <c r="E159" s="14" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F159" s="14" t="n"/>
       <c r="G159" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
-        </is>
-      </c>
-      <c r="H159" s="14" t="inlineStr">
-        <is>
-          <t>521.3м.660</t>
-        </is>
-      </c>
+          <t>Клапан штуцерный угловой Ду25</t>
+        </is>
+      </c>
+      <c r="H159" s="19" t="inlineStr"/>
       <c r="I159" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -11933,19 +12203,19 @@
       </c>
       <c r="J159" s="14" t="inlineStr"/>
       <c r="K159" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L159" s="20" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="M159" s="16" t="n">
         <v>10</v>
       </c>
       <c r="N159" s="21" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="O159" s="14" t="n">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="P159" s="14" t="inlineStr"/>
       <c r="Q159" s="15" t="inlineStr">
@@ -11955,7 +12225,7 @@
       </c>
       <c r="R159" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11979,17 +12249,17 @@
         </is>
       </c>
       <c r="E160" s="14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F160" s="14" t="n"/>
       <c r="G160" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr">
         <is>
-          <t>Без чертежа</t>
+          <t>521-03.387</t>
         </is>
       </c>
       <c r="I160" s="14" t="inlineStr">
@@ -11999,19 +12269,19 @@
       </c>
       <c r="J160" s="14" t="inlineStr"/>
       <c r="K160" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L160" s="20" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="M160" s="16" t="n">
         <v>10</v>
       </c>
       <c r="N160" s="21" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="O160" s="14" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="P160" s="14" t="inlineStr"/>
       <c r="Q160" s="15" t="inlineStr">
@@ -12021,7 +12291,7 @@
       </c>
       <c r="R160" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -12044,18 +12314,16 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="E161" s="14" t="n">
-        <v>20</v>
-      </c>
+      <c r="E161" s="14" t="n"/>
       <c r="F161" s="14" t="n"/>
       <c r="G161" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру100</t>
+          <t>Клапан штуцерный угловой Рр150/10</t>
         </is>
       </c>
       <c r="H161" s="14" t="inlineStr">
         <is>
-          <t>521-01.468-05</t>
+          <t>521-ц22п</t>
         </is>
       </c>
       <c r="I161" s="14" t="inlineStr">
@@ -12065,19 +12333,19 @@
       </c>
       <c r="J161" s="14" t="inlineStr"/>
       <c r="K161" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L161" s="20" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="M161" s="16" t="n">
         <v>10</v>
       </c>
       <c r="N161" s="21" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="O161" s="14" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="P161" s="14" t="inlineStr"/>
       <c r="Q161" s="15" t="inlineStr">
@@ -12107,19 +12375,23 @@
       </c>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E162" s="14" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F162" s="14" t="n"/>
       <c r="G162" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
-        </is>
-      </c>
-      <c r="H162" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
+        </is>
+      </c>
+      <c r="H162" s="14" t="inlineStr">
+        <is>
+          <t>521.3м.660</t>
+        </is>
+      </c>
       <c r="I162" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -12127,29 +12399,29 @@
       </c>
       <c r="J162" s="14" t="inlineStr"/>
       <c r="K162" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L162" s="20" t="n">
-        <v>9.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="M162" s="16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N162" s="21" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="O162" s="14" t="n">
-        <v>25000</v>
+        <v>12500</v>
       </c>
       <c r="P162" s="14" t="inlineStr"/>
       <c r="Q162" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R162" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12169,21 +12441,21 @@
       </c>
       <c r="D163" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E163" s="14" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F163" s="14" t="n"/>
       <c r="G163" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
         </is>
       </c>
       <c r="H163" s="14" t="inlineStr">
         <is>
-          <t>521-01.200</t>
+          <t>Без чертежа</t>
         </is>
       </c>
       <c r="I163" s="14" t="inlineStr">
@@ -12191,25 +12463,21 @@
           <t>не указано</t>
         </is>
       </c>
-      <c r="J163" s="23" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
-        </is>
-      </c>
+      <c r="J163" s="14" t="inlineStr"/>
       <c r="K163" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L163" s="20" t="n">
-        <v>9.1</v>
+        <v>1.9</v>
       </c>
       <c r="M163" s="16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N163" s="21" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="O163" s="14" t="n">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="P163" s="14" t="inlineStr"/>
       <c r="Q163" s="15" t="inlineStr">
@@ -12219,7 +12487,7 @@
       </c>
       <c r="R163" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12239,21 +12507,21 @@
       </c>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E164" s="14" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F164" s="14" t="n"/>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру10</t>
+          <t>Клапан штуцерный угловой Ду20 Ру100</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr">
         <is>
-          <t>522-03.202</t>
+          <t>521-01.468-05</t>
         </is>
       </c>
       <c r="I164" s="14" t="inlineStr">
@@ -12261,25 +12529,21 @@
           <t>не указано</t>
         </is>
       </c>
-      <c r="J164" s="23" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
-        </is>
-      </c>
+      <c r="J164" s="14" t="inlineStr"/>
       <c r="K164" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L164" s="20" t="n">
-        <v>9.1</v>
+        <v>1.9</v>
       </c>
       <c r="M164" s="16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N164" s="21" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="O164" s="14" t="n">
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="P164" s="14" t="inlineStr"/>
       <c r="Q164" s="15" t="inlineStr">
@@ -12289,7 +12553,7 @@
       </c>
       <c r="R164" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -12309,23 +12573,19 @@
       </c>
       <c r="D165" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E165" s="14" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F165" s="14" t="n"/>
       <c r="G165" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
-        </is>
-      </c>
-      <c r="H165" s="14" t="inlineStr">
-        <is>
-          <t>522-01.500-04</t>
-        </is>
-      </c>
+          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
+        </is>
+      </c>
+      <c r="H165" s="19" t="inlineStr"/>
       <c r="I165" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -12333,19 +12593,19 @@
       </c>
       <c r="J165" s="14" t="inlineStr"/>
       <c r="K165" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L165" s="20" t="n">
-        <v>2.6</v>
+        <v>9.5</v>
       </c>
       <c r="M165" s="16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N165" s="21" t="n">
         <v>0.005</v>
       </c>
       <c r="O165" s="14" t="n">
-        <v>6000</v>
+        <v>9600</v>
       </c>
       <c r="P165" s="14" t="inlineStr"/>
       <c r="Q165" s="15" t="inlineStr">
@@ -12355,7 +12615,7 @@
       </c>
       <c r="R165" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -12375,21 +12635,21 @@
       </c>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E166" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F166" s="14" t="n"/>
       <c r="G166" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="H166" s="14" t="inlineStr">
         <is>
-          <t>536-3м 5</t>
+          <t>595-03.008</t>
         </is>
       </c>
       <c r="I166" s="14" t="inlineStr">
@@ -12399,24 +12659,24 @@
       </c>
       <c r="J166" s="14" t="inlineStr"/>
       <c r="K166" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L166" s="20" t="n">
-        <v>1.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M166" s="16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N166" s="21" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="O166" s="14" t="n">
-        <v>6500</v>
+        <v>25000</v>
       </c>
       <c r="P166" s="14" t="inlineStr"/>
       <c r="Q166" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R166" s="14" t="inlineStr">
@@ -12441,21 +12701,21 @@
       </c>
       <c r="D167" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E167" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F167" s="14" t="n"/>
       <c r="G167" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
         </is>
       </c>
       <c r="H167" s="14" t="inlineStr">
         <is>
-          <t>Без чертежа</t>
+          <t>595-01.002</t>
         </is>
       </c>
       <c r="I167" s="14" t="inlineStr">
@@ -12465,24 +12725,24 @@
       </c>
       <c r="J167" s="14" t="inlineStr"/>
       <c r="K167" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L167" s="20" t="n">
-        <v>1.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M167" s="16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N167" s="21" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="O167" s="14" t="n">
-        <v>6000</v>
+        <v>22500</v>
       </c>
       <c r="P167" s="14" t="inlineStr"/>
       <c r="Q167" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R167" s="14" t="inlineStr">
@@ -12507,23 +12767,19 @@
       </c>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E168" s="14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F168" s="14" t="n"/>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
-        </is>
-      </c>
-      <c r="H168" s="14" t="inlineStr">
-        <is>
-          <t>521-03.420</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
+        </is>
+      </c>
+      <c r="H168" s="19" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -12531,29 +12787,29 @@
       </c>
       <c r="J168" s="14" t="inlineStr"/>
       <c r="K168" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L168" s="20" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M168" s="16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N168" s="21" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="O168" s="14" t="n">
-        <v>6000</v>
+        <v>25000</v>
       </c>
       <c r="P168" s="14" t="inlineStr"/>
       <c r="Q168" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R168" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -12577,17 +12833,17 @@
         </is>
       </c>
       <c r="E169" s="14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F169" s="14" t="n"/>
       <c r="G169" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="H169" s="14" t="inlineStr">
         <is>
-          <t>522 3м 13</t>
+          <t>522-01.500-04</t>
         </is>
       </c>
       <c r="I169" s="14" t="inlineStr">
@@ -12600,13 +12856,13 @@
         <v>3</v>
       </c>
       <c r="L169" s="20" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="M169" s="16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N169" s="21" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="O169" s="14" t="n">
         <v>6000</v>
@@ -12648,12 +12904,12 @@
       <c r="F170" s="14" t="n"/>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr">
         <is>
-          <t>521-01464-02</t>
+          <t>536-3м 5</t>
         </is>
       </c>
       <c r="I170" s="14" t="inlineStr">
@@ -12663,19 +12919,19 @@
       </c>
       <c r="J170" s="14" t="inlineStr"/>
       <c r="K170" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L170" s="20" t="n">
         <v>1.9</v>
       </c>
       <c r="M170" s="16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N170" s="21" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="O170" s="14" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="P170" s="14" t="inlineStr"/>
       <c r="Q170" s="15" t="inlineStr">
@@ -12705,19 +12961,23 @@
       </c>
       <c r="D171" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E171" s="14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F171" s="14" t="n"/>
       <c r="G171" s="15" t="inlineStr">
         <is>
-          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
-        </is>
-      </c>
-      <c r="H171" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="H171" s="14" t="inlineStr">
+        <is>
+          <t>Без чертежа</t>
+        </is>
+      </c>
       <c r="I171" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -12725,19 +12985,19 @@
       </c>
       <c r="J171" s="14" t="inlineStr"/>
       <c r="K171" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L171" s="20" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="M171" s="16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N171" s="21" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="O171" s="14" t="n">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="P171" s="14" t="inlineStr"/>
       <c r="Q171" s="15" t="inlineStr">
@@ -12747,7 +13007,7 @@
       </c>
       <c r="R171" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12767,21 +13027,21 @@
       </c>
       <c r="D172" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E172" s="14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F172" s="14" t="n"/>
       <c r="G172" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr">
         <is>
-          <t>521-3М539</t>
+          <t>522 3м 13</t>
         </is>
       </c>
       <c r="I172" s="14" t="inlineStr">
@@ -12789,25 +13049,21 @@
           <t>не указано</t>
         </is>
       </c>
-      <c r="J172" s="23" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
-        </is>
-      </c>
+      <c r="J172" s="14" t="inlineStr"/>
       <c r="K172" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L172" s="20" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="M172" s="16" t="n">
         <v>6</v>
       </c>
       <c r="N172" s="21" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="O172" s="14" t="n">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="P172" s="14" t="inlineStr"/>
       <c r="Q172" s="15" t="inlineStr">
@@ -12817,7 +13073,7 @@
       </c>
       <c r="R172" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12837,21 +13093,21 @@
       </c>
       <c r="D173" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E173" s="14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F173" s="14" t="n"/>
       <c r="G173" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ25 ???</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="H173" s="14" t="inlineStr">
         <is>
-          <t>с камчатки</t>
+          <t>521-01464-02</t>
         </is>
       </c>
       <c r="I173" s="14" t="inlineStr">
@@ -12861,19 +13117,19 @@
       </c>
       <c r="J173" s="14" t="inlineStr"/>
       <c r="K173" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L173" s="20" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="M173" s="16" t="n">
         <v>6</v>
       </c>
       <c r="N173" s="21" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="O173" s="14" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="P173" s="14" t="inlineStr"/>
       <c r="Q173" s="15" t="inlineStr">
@@ -12883,7 +13139,7 @@
       </c>
       <c r="R173" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12903,21 +13159,21 @@
       </c>
       <c r="D174" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E174" s="14" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F174" s="14" t="n"/>
       <c r="G174" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr">
         <is>
-          <t>521. 3м.666</t>
+          <t>521-01.200</t>
         </is>
       </c>
       <c r="I174" s="14" t="inlineStr">
@@ -12925,21 +13181,25 @@
           <t>не указано</t>
         </is>
       </c>
-      <c r="J174" s="14" t="inlineStr"/>
+      <c r="J174" s="23" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="K174" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L174" s="20" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="M174" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N174" s="21" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="O174" s="14" t="n">
-        <v>6500</v>
+        <v>18000</v>
       </c>
       <c r="P174" s="14" t="inlineStr"/>
       <c r="Q174" s="15" t="inlineStr">
@@ -12949,7 +13209,7 @@
       </c>
       <c r="R174" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -12969,21 +13229,21 @@
       </c>
       <c r="D175" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E175" s="14" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F175" s="14" t="n"/>
       <c r="G175" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+          <t>Клапан фланцевый угловой Ду40 Ру10</t>
         </is>
       </c>
       <c r="H175" s="14" t="inlineStr">
         <is>
-          <t>522-01.498</t>
+          <t>522-03.202</t>
         </is>
       </c>
       <c r="I175" s="14" t="inlineStr">
@@ -12991,21 +13251,25 @@
           <t>не указано</t>
         </is>
       </c>
-      <c r="J175" s="14" t="inlineStr"/>
+      <c r="J175" s="23" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="K175" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L175" s="20" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="M175" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N175" s="21" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="O175" s="14" t="n">
-        <v>6500</v>
+        <v>16000</v>
       </c>
       <c r="P175" s="14" t="inlineStr"/>
       <c r="Q175" s="15" t="inlineStr">
@@ -13015,7 +13279,7 @@
       </c>
       <c r="R175" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -13035,21 +13299,21 @@
       </c>
       <c r="D176" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E176" s="14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F176" s="14" t="n"/>
       <c r="G176" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру40</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="H176" s="14" t="inlineStr">
         <is>
-          <t>521-01.465-02</t>
+          <t>521-3М539</t>
         </is>
       </c>
       <c r="I176" s="14" t="inlineStr">
@@ -13057,21 +13321,25 @@
           <t>не указано</t>
         </is>
       </c>
-      <c r="J176" s="14" t="inlineStr"/>
+      <c r="J176" s="23" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="K176" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L176" s="20" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="M176" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N176" s="21" t="n">
         <v>0.003</v>
       </c>
       <c r="O176" s="14" t="n">
-        <v>6000</v>
+        <v>9600</v>
       </c>
       <c r="P176" s="14" t="inlineStr"/>
       <c r="Q176" s="15" t="inlineStr">
@@ -13081,7 +13349,7 @@
       </c>
       <c r="R176" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -13101,21 +13369,21 @@
       </c>
       <c r="D177" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E177" s="14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F177" s="14" t="n"/>
       <c r="G177" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Клапан фланцевый проходной ДУ25 ???</t>
         </is>
       </c>
       <c r="H177" s="14" t="inlineStr">
         <is>
-          <t>521-35.3362</t>
+          <t>с камчатки</t>
         </is>
       </c>
       <c r="I177" s="14" t="inlineStr">
@@ -13125,19 +13393,19 @@
       </c>
       <c r="J177" s="14" t="inlineStr"/>
       <c r="K177" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L177" s="20" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="M177" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N177" s="21" t="n">
         <v>0.003</v>
       </c>
       <c r="O177" s="14" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="P177" s="14" t="inlineStr"/>
       <c r="Q177" s="15" t="inlineStr">
@@ -13147,7 +13415,7 @@
       </c>
       <c r="R177" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -13171,17 +13439,17 @@
         </is>
       </c>
       <c r="E178" s="14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F178" s="14" t="n"/>
       <c r="G178" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду6Ру100</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
       <c r="H178" s="14" t="inlineStr">
         <is>
-          <t>521-01.467-02</t>
+          <t>521. 3м.666</t>
         </is>
       </c>
       <c r="I178" s="14" t="inlineStr">
@@ -13191,19 +13459,19 @@
       </c>
       <c r="J178" s="14" t="inlineStr"/>
       <c r="K178" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L178" s="20" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="M178" s="16" t="n">
         <v>5</v>
       </c>
       <c r="N178" s="21" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="O178" s="14" t="n">
-        <v>2000</v>
+        <v>6500</v>
       </c>
       <c r="P178" s="14" t="inlineStr"/>
       <c r="Q178" s="15" t="inlineStr">
@@ -13213,7 +13481,7 @@
       </c>
       <c r="R178" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -13233,7 +13501,7 @@
       </c>
       <c r="D179" s="14" t="inlineStr">
         <is>
-          <t>кран</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E179" s="14" t="n">
@@ -13242,10 +13510,14 @@
       <c r="F179" s="14" t="n"/>
       <c r="G179" s="15" t="inlineStr">
         <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
-        </is>
-      </c>
-      <c r="H179" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+        </is>
+      </c>
+      <c r="H179" s="14" t="inlineStr">
+        <is>
+          <t>522-01.498</t>
+        </is>
+      </c>
       <c r="I179" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -13253,19 +13525,19 @@
       </c>
       <c r="J179" s="14" t="inlineStr"/>
       <c r="K179" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L179" s="20" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="M179" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N179" s="21" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="O179" s="14" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="P179" s="14" t="inlineStr"/>
       <c r="Q179" s="15" t="inlineStr">
@@ -13275,7 +13547,7 @@
       </c>
       <c r="R179" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -13299,17 +13571,17 @@
         </is>
       </c>
       <c r="E180" s="14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F180" s="14" t="n"/>
       <c r="G180" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный угловой Ду15Ру40</t>
         </is>
       </c>
       <c r="H180" s="14" t="inlineStr">
         <is>
-          <t>521 3м 726</t>
+          <t>521-01.465-02</t>
         </is>
       </c>
       <c r="I180" s="14" t="inlineStr">
@@ -13322,13 +13594,13 @@
         <v>2</v>
       </c>
       <c r="L180" s="20" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="M180" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N180" s="21" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="O180" s="14" t="n">
         <v>6000</v>
@@ -13365,17 +13637,17 @@
         </is>
       </c>
       <c r="E181" s="14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F181" s="14" t="n"/>
       <c r="G181" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="H181" s="14" t="inlineStr">
         <is>
-          <t>521-01.052</t>
+          <t>521-35.3362</t>
         </is>
       </c>
       <c r="I181" s="14" t="inlineStr">
@@ -13388,13 +13660,13 @@
         <v>2</v>
       </c>
       <c r="L181" s="20" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="M181" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N181" s="21" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="O181" s="14" t="n">
         <v>6000</v>
@@ -13431,17 +13703,17 @@
         </is>
       </c>
       <c r="E182" s="14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F182" s="14" t="n"/>
       <c r="G182" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="H182" s="14" t="inlineStr">
         <is>
-          <t>521-01.470-02</t>
+          <t>521-03.420</t>
         </is>
       </c>
       <c r="I182" s="14" t="inlineStr">
@@ -13454,13 +13726,13 @@
         <v>2</v>
       </c>
       <c r="L182" s="20" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M182" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N182" s="21" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="O182" s="14" t="n">
         <v>6000</v>
@@ -13473,7 +13745,7 @@
       </c>
       <c r="R182" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -13497,17 +13769,17 @@
         </is>
       </c>
       <c r="E183" s="14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F183" s="14" t="n"/>
       <c r="G183" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="H183" s="14" t="inlineStr">
         <is>
-          <t>521-01.468-05</t>
+          <t>521-01.469-02</t>
         </is>
       </c>
       <c r="I183" s="14" t="inlineStr">
@@ -13520,16 +13792,16 @@
         <v>2</v>
       </c>
       <c r="L183" s="20" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M183" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N183" s="21" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="O183" s="14" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="P183" s="14" t="inlineStr"/>
       <c r="Q183" s="15" t="inlineStr">
@@ -13539,7 +13811,7 @@
       </c>
       <c r="R183" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -13559,23 +13831,19 @@
       </c>
       <c r="D184" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>кран</t>
         </is>
       </c>
       <c r="E184" s="14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F184" s="14" t="n"/>
       <c r="G184" s="15" t="inlineStr">
         <is>
-          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
-        </is>
-      </c>
-      <c r="H184" s="14" t="inlineStr">
-        <is>
-          <t>522-03.123</t>
-        </is>
-      </c>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
+        </is>
+      </c>
+      <c r="H184" s="19" t="inlineStr"/>
       <c r="I184" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -13583,19 +13851,19 @@
       </c>
       <c r="J184" s="14" t="inlineStr"/>
       <c r="K184" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L184" s="20" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="M184" s="16" t="n">
         <v>4</v>
       </c>
       <c r="N184" s="21" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="O184" s="14" t="n">
-        <v>4800</v>
+        <v>7500</v>
       </c>
       <c r="P184" s="14" t="inlineStr"/>
       <c r="Q184" s="15" t="inlineStr">
@@ -13634,12 +13902,12 @@
       <c r="F185" s="14" t="n"/>
       <c r="G185" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="H185" s="14" t="inlineStr">
         <is>
-          <t>522-35.3632</t>
+          <t>521 3м 726</t>
         </is>
       </c>
       <c r="I185" s="14" t="inlineStr">
@@ -13661,7 +13929,7 @@
         <v>0.004</v>
       </c>
       <c r="O185" s="14" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="P185" s="14" t="inlineStr"/>
       <c r="Q185" s="15" t="inlineStr">
@@ -13695,17 +13963,17 @@
         </is>
       </c>
       <c r="E186" s="14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F186" s="14" t="n"/>
       <c r="G186" s="15" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="H186" s="14" t="inlineStr">
         <is>
-          <t>М528-03.001</t>
+          <t>521-01.052</t>
         </is>
       </c>
       <c r="I186" s="14" t="inlineStr">
@@ -13715,19 +13983,19 @@
       </c>
       <c r="J186" s="14" t="inlineStr"/>
       <c r="K186" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L186" s="20" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="M186" s="16" t="n">
         <v>4</v>
       </c>
       <c r="N186" s="21" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="O186" s="14" t="n">
-        <v>12500</v>
+        <v>6000</v>
       </c>
       <c r="P186" s="14" t="inlineStr"/>
       <c r="Q186" s="15" t="inlineStr">
@@ -13737,7 +14005,7 @@
       </c>
       <c r="R186" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -13761,17 +14029,17 @@
         </is>
       </c>
       <c r="E187" s="14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F187" s="14" t="n"/>
       <c r="G187" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="H187" s="14" t="inlineStr">
         <is>
-          <t>521--01.468-08</t>
+          <t>521-01.470-02</t>
         </is>
       </c>
       <c r="I187" s="14" t="inlineStr">
@@ -13781,19 +14049,19 @@
       </c>
       <c r="J187" s="14" t="inlineStr"/>
       <c r="K187" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L187" s="20" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="M187" s="16" t="n">
         <v>4</v>
       </c>
       <c r="N187" s="21" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="O187" s="14" t="n">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="P187" s="14" t="inlineStr"/>
       <c r="Q187" s="15" t="inlineStr">
@@ -13803,7 +14071,7 @@
       </c>
       <c r="R187" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -13827,17 +14095,17 @@
         </is>
       </c>
       <c r="E188" s="14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F188" s="14" t="n"/>
       <c r="G188" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="H188" s="14" t="inlineStr">
         <is>
-          <t>521--35.3363</t>
+          <t>521-01.468-05</t>
         </is>
       </c>
       <c r="I188" s="14" t="inlineStr">
@@ -13847,19 +14115,19 @@
       </c>
       <c r="J188" s="14" t="inlineStr"/>
       <c r="K188" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L188" s="20" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="M188" s="16" t="n">
         <v>4</v>
       </c>
       <c r="N188" s="21" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="O188" s="14" t="n">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="P188" s="14" t="inlineStr"/>
       <c r="Q188" s="15" t="inlineStr">
@@ -13869,7 +14137,7 @@
       </c>
       <c r="R188" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -13893,17 +14161,17 @@
         </is>
       </c>
       <c r="E189" s="14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F189" s="14" t="n"/>
       <c r="G189" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
         </is>
       </c>
       <c r="H189" s="14" t="inlineStr">
         <is>
-          <t>521-01.464-06</t>
+          <t>522-03.123</t>
         </is>
       </c>
       <c r="I189" s="14" t="inlineStr">
@@ -13913,19 +14181,19 @@
       </c>
       <c r="J189" s="14" t="inlineStr"/>
       <c r="K189" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L189" s="20" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="M189" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N189" s="21" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="O189" s="14" t="n">
-        <v>9600</v>
+        <v>4800</v>
       </c>
       <c r="P189" s="14" t="inlineStr"/>
       <c r="Q189" s="15" t="inlineStr">
@@ -13959,17 +14227,17 @@
         </is>
       </c>
       <c r="E190" s="14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F190" s="14" t="n"/>
       <c r="G190" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
       <c r="H190" s="14" t="inlineStr">
         <is>
-          <t>522-01.500-07</t>
+          <t>522-35.3632</t>
         </is>
       </c>
       <c r="I190" s="14" t="inlineStr">
@@ -13979,19 +14247,19 @@
       </c>
       <c r="J190" s="14" t="inlineStr"/>
       <c r="K190" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L190" s="20" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="M190" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N190" s="21" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="O190" s="14" t="n">
-        <v>9600</v>
+        <v>4500</v>
       </c>
       <c r="P190" s="14" t="inlineStr"/>
       <c r="Q190" s="15" t="inlineStr">
@@ -14001,7 +14269,7 @@
       </c>
       <c r="R190" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -14025,17 +14293,17 @@
         </is>
       </c>
       <c r="E191" s="14" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F191" s="14" t="n"/>
       <c r="G191" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
       <c r="H191" s="14" t="inlineStr">
         <is>
-          <t>521-01.465-01</t>
+          <t>521-01.464-06</t>
         </is>
       </c>
       <c r="I191" s="14" t="inlineStr">
@@ -14048,16 +14316,16 @@
         <v>1</v>
       </c>
       <c r="L191" s="20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="M191" s="16" t="n">
         <v>3</v>
       </c>
       <c r="N191" s="21" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="O191" s="14" t="n">
-        <v>20200</v>
+        <v>9600</v>
       </c>
       <c r="P191" s="14" t="inlineStr"/>
       <c r="Q191" s="15" t="inlineStr">
@@ -14091,17 +14359,17 @@
         </is>
       </c>
       <c r="E192" s="14" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F192" s="14" t="n"/>
       <c r="G192" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
       <c r="H192" s="14" t="inlineStr">
         <is>
-          <t>521-35.3238</t>
+          <t>522-01.500-07</t>
         </is>
       </c>
       <c r="I192" s="14" t="inlineStr">
@@ -14114,16 +14382,16 @@
         <v>1</v>
       </c>
       <c r="L192" s="20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="M192" s="16" t="n">
         <v>3</v>
       </c>
       <c r="N192" s="21" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="O192" s="14" t="n">
-        <v>6000</v>
+        <v>9600</v>
       </c>
       <c r="P192" s="14" t="inlineStr"/>
       <c r="Q192" s="15" t="inlineStr">
@@ -14157,17 +14425,17 @@
         </is>
       </c>
       <c r="E193" s="14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F193" s="14" t="n"/>
       <c r="G193" s="15" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
         </is>
       </c>
       <c r="H193" s="14" t="inlineStr">
         <is>
-          <t>525-35.2634</t>
+          <t>522-01.501-01</t>
         </is>
       </c>
       <c r="I193" s="14" t="inlineStr">
@@ -14180,16 +14448,16 @@
         <v>1</v>
       </c>
       <c r="L193" s="20" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M193" s="16" t="n">
         <v>3</v>
       </c>
       <c r="N193" s="21" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="O193" s="14" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="P193" s="14" t="inlineStr"/>
       <c r="Q193" s="15" t="inlineStr">
@@ -14199,7 +14467,7 @@
       </c>
       <c r="R193" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -14223,17 +14491,17 @@
         </is>
       </c>
       <c r="E194" s="14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F194" s="14" t="n"/>
       <c r="G194" s="15" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
         </is>
       </c>
       <c r="H194" s="14" t="inlineStr">
         <is>
-          <t>525-35.2634-04</t>
+          <t>521-01.471-02</t>
         </is>
       </c>
       <c r="I194" s="14" t="inlineStr">
@@ -14246,16 +14514,16 @@
         <v>1</v>
       </c>
       <c r="L194" s="20" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M194" s="16" t="n">
         <v>3</v>
       </c>
       <c r="N194" s="21" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="O194" s="14" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="P194" s="14" t="inlineStr"/>
       <c r="Q194" s="15" t="inlineStr">
@@ -14265,7 +14533,7 @@
       </c>
       <c r="R194" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -14289,17 +14557,17 @@
         </is>
       </c>
       <c r="E195" s="14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F195" s="14" t="n"/>
       <c r="G195" s="15" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
       <c r="H195" s="14" t="inlineStr">
         <is>
-          <t>524-03.174</t>
+          <t>521-01.470.02</t>
         </is>
       </c>
       <c r="I195" s="14" t="inlineStr">
@@ -14312,16 +14580,16 @@
         <v>1</v>
       </c>
       <c r="L195" s="20" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M195" s="16" t="n">
         <v>3</v>
       </c>
       <c r="N195" s="21" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="O195" s="14" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="P195" s="14" t="inlineStr"/>
       <c r="Q195" s="15" t="inlineStr">
@@ -14331,7 +14599,7 @@
       </c>
       <c r="R195" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -14355,17 +14623,17 @@
         </is>
       </c>
       <c r="E196" s="14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F196" s="14" t="n"/>
       <c r="G196" s="15" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
+          <t>Клапан штуцерный проходной Ду 15</t>
         </is>
       </c>
       <c r="H196" s="14" t="inlineStr">
         <is>
-          <t>524-03.173</t>
+          <t>521 3м.770</t>
         </is>
       </c>
       <c r="I196" s="14" t="inlineStr">
@@ -14378,16 +14646,16 @@
         <v>1</v>
       </c>
       <c r="L196" s="20" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M196" s="16" t="n">
         <v>3</v>
       </c>
       <c r="N196" s="21" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="O196" s="14" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="P196" s="14" t="inlineStr"/>
       <c r="Q196" s="15" t="inlineStr">
@@ -14397,7 +14665,7 @@
       </c>
       <c r="R196" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -14421,17 +14689,17 @@
         </is>
       </c>
       <c r="E197" s="14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F197" s="14" t="n"/>
       <c r="G197" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+          <t>Клапан штуцерный проходной Ду 15</t>
         </is>
       </c>
       <c r="H197" s="14" t="inlineStr">
         <is>
-          <t>522-01-493-01</t>
+          <t>без чертежа</t>
         </is>
       </c>
       <c r="I197" s="14" t="inlineStr">
@@ -14444,16 +14712,16 @@
         <v>1</v>
       </c>
       <c r="L197" s="20" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M197" s="16" t="n">
         <v>3</v>
       </c>
       <c r="N197" s="21" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="O197" s="14" t="n">
-        <v>4000</v>
+        <v>6500</v>
       </c>
       <c r="P197" s="14" t="inlineStr"/>
       <c r="Q197" s="15" t="inlineStr">
@@ -14463,7 +14731,7 @@
       </c>
       <c r="R197" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -14492,12 +14760,12 @@
       <c r="F198" s="14" t="n"/>
       <c r="G198" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
         </is>
       </c>
       <c r="H198" s="14" t="inlineStr">
         <is>
-          <t>522-01.501-01</t>
+          <t>521-01.470</t>
         </is>
       </c>
       <c r="I198" s="14" t="inlineStr">
@@ -14558,12 +14826,12 @@
       <c r="F199" s="14" t="n"/>
       <c r="G199" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="H199" s="14" t="inlineStr">
         <is>
-          <t>521-01.471-02</t>
+          <t>521-01.464-02</t>
         </is>
       </c>
       <c r="I199" s="14" t="inlineStr">
@@ -14585,7 +14853,7 @@
         <v>0.002</v>
       </c>
       <c r="O199" s="14" t="n">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="P199" s="14" t="inlineStr"/>
       <c r="Q199" s="15" t="inlineStr">
@@ -14624,12 +14892,12 @@
       <c r="F200" s="14" t="n"/>
       <c r="G200" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr">
         <is>
-          <t>521-01.470.02</t>
+          <t>522-01.500-05</t>
         </is>
       </c>
       <c r="I200" s="14" t="inlineStr">
@@ -14651,7 +14919,7 @@
         <v>0.002</v>
       </c>
       <c r="O200" s="14" t="n">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="P200" s="14" t="inlineStr"/>
       <c r="Q200" s="15" t="inlineStr">
@@ -14685,17 +14953,17 @@
         </is>
       </c>
       <c r="E201" s="14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F201" s="14" t="n"/>
       <c r="G201" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="H201" s="14" t="inlineStr">
         <is>
-          <t>521 3м.770</t>
+          <t>521-01.465-01</t>
         </is>
       </c>
       <c r="I201" s="14" t="inlineStr">
@@ -14708,16 +14976,16 @@
         <v>1</v>
       </c>
       <c r="L201" s="20" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M201" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N201" s="21" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="O201" s="14" t="n">
-        <v>6500</v>
+        <v>20200</v>
       </c>
       <c r="P201" s="14" t="inlineStr"/>
       <c r="Q201" s="15" t="inlineStr">
@@ -14727,7 +14995,7 @@
       </c>
       <c r="R201" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -14751,17 +15019,17 @@
         </is>
       </c>
       <c r="E202" s="14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F202" s="14" t="n"/>
       <c r="G202" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="H202" s="14" t="inlineStr">
         <is>
-          <t>без чертежа</t>
+          <t>521-35.3238</t>
         </is>
       </c>
       <c r="I202" s="14" t="inlineStr">
@@ -14774,16 +15042,16 @@
         <v>1</v>
       </c>
       <c r="L202" s="20" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M202" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N202" s="21" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="O202" s="14" t="n">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="P202" s="14" t="inlineStr"/>
       <c r="Q202" s="15" t="inlineStr">
@@ -14793,7 +15061,7 @@
       </c>
       <c r="R202" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -14817,17 +15085,17 @@
         </is>
       </c>
       <c r="E203" s="14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F203" s="14" t="n"/>
       <c r="G203" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
       <c r="H203" s="14" t="inlineStr">
         <is>
-          <t>521-01.470</t>
+          <t>522-01-493-01</t>
         </is>
       </c>
       <c r="I203" s="14" t="inlineStr">
@@ -14840,16 +15108,16 @@
         <v>1</v>
       </c>
       <c r="L203" s="20" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M203" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N203" s="21" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="O203" s="14" t="n">
-        <v>6500</v>
+        <v>4000</v>
       </c>
       <c r="P203" s="14" t="inlineStr"/>
       <c r="Q203" s="15" t="inlineStr">
@@ -14859,7 +15127,7 @@
       </c>
       <c r="R203" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -14883,17 +15151,17 @@
         </is>
       </c>
       <c r="E204" s="14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F204" s="14" t="n"/>
       <c r="G204" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Клапан штуцерный угловой Ду6Ру100</t>
         </is>
       </c>
       <c r="H204" s="14" t="inlineStr">
         <is>
-          <t>521-01.464-02</t>
+          <t>521-01.467-02</t>
         </is>
       </c>
       <c r="I204" s="14" t="inlineStr">
@@ -14903,19 +15171,19 @@
       </c>
       <c r="J204" s="14" t="inlineStr"/>
       <c r="K204" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L204" s="20" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="M204" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N204" s="21" t="n">
         <v>0.002</v>
       </c>
       <c r="O204" s="14" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="P204" s="14" t="inlineStr"/>
       <c r="Q204" s="15" t="inlineStr">
@@ -14925,7 +15193,7 @@
       </c>
       <c r="R204" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -14949,17 +15217,17 @@
         </is>
       </c>
       <c r="E205" s="14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F205" s="14" t="n"/>
       <c r="G205" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr">
         <is>
-          <t>522-01.500-05</t>
+          <t>521-03.479</t>
         </is>
       </c>
       <c r="I205" s="14" t="inlineStr">
@@ -14972,16 +15240,16 @@
         <v>1</v>
       </c>
       <c r="L205" s="20" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="M205" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N205" s="21" t="n">
         <v>0.002</v>
       </c>
       <c r="O205" s="14" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="P205" s="14" t="inlineStr"/>
       <c r="Q205" s="15" t="inlineStr">
@@ -14991,7 +15259,7 @@
       </c>
       <c r="R205" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15020,12 +15288,12 @@
       <c r="F206" s="14" t="n"/>
       <c r="G206" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
         </is>
       </c>
       <c r="H206" s="14" t="inlineStr">
         <is>
-          <t>521-03.479</t>
+          <t>522-03.089</t>
         </is>
       </c>
       <c r="I206" s="14" t="inlineStr">
@@ -15047,7 +15315,7 @@
         <v>0.002</v>
       </c>
       <c r="O206" s="14" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="P206" s="14" t="inlineStr"/>
       <c r="Q206" s="15" t="inlineStr">
@@ -15086,12 +15354,12 @@
       <c r="F207" s="14" t="n"/>
       <c r="G207" s="15" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr">
         <is>
-          <t>522-03.089</t>
+          <t>536 3м .333</t>
         </is>
       </c>
       <c r="I207" s="14" t="inlineStr">
@@ -15123,7 +15391,7 @@
       </c>
       <c r="R207" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -15152,12 +15420,12 @@
       <c r="F208" s="14" t="n"/>
       <c r="G208" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="H208" s="14" t="inlineStr">
         <is>
-          <t>536 3м .333</t>
+          <t>521 3м 30</t>
         </is>
       </c>
       <c r="I208" s="14" t="inlineStr">
@@ -15218,12 +15486,12 @@
       <c r="F209" s="14" t="n"/>
       <c r="G209" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
         </is>
       </c>
       <c r="H209" s="14" t="inlineStr">
         <is>
-          <t>521 3м 30</t>
+          <t>522-35 240</t>
         </is>
       </c>
       <c r="I209" s="14" t="inlineStr">
@@ -15284,12 +15552,12 @@
       <c r="F210" s="14" t="n"/>
       <c r="G210" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="H210" s="14" t="inlineStr">
         <is>
-          <t>522-35 240</t>
+          <t>521-01.052</t>
         </is>
       </c>
       <c r="I210" s="14" t="inlineStr">
@@ -15355,7 +15623,7 @@
       </c>
       <c r="H211" s="14" t="inlineStr">
         <is>
-          <t>521-01.052</t>
+          <t>521-01.471-03</t>
         </is>
       </c>
       <c r="I211" s="14" t="inlineStr">
@@ -15421,7 +15689,7 @@
       </c>
       <c r="H212" s="14" t="inlineStr">
         <is>
-          <t>521-01.471-03</t>
+          <t>522-01.498.-03</t>
         </is>
       </c>
       <c r="I212" s="14" t="inlineStr">
@@ -15487,7 +15755,7 @@
       </c>
       <c r="H213" s="14" t="inlineStr">
         <is>
-          <t>522-01.498.-03</t>
+          <t>425-322710</t>
         </is>
       </c>
       <c r="I213" s="14" t="inlineStr">
@@ -15548,12 +15816,12 @@
       <c r="F214" s="14" t="n"/>
       <c r="G214" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
       <c r="H214" s="14" t="inlineStr">
         <is>
-          <t>425-322710</t>
+          <t>521-01.465-03</t>
         </is>
       </c>
       <c r="I214" s="14" t="inlineStr">
@@ -15575,7 +15843,7 @@
         <v>0.002</v>
       </c>
       <c r="O214" s="14" t="n">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="P214" s="14" t="inlineStr"/>
       <c r="Q214" s="15" t="inlineStr">
@@ -15614,12 +15882,12 @@
       <c r="F215" s="14" t="n"/>
       <c r="G215" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
         </is>
       </c>
       <c r="H215" s="14" t="inlineStr">
         <is>
-          <t>521-01.465-03</t>
+          <t>522-3м-9</t>
         </is>
       </c>
       <c r="I215" s="14" t="inlineStr">
@@ -15641,7 +15909,7 @@
         <v>0.002</v>
       </c>
       <c r="O215" s="14" t="n">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="P215" s="14" t="inlineStr"/>
       <c r="Q215" s="15" t="inlineStr">
@@ -15651,7 +15919,7 @@
       </c>
       <c r="R215" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15675,17 +15943,17 @@
         </is>
       </c>
       <c r="E216" s="14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F216" s="14" t="n"/>
       <c r="G216" s="15" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="H216" s="14" t="inlineStr">
         <is>
-          <t>522-3м-9</t>
+          <t>521--01.468-08</t>
         </is>
       </c>
       <c r="I216" s="14" t="inlineStr">
@@ -15698,16 +15966,16 @@
         <v>1</v>
       </c>
       <c r="L216" s="20" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M216" s="16" t="n">
         <v>2</v>
       </c>
       <c r="N216" s="21" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="O216" s="14" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="P216" s="14" t="inlineStr"/>
       <c r="Q216" s="15" t="inlineStr">
@@ -15741,22 +16009,22 @@
         </is>
       </c>
       <c r="E217" s="14" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F217" s="14" t="n"/>
       <c r="G217" s="15" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="H217" s="14" t="inlineStr">
         <is>
-          <t>521-02.013</t>
+          <t>521--35.3363</t>
         </is>
       </c>
       <c r="I217" s="14" t="inlineStr">
         <is>
-          <t>б/у</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="J217" s="14" t="inlineStr"/>
@@ -15764,16 +16032,16 @@
         <v>1</v>
       </c>
       <c r="L217" s="20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M217" s="16" t="n">
         <v>2</v>
       </c>
       <c r="N217" s="21" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="O217" s="14" t="n">
-        <v>4500</v>
+        <v>7500</v>
       </c>
       <c r="P217" s="14" t="inlineStr"/>
       <c r="Q217" s="15" t="inlineStr">
@@ -15817,7 +16085,7 @@
       </c>
       <c r="H218" s="14" t="inlineStr">
         <is>
-          <t>521-02.014</t>
+          <t>521-02.013</t>
         </is>
       </c>
       <c r="I218" s="14" t="inlineStr">
@@ -15830,10 +16098,10 @@
         <v>1</v>
       </c>
       <c r="L218" s="20" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="M218" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N218" s="21" t="n">
         <v>0.001</v>
@@ -15857,31 +16125,35 @@
       <c r="A219" s="14" t="n">
         <v>215</v>
       </c>
-      <c r="B219" s="18" t="inlineStr">
-        <is>
-          <t>А. Согласованный список</t>
+      <c r="B219" s="22" t="inlineStr">
+        <is>
+          <t>Б. Добор со склада</t>
         </is>
       </c>
       <c r="C219" s="14" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D219" s="14" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E219" s="14" t="n">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="F219" s="14" t="n"/>
       <c r="G219" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду200</t>
-        </is>
-      </c>
-      <c r="H219" s="19" t="inlineStr"/>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
+        </is>
+      </c>
+      <c r="H219" s="14" t="inlineStr">
+        <is>
+          <t>521-02.014</t>
+        </is>
+      </c>
       <c r="I219" s="14" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -15889,35 +16161,29 @@
       </c>
       <c r="J219" s="14" t="inlineStr"/>
       <c r="K219" s="14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L219" s="20" t="n">
-        <v>148</v>
+        <v>0.7</v>
       </c>
       <c r="M219" s="16" t="n">
-        <v>1184</v>
+        <v>1</v>
       </c>
       <c r="N219" s="21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O219" s="14" t="inlineStr">
-        <is>
-          <t>150-170</t>
-        </is>
-      </c>
-      <c r="P219" s="14" t="inlineStr">
-        <is>
-          <t>280-320</t>
-        </is>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="O219" s="14" t="n">
+        <v>4500</v>
+      </c>
+      <c r="P219" s="14" t="inlineStr"/>
       <c r="Q219" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R219" s="14" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15941,12 +16207,12 @@
         </is>
       </c>
       <c r="E220" s="14" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F220" s="14" t="n"/>
       <c r="G220" s="15" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 150</t>
+          <t>Фильтр забортной воды Ду200</t>
         </is>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
@@ -15957,25 +16223,25 @@
       </c>
       <c r="J220" s="14" t="inlineStr"/>
       <c r="K220" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L220" s="20" t="n">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="M220" s="16" t="n">
-        <v>320</v>
+        <v>1184</v>
       </c>
       <c r="N220" s="21" t="n">
-        <v>0.5</v>
+        <v>1.28</v>
       </c>
       <c r="O220" s="14" t="inlineStr">
         <is>
-          <t>75-90</t>
+          <t>150-170</t>
         </is>
       </c>
       <c r="P220" s="14" t="inlineStr">
         <is>
-          <t>170-190</t>
+          <t>280-320</t>
         </is>
       </c>
       <c r="Q220" s="15" t="inlineStr">
@@ -16009,12 +16275,12 @@
         </is>
       </c>
       <c r="E221" s="14" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F221" s="14" t="n"/>
       <c r="G221" s="15" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 80</t>
+          <t>Фильтр заборной воды ДУ 150</t>
         </is>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
@@ -16028,16 +16294,24 @@
         <v>5</v>
       </c>
       <c r="L221" s="20" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="M221" s="16" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="N221" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O221" s="14" t="inlineStr"/>
-      <c r="P221" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="O221" s="14" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="P221" s="14" t="inlineStr">
+        <is>
+          <t>170-190</t>
+        </is>
+      </c>
       <c r="Q221" s="15" t="inlineStr">
         <is>
           <t>Обрешетка, ставится верхним ярусом на ящики</t>
@@ -16069,12 +16343,12 @@
         </is>
       </c>
       <c r="E222" s="14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F222" s="14" t="n"/>
       <c r="G222" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 100</t>
+          <t>Фильтр заборной воды ДУ 80</t>
         </is>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
@@ -16085,27 +16359,19 @@
       </c>
       <c r="J222" s="14" t="inlineStr"/>
       <c r="K222" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L222" s="20" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="M222" s="16" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="N222" s="21" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="O222" s="14" t="inlineStr">
-        <is>
-          <t>55-650</t>
-        </is>
-      </c>
-      <c r="P222" s="14" t="inlineStr">
-        <is>
-          <t>150-160</t>
-        </is>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="O222" s="14" t="inlineStr"/>
+      <c r="P222" s="14" t="inlineStr"/>
       <c r="Q222" s="15" t="inlineStr">
         <is>
           <t>Обрешетка, ставится верхним ярусом на ящики</t>
@@ -16133,60 +16399,50 @@
       </c>
       <c r="D223" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>фильтр забортной воды</t>
         </is>
       </c>
       <c r="E223" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="F223" s="14" t="n">
-        <v>10</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F223" s="14" t="n"/>
       <c r="G223" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
-        </is>
-      </c>
-      <c r="H223" s="14" t="inlineStr">
-        <is>
-          <t>521-182.110</t>
-        </is>
-      </c>
+          <t>Фильтр забортной воды Ду 100</t>
+        </is>
+      </c>
+      <c r="H223" s="19" t="inlineStr"/>
       <c r="I223" s="14" t="inlineStr">
         <is>
-          <t>новый</t>
-        </is>
-      </c>
-      <c r="J223" s="23" t="inlineStr">
-        <is>
-          <t>титан</t>
-        </is>
-      </c>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="J223" s="14" t="inlineStr"/>
       <c r="K223" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L223" s="20" t="n">
-        <v>3.5</v>
+        <v>42</v>
       </c>
       <c r="M223" s="16" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="N223" s="21" t="n">
-        <v>0.06</v>
+        <v>0.045</v>
       </c>
       <c r="O223" s="14" t="inlineStr">
         <is>
-          <t>25-35000</t>
+          <t>55-650</t>
         </is>
       </c>
       <c r="P223" s="14" t="inlineStr">
         <is>
-          <t>80-100000</t>
+          <t>150-160</t>
         </is>
       </c>
       <c r="Q223" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="R223" s="14" t="inlineStr">
@@ -16215,19 +16471,19 @@
         </is>
       </c>
       <c r="E224" s="14" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F224" s="14" t="n">
         <v>10</v>
       </c>
       <c r="G224" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
+          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
         </is>
       </c>
       <c r="H224" s="14" t="inlineStr">
         <is>
-          <t>521-182.116</t>
+          <t>521-182.110</t>
         </is>
       </c>
       <c r="I224" s="14" t="inlineStr">
@@ -16241,30 +16497,30 @@
         </is>
       </c>
       <c r="K224" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L224" s="20" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="M224" s="16" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N224" s="21" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
       <c r="O224" s="14" t="inlineStr">
         <is>
-          <t>40-55000</t>
+          <t>25-35000</t>
         </is>
       </c>
       <c r="P224" s="14" t="inlineStr">
         <is>
-          <t>120-140000</t>
+          <t>80-100000</t>
         </is>
       </c>
       <c r="Q224" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R224" s="14" t="inlineStr">
@@ -16277,9 +16533,9 @@
       <c r="A225" s="14" t="n">
         <v>221</v>
       </c>
-      <c r="B225" s="22" t="inlineStr">
-        <is>
-          <t>Б. Добор со склада</t>
+      <c r="B225" s="18" t="inlineStr">
+        <is>
+          <t>А. Согласованный список</t>
         </is>
       </c>
       <c r="C225" s="14" t="inlineStr">
@@ -16289,49 +16545,65 @@
       </c>
       <c r="D225" s="14" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E225" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="F225" s="14" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="F225" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="G225" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 300</t>
-        </is>
-      </c>
-      <c r="H225" s="19" t="inlineStr"/>
+          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
+        </is>
+      </c>
+      <c r="H225" s="14" t="inlineStr">
+        <is>
+          <t>521-182.116</t>
+        </is>
+      </c>
       <c r="I225" s="14" t="inlineStr">
         <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="J225" s="14" t="inlineStr"/>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="J225" s="23" t="inlineStr">
+        <is>
+          <t>титан</t>
+        </is>
+      </c>
       <c r="K225" s="14" t="n">
         <v>1</v>
       </c>
       <c r="L225" s="20" t="n">
-        <v>172</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M225" s="16" t="n">
-        <v>172</v>
+        <v>10</v>
       </c>
       <c r="N225" s="21" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O225" s="14" t="n">
-        <v>400000</v>
-      </c>
-      <c r="P225" s="14" t="inlineStr"/>
+        <v>0.045</v>
+      </c>
+      <c r="O225" s="14" t="inlineStr">
+        <is>
+          <t>40-55000</t>
+        </is>
+      </c>
+      <c r="P225" s="14" t="inlineStr">
+        <is>
+          <t>120-140000</t>
+        </is>
+      </c>
       <c r="Q225" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="R225" s="14" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16355,19 +16627,15 @@
         </is>
       </c>
       <c r="E226" s="14" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F226" s="14" t="n"/>
       <c r="G226" s="15" t="inlineStr">
         <is>
-          <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
-        </is>
-      </c>
-      <c r="H226" s="14" t="inlineStr">
-        <is>
-          <t>427-03-109-2</t>
-        </is>
-      </c>
+          <t>Фильтр забортной воды Ду 300</t>
+        </is>
+      </c>
+      <c r="H226" s="19" t="inlineStr"/>
       <c r="I226" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -16375,19 +16643,19 @@
       </c>
       <c r="J226" s="14" t="inlineStr"/>
       <c r="K226" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L226" s="20" t="n">
-        <v>43.5</v>
+        <v>172</v>
       </c>
       <c r="M226" s="16" t="n">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="N226" s="21" t="n">
-        <v>0.135</v>
+        <v>0.35</v>
       </c>
       <c r="O226" s="14" t="n">
-        <v>120000</v>
+        <v>400000</v>
       </c>
       <c r="P226" s="14" t="inlineStr"/>
       <c r="Q226" s="15" t="inlineStr">
@@ -16397,7 +16665,7 @@
       </c>
       <c r="R226" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -16417,50 +16685,48 @@
       </c>
       <c r="D227" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>фильтр забортной воды</t>
         </is>
       </c>
       <c r="E227" s="14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F227" s="14" t="n"/>
       <c r="G227" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
+          <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
         </is>
       </c>
       <c r="H227" s="14" t="inlineStr">
         <is>
-          <t>521-182.110</t>
+          <t>427-03-109-2</t>
         </is>
       </c>
       <c r="I227" s="14" t="inlineStr">
         <is>
-          <t>новый</t>
-        </is>
-      </c>
-      <c r="J227" s="23" t="inlineStr">
-        <is>
-          <t>титан</t>
-        </is>
-      </c>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="J227" s="14" t="inlineStr"/>
       <c r="K227" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L227" s="20" t="n">
-        <v>9.199999999999999</v>
+        <v>43.5</v>
       </c>
       <c r="M227" s="16" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="N227" s="21" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O227" s="14" t="inlineStr"/>
+        <v>0.135</v>
+      </c>
+      <c r="O227" s="14" t="n">
+        <v>120000</v>
+      </c>
       <c r="P227" s="14" t="inlineStr"/>
       <c r="Q227" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="R227" s="14" t="inlineStr">
@@ -16485,7 +16751,7 @@
       </c>
       <c r="D228" s="14" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E228" s="14" t="n">
@@ -16494,40 +16760,46 @@
       <c r="F228" s="14" t="n"/>
       <c r="G228" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 50</t>
-        </is>
-      </c>
-      <c r="H228" s="19" t="inlineStr"/>
+          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
+        </is>
+      </c>
+      <c r="H228" s="14" t="inlineStr">
+        <is>
+          <t>521-182.110</t>
+        </is>
+      </c>
       <c r="I228" s="14" t="inlineStr">
         <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="J228" s="14" t="inlineStr"/>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="J228" s="23" t="inlineStr">
+        <is>
+          <t>титан</t>
+        </is>
+      </c>
       <c r="K228" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L228" s="20" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M228" s="16" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="N228" s="21" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="O228" s="14" t="n">
-        <v>60000</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="O228" s="14" t="inlineStr"/>
       <c r="P228" s="14" t="inlineStr"/>
       <c r="Q228" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R228" s="14" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -16551,12 +16823,12 @@
         </is>
       </c>
       <c r="E229" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F229" s="14" t="n"/>
       <c r="G229" s="15" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду20 маленькая</t>
+          <t>Фильтр забортной воды Ду 50</t>
         </is>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
@@ -16570,16 +16842,16 @@
         <v>1</v>
       </c>
       <c r="L229" s="20" t="n">
-        <v>1</v>
+        <v>7.8</v>
       </c>
       <c r="M229" s="16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N229" s="21" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="O229" s="14" t="n">
-        <v>3000</v>
+        <v>60000</v>
       </c>
       <c r="P229" s="14" t="inlineStr"/>
       <c r="Q229" s="15" t="inlineStr">
@@ -16589,31 +16861,93 @@
       </c>
       <c r="R229" s="14" t="inlineStr">
         <is>
+          <t>Фойе</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="14" t="n">
+        <v>226</v>
+      </c>
+      <c r="B230" s="22" t="inlineStr">
+        <is>
+          <t>Б. Добор со склада</t>
+        </is>
+      </c>
+      <c r="C230" s="14" t="inlineStr">
+        <is>
+          <t>Ярус 4, верх</t>
+        </is>
+      </c>
+      <c r="D230" s="14" t="inlineStr">
+        <is>
+          <t>фильтр забортной воды</t>
+        </is>
+      </c>
+      <c r="E230" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F230" s="14" t="n"/>
+      <c r="G230" s="15" t="inlineStr">
+        <is>
+          <t>Сетка на фильтр Ду20 маленькая</t>
+        </is>
+      </c>
+      <c r="H230" s="19" t="inlineStr"/>
+      <c r="I230" s="14" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="J230" s="14" t="inlineStr"/>
+      <c r="K230" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N230" s="21" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O230" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P230" s="14" t="inlineStr"/>
+      <c r="Q230" s="15" t="inlineStr">
+        <is>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+        </is>
+      </c>
+      <c r="R230" s="14" t="inlineStr">
+        <is>
           <t>Склад 2</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="G230" s="3" t="inlineStr">
+    <row r="231">
+      <c r="G231" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="K230" s="9">
-        <f>SUM(K5:K229)</f>
+      <c r="K231" s="9">
+        <f>SUM(K5:K230)</f>
         <v/>
       </c>
-      <c r="M230" s="9">
-        <f>SUM(M5:M229)</f>
+      <c r="M231" s="9">
+        <f>SUM(M5:M230)</f>
         <v/>
       </c>
-      <c r="N230" s="10">
-        <f>SUM(N5:N229)</f>
+      <c r="N231" s="10">
+        <f>SUM(N5:N230)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R229"/>
+  <autoFilter ref="A4:R230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16624,7 +16958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17143,16 +17477,16 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E11" s="14" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200</t>
+          <t>Клапан проходной ДУ 125 корпус</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
@@ -17166,21 +17500,21 @@
         <v>1</v>
       </c>
       <c r="L11" s="20" t="n">
-        <v>110</v>
+        <v>135.3</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="N11" s="21" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O11" s="14" t="n">
-        <v>150000</v>
+        <v>37000</v>
       </c>
       <c r="P11" s="14" t="inlineStr"/>
       <c r="Q11" s="15" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="R11" s="14" t="inlineStr">
@@ -17205,14 +17539,16 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="n"/>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>200</v>
+      </c>
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
+          <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
@@ -17226,26 +17562,26 @@
         <v>1</v>
       </c>
       <c r="L12" s="20" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="N12" s="21" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="P12" s="14" t="inlineStr"/>
       <c r="Q12" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Поддон с обрешеткой, крепление к полу</t>
         </is>
       </c>
       <c r="R12" s="14" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -17268,13 +17604,11 @@
           <t>клинкет (задвижка)</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>100</v>
-      </c>
+      <c r="E13" s="14" t="n"/>
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Клинкет Ду 100, сталь</t>
+          <t>Электропривод к задвижке</t>
         </is>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
@@ -17285,29 +17619,29 @@
       </c>
       <c r="J13" s="14" t="inlineStr"/>
       <c r="K13" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="20" t="n">
-        <v>19.2</v>
+        <v>40</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N13" s="21" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="O13" s="14" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="P13" s="14" t="inlineStr"/>
       <c r="Q13" s="15" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R13" s="14" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -17322,52 +17656,54 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E14" s="14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Клинкет Ду 100, сталь</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr"/>
       <c r="K14" s="14" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L14" s="20" t="n">
-        <v>57.8</v>
+        <v>19.2</v>
       </c>
       <c r="M14" s="16" t="n">
-        <v>751</v>
+        <v>38</v>
       </c>
       <c r="N14" s="21" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="O14" s="14" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="O14" s="14" t="n">
+        <v>30000</v>
+      </c>
       <c r="P14" s="14" t="inlineStr"/>
       <c r="Q14" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="R14" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -17396,27 +17732,27 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="J15" s="14" t="inlineStr"/>
       <c r="K15" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>57.8</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>462</v>
+        <v>751</v>
       </c>
       <c r="N15" s="21" t="n">
-        <v>0.24</v>
+        <v>0.39</v>
       </c>
       <c r="O15" s="14" t="inlineStr"/>
       <c r="P15" s="14" t="inlineStr"/>
@@ -17447,16 +17783,16 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E16" s="14" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65</t>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
@@ -17467,20 +17803,18 @@
       </c>
       <c r="J16" s="14" t="inlineStr"/>
       <c r="K16" s="14" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="L16" s="20" t="n">
-        <v>17</v>
+        <v>57.8</v>
       </c>
       <c r="M16" s="16" t="n">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="N16" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O16" s="14" t="n">
-        <v>27000</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="O16" s="14" t="inlineStr"/>
       <c r="P16" s="14" t="inlineStr"/>
       <c r="Q16" s="15" t="inlineStr">
         <is>
@@ -17489,7 +17823,7 @@
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -17509,16 +17843,16 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E17" s="14" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10</t>
+          <t>Клапан фланцевый проходной Ду65</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
@@ -17529,24 +17863,24 @@
       </c>
       <c r="J17" s="14" t="inlineStr"/>
       <c r="K17" s="14" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="L17" s="20" t="n">
-        <v>3.2</v>
+        <v>17</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>264</v>
+        <v>425</v>
       </c>
       <c r="N17" s="21" t="n">
-        <v>0.083</v>
+        <v>0.5</v>
       </c>
       <c r="O17" s="14" t="n">
-        <v>3500</v>
+        <v>27000</v>
       </c>
       <c r="P17" s="14" t="inlineStr"/>
       <c r="Q17" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R17" s="14" t="inlineStr">
@@ -17571,23 +17905,19 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E18" s="14" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>526-03.097</t>
-        </is>
-      </c>
+          <t>Клапан штуцерный проходной Ду 10</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr"/>
       <c r="I18" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -17595,24 +17925,24 @@
       </c>
       <c r="J18" s="14" t="inlineStr"/>
       <c r="K18" s="14" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>57.8</v>
+        <v>2.3</v>
       </c>
       <c r="M18" s="16" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="N18" s="21" t="n">
-        <v>0.09</v>
+        <v>0.083</v>
       </c>
       <c r="O18" s="14" t="n">
-        <v>80000</v>
+        <v>3500</v>
       </c>
       <c r="P18" s="14" t="inlineStr"/>
       <c r="Q18" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R18" s="14" t="inlineStr">
@@ -17637,19 +17967,23 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="E19" s="14" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду40 - БРАК</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr"/>
+          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>526-03.097</t>
+        </is>
+      </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -17657,29 +17991,29 @@
       </c>
       <c r="J19" s="14" t="inlineStr"/>
       <c r="K19" s="14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L19" s="20" t="n">
-        <v>9.1</v>
+        <v>57.8</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="N19" s="21" t="n">
-        <v>0.104</v>
+        <v>0.09</v>
       </c>
       <c r="O19" s="14" t="n">
-        <v>12000</v>
+        <v>80000</v>
       </c>
       <c r="P19" s="14" t="inlineStr"/>
       <c r="Q19" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R19" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -17885,21 +18219,21 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E23" s="14" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>521-01.471-01</t>
+          <t>521-01.180</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -17909,19 +18243,19 @@
       </c>
       <c r="J23" s="14" t="inlineStr"/>
       <c r="K23" s="14" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L23" s="20" t="n">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
       <c r="M23" s="16" t="n">
         <v>57</v>
       </c>
       <c r="N23" s="21" t="n">
-        <v>0.018</v>
+        <v>0.03</v>
       </c>
       <c r="O23" s="14" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="P23" s="14" t="inlineStr"/>
       <c r="Q23" s="15" t="inlineStr">
@@ -17931,7 +18265,7 @@
       </c>
       <c r="R23" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -17955,12 +18289,12 @@
         </is>
       </c>
       <c r="E24" s="14" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
@@ -17974,21 +18308,21 @@
         <v>6</v>
       </c>
       <c r="L24" s="20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="M24" s="16" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N24" s="21" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="O24" s="14" t="n">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="P24" s="14" t="inlineStr"/>
       <c r="Q24" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R24" s="14" t="inlineStr">
@@ -18013,21 +18347,21 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду70 Ру10</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>522-01.226</t>
+          <t>521-03.023</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -18040,16 +18374,16 @@
         <v>2</v>
       </c>
       <c r="L25" s="20" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M25" s="16" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="N25" s="21" t="n">
-        <v>0.044</v>
+        <v>0.06</v>
       </c>
       <c r="O25" s="14" t="n">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="P25" s="14" t="inlineStr"/>
       <c r="Q25" s="15" t="inlineStr">
@@ -18059,7 +18393,7 @@
       </c>
       <c r="R25" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -18082,11 +18416,13 @@
           <t>клапан фланцевый</t>
         </is>
       </c>
-      <c r="E26" s="14" t="n"/>
+      <c r="E26" s="14" t="n">
+        <v>50</v>
+      </c>
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый сталь</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
@@ -18097,29 +18433,29 @@
       </c>
       <c r="J26" s="14" t="inlineStr"/>
       <c r="K26" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L26" s="20" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M26" s="16" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N26" s="21" t="n">
-        <v>0.02</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O26" s="14" t="n">
-        <v>18000</v>
+        <v>7500</v>
       </c>
       <c r="P26" s="14" t="inlineStr"/>
       <c r="Q26" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R26" s="14" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -18139,17 +18475,23 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="n"/>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
-        </is>
-      </c>
-      <c r="H27" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>521-01.471-01</t>
+        </is>
+      </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -18157,19 +18499,19 @@
       </c>
       <c r="J27" s="14" t="inlineStr"/>
       <c r="K27" s="14" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L27" s="20" t="n">
-        <v>40</v>
+        <v>2.3</v>
       </c>
       <c r="M27" s="16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N27" s="21" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="O27" s="14" t="n">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="P27" s="14" t="inlineStr"/>
       <c r="Q27" s="15" t="inlineStr">
@@ -18179,7 +18521,7 @@
       </c>
       <c r="R27" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -18203,15 +18545,19 @@
         </is>
       </c>
       <c r="E28" s="14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
-        </is>
-      </c>
-      <c r="H28" s="19" t="inlineStr"/>
+          <t>Клапан фланцевый проходной Ду70 Ру10</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>522-01.226</t>
+        </is>
+      </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -18222,16 +18568,16 @@
         <v>2</v>
       </c>
       <c r="L28" s="20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M28" s="16" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="N28" s="21" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="O28" s="14" t="n">
-        <v>9750</v>
+        <v>30000</v>
       </c>
       <c r="P28" s="14" t="inlineStr"/>
       <c r="Q28" s="15" t="inlineStr">
@@ -18241,7 +18587,7 @@
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -18261,36 +18607,38 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E29" s="14" t="n"/>
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Клапан электромагнитный б/у</t>
+          <t>Клапан проходной фланцевый сталь</t>
         </is>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>б/у</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="J29" s="14" t="inlineStr"/>
       <c r="K29" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L29" s="20" t="n">
-        <v>7.7</v>
+        <v>20</v>
       </c>
       <c r="M29" s="16" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N29" s="21" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O29" s="14" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="O29" s="14" t="n">
+        <v>18000</v>
+      </c>
       <c r="P29" s="14" t="inlineStr"/>
       <c r="Q29" s="15" t="inlineStr">
         <is>
@@ -18299,7 +18647,7 @@
       </c>
       <c r="R29" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -18319,23 +18667,17 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>10</v>
-      </c>
+          <t>коробка клапанная</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n"/>
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>521-01.469-03</t>
-        </is>
-      </c>
+          <t>Коробка 2-х клапанная корпус</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="inlineStr"/>
       <c r="I30" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -18343,19 +18685,19 @@
       </c>
       <c r="J30" s="14" t="inlineStr"/>
       <c r="K30" s="14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L30" s="20" t="n">
-        <v>3.2</v>
+        <v>40</v>
       </c>
       <c r="M30" s="16" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="N30" s="21" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="O30" s="14" t="n">
-        <v>4500</v>
+        <v>20000</v>
       </c>
       <c r="P30" s="14" t="inlineStr"/>
       <c r="Q30" s="15" t="inlineStr">
@@ -18365,7 +18707,7 @@
       </c>
       <c r="R30" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -18385,44 +18727,36 @@
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>10</v>
-      </c>
+          <t>клапан электромагнитный</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n"/>
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>521-35.2754</t>
-        </is>
-      </c>
+          <t>Клапан электромагнитный б/у</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr"/>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>б/у</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr"/>
       <c r="K31" s="14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L31" s="20" t="n">
-        <v>3.2</v>
+        <v>12.3</v>
       </c>
       <c r="M31" s="16" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="N31" s="21" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="O31" s="14" t="n">
-        <v>4000</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="O31" s="14" t="inlineStr"/>
       <c r="P31" s="14" t="inlineStr"/>
       <c r="Q31" s="15" t="inlineStr">
         <is>
@@ -18431,7 +18765,7 @@
       </c>
       <c r="R31" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -18451,23 +18785,19 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E32" s="14" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Р160</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>522-03,149</t>
-        </is>
-      </c>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="inlineStr"/>
       <c r="I32" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -18475,29 +18805,29 @@
       </c>
       <c r="J32" s="14" t="inlineStr"/>
       <c r="K32" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L32" s="20" t="n">
-        <v>3.2</v>
+        <v>17</v>
       </c>
       <c r="M32" s="16" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="N32" s="21" t="n">
-        <v>0.006</v>
+        <v>0.04</v>
       </c>
       <c r="O32" s="14" t="n">
-        <v>4000</v>
+        <v>9750</v>
       </c>
       <c r="P32" s="14" t="inlineStr"/>
       <c r="Q32" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R32" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -18517,23 +18847,19 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="E33" s="14" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F33" s="14" t="n"/>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65 Ру10</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>521-03.488</t>
-        </is>
-      </c>
+          <t>Захлопка Ду50Ру6 - БРАК</t>
+        </is>
+      </c>
+      <c r="H33" s="19" t="inlineStr"/>
       <c r="I33" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -18541,19 +18867,19 @@
       </c>
       <c r="J33" s="14" t="inlineStr"/>
       <c r="K33" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="20" t="n">
-        <v>17</v>
+        <v>10.8</v>
       </c>
       <c r="M33" s="16" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="N33" s="21" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>27000</v>
+        <v>17500</v>
       </c>
       <c r="P33" s="14" t="inlineStr"/>
       <c r="Q33" s="15" t="inlineStr">
@@ -18563,7 +18889,7 @@
       </c>
       <c r="R33" s="14" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -18583,49 +18909,45 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>65</v>
-      </c>
+          <t>клапан электромагнитный</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="n"/>
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
+          <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr"/>
       <c r="K34" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="20" t="n">
-        <v>17</v>
+        <v>12.3</v>
       </c>
       <c r="M34" s="16" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N34" s="21" t="n">
         <v>0.02</v>
       </c>
-      <c r="O34" s="14" t="n">
-        <v>18000</v>
-      </c>
+      <c r="O34" s="14" t="inlineStr"/>
       <c r="P34" s="14" t="inlineStr"/>
       <c r="Q34" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R34" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -18649,15 +18971,19 @@
         </is>
       </c>
       <c r="E35" s="14" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F35" s="14" t="n"/>
       <c r="G35" s="15" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
-        </is>
-      </c>
-      <c r="H35" s="19" t="inlineStr"/>
+          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>УН522-3М38</t>
+        </is>
+      </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -18665,29 +18991,29 @@
       </c>
       <c r="J35" s="14" t="inlineStr"/>
       <c r="K35" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="20" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="M35" s="16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N35" s="21" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O35" s="14" t="n">
-        <v>9750</v>
+        <v>14000</v>
       </c>
       <c r="P35" s="14" t="inlineStr"/>
       <c r="Q35" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R35" s="14" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -18707,23 +19033,19 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E36" s="14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>522-01-493</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
+        </is>
+      </c>
+      <c r="H36" s="19" t="inlineStr"/>
       <c r="I36" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -18731,29 +19053,29 @@
       </c>
       <c r="J36" s="14" t="inlineStr"/>
       <c r="K36" s="14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L36" s="20" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M36" s="16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N36" s="21" t="n">
-        <v>0.005</v>
+        <v>0.024</v>
       </c>
       <c r="O36" s="14" t="n">
-        <v>4000</v>
+        <v>15000</v>
       </c>
       <c r="P36" s="14" t="inlineStr"/>
       <c r="Q36" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R36" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -18773,45 +19095,53 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="n"/>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>65</v>
+      </c>
       <c r="F37" s="14" t="n"/>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
-        </is>
-      </c>
-      <c r="H37" s="19" t="inlineStr"/>
+          <t>Клапан фланцевый проходной Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>521-03.488</t>
+        </is>
+      </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr"/>
       <c r="K37" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37" s="20" t="n">
-        <v>7.7</v>
+        <v>17</v>
       </c>
       <c r="M37" s="16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N37" s="21" t="n">
         <v>0.02</v>
       </c>
-      <c r="O37" s="14" t="inlineStr"/>
+      <c r="O37" s="14" t="n">
+        <v>27000</v>
+      </c>
       <c r="P37" s="14" t="inlineStr"/>
       <c r="Q37" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R37" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -18831,23 +19161,19 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E38" s="14" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>521-01.471-01</t>
-        </is>
-      </c>
+          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
+        </is>
+      </c>
+      <c r="H38" s="19" t="inlineStr"/>
       <c r="I38" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -18855,29 +19181,29 @@
       </c>
       <c r="J38" s="14" t="inlineStr"/>
       <c r="K38" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L38" s="20" t="n">
-        <v>3.2</v>
+        <v>17</v>
       </c>
       <c r="M38" s="16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N38" s="21" t="n">
-        <v>0.004</v>
+        <v>0.02</v>
       </c>
       <c r="O38" s="14" t="n">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="P38" s="14" t="inlineStr"/>
       <c r="Q38" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R38" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -18901,19 +19227,15 @@
         </is>
       </c>
       <c r="E39" s="14" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>595-01-010</t>
-        </is>
-      </c>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr"/>
       <c r="I39" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -18921,27 +19243,29 @@
       </c>
       <c r="J39" s="14" t="inlineStr"/>
       <c r="K39" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="20" t="n">
-        <v>5.6</v>
+        <v>17</v>
       </c>
       <c r="M39" s="16" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N39" s="21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O39" s="14" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="O39" s="14" t="n">
+        <v>9750</v>
+      </c>
       <c r="P39" s="14" t="inlineStr"/>
       <c r="Q39" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R39" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -18961,21 +19285,21 @@
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E40" s="14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F40" s="14" t="n"/>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>595-3М-48</t>
+          <t>522-01.497</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
@@ -18985,27 +19309,29 @@
       </c>
       <c r="J40" s="14" t="inlineStr"/>
       <c r="K40" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L40" s="20" t="n">
-        <v>9.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="M40" s="16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N40" s="21" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="O40" s="14" t="inlineStr"/>
+        <v>0.005</v>
+      </c>
+      <c r="O40" s="14" t="n">
+        <v>2000</v>
+      </c>
       <c r="P40" s="14" t="inlineStr"/>
       <c r="Q40" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R40" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -19029,17 +19355,17 @@
         </is>
       </c>
       <c r="E41" s="14" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F41" s="14" t="n"/>
       <c r="G41" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>595-35-021</t>
+          <t>521-01.068</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -19052,24 +19378,26 @@
         <v>1</v>
       </c>
       <c r="L41" s="20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="M41" s="16" t="n">
         <v>9</v>
       </c>
       <c r="N41" s="21" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="O41" s="14" t="inlineStr"/>
+        <v>0.005</v>
+      </c>
+      <c r="O41" s="14" t="n">
+        <v>9600</v>
+      </c>
       <c r="P41" s="14" t="inlineStr"/>
       <c r="Q41" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R41" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -19093,17 +19421,17 @@
         </is>
       </c>
       <c r="E42" s="14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F42" s="14" t="n"/>
       <c r="G42" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>521-35.2608-01</t>
+          <t>521-01.471-01</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
@@ -19113,18 +19441,20 @@
       </c>
       <c r="J42" s="14" t="inlineStr"/>
       <c r="K42" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="20" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M42" s="16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N42" s="21" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O42" s="14" t="inlineStr"/>
+        <v>0.004</v>
+      </c>
+      <c r="O42" s="14" t="n">
+        <v>2000</v>
+      </c>
       <c r="P42" s="14" t="inlineStr"/>
       <c r="Q42" s="15" t="inlineStr">
         <is>
@@ -19133,7 +19463,7 @@
       </c>
       <c r="R42" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -19153,19 +19483,21 @@
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="n"/>
+          <t>клапан пожарный</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>50</v>
+      </c>
       <c r="F43" s="14" t="n"/>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>587-182.126</t>
+          <t>595-3М-48</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -19178,19 +19510,19 @@
         <v>1</v>
       </c>
       <c r="L43" s="20" t="n">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M43" s="16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N43" s="21" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="O43" s="14" t="inlineStr"/>
       <c r="P43" s="14" t="inlineStr"/>
       <c r="Q43" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R43" s="14" t="inlineStr">
@@ -19215,19 +19547,21 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
-        </is>
-      </c>
-      <c r="E44" s="14" t="n"/>
+          <t>клапан пожарный</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>50</v>
+      </c>
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="15" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>2619802505</t>
+          <t>595-35-021</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
@@ -19240,19 +19574,19 @@
         <v>1</v>
       </c>
       <c r="L44" s="20" t="n">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M44" s="16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N44" s="21" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="O44" s="14" t="inlineStr"/>
       <c r="P44" s="14" t="inlineStr"/>
       <c r="Q44" s="15" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="R44" s="14" t="inlineStr">
@@ -19281,17 +19615,17 @@
         </is>
       </c>
       <c r="E45" s="14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F45" s="14" t="n"/>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>521-03.124</t>
+          <t>521-35.2608-01</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -19301,20 +19635,18 @@
       </c>
       <c r="J45" s="14" t="inlineStr"/>
       <c r="K45" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="20" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M45" s="16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N45" s="21" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="O45" s="14" t="n">
-        <v>1250</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="O45" s="14" t="inlineStr"/>
       <c r="P45" s="14" t="inlineStr"/>
       <c r="Q45" s="15" t="inlineStr">
         <is>
@@ -19343,23 +19675,17 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>10</v>
-      </c>
+          <t>клапан без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="n"/>
       <c r="F46" s="14" t="n"/>
       <c r="G46" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>521-01.469-02</t>
-        </is>
-      </c>
+          <t>Судовая запорная арматура</t>
+        </is>
+      </c>
+      <c r="H46" s="19" t="inlineStr"/>
       <c r="I46" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -19367,19 +19693,19 @@
       </c>
       <c r="J46" s="14" t="inlineStr"/>
       <c r="K46" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" s="20" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="M46" s="16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N46" s="21" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="O46" s="14" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="P46" s="14" t="inlineStr"/>
       <c r="Q46" s="15" t="inlineStr">
@@ -19389,7 +19715,7 @@
       </c>
       <c r="R46" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -19409,21 +19735,19 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>10</v>
-      </c>
+          <t>клапан без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="n"/>
       <c r="F47" s="14" t="n"/>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Клапан</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>522-01.497</t>
+          <t>587-182.126</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -19433,20 +19757,18 @@
       </c>
       <c r="J47" s="14" t="inlineStr"/>
       <c r="K47" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="20" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="M47" s="16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N47" s="21" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O47" s="14" t="n">
-        <v>2000</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="O47" s="14" t="inlineStr"/>
       <c r="P47" s="14" t="inlineStr"/>
       <c r="Q47" s="15" t="inlineStr">
         <is>
@@ -19455,7 +19777,7 @@
       </c>
       <c r="R47" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -19475,21 +19797,19 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>32</v>
-      </c>
+          <t>клапан без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="n"/>
       <c r="F48" s="14" t="n"/>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>595-03-006</t>
+          <t>2619802505</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
@@ -19502,13 +19822,13 @@
         <v>1</v>
       </c>
       <c r="L48" s="20" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="M48" s="16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N48" s="21" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O48" s="14" t="inlineStr"/>
       <c r="P48" s="14" t="inlineStr"/>
@@ -19539,7 +19859,7 @@
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E49" s="14" t="n">
@@ -19548,10 +19868,14 @@
       <c r="F49" s="14" t="n"/>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
-        </is>
-      </c>
-      <c r="H49" s="19" t="inlineStr"/>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>595-03-006</t>
+        </is>
+      </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -19562,17 +19886,15 @@
         <v>1</v>
       </c>
       <c r="L49" s="20" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="M49" s="16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N49" s="21" t="n">
         <v>0.005</v>
       </c>
-      <c r="O49" s="14" t="n">
-        <v>1500</v>
-      </c>
+      <c r="O49" s="14" t="inlineStr"/>
       <c r="P49" s="14" t="inlineStr"/>
       <c r="Q49" s="15" t="inlineStr">
         <is>
@@ -19605,17 +19927,17 @@
         </is>
       </c>
       <c r="E50" s="14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F50" s="14" t="n"/>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>521-3м-953</t>
+          <t>521-03.124</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
@@ -19625,19 +19947,19 @@
       </c>
       <c r="J50" s="14" t="inlineStr"/>
       <c r="K50" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="20" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M50" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N50" s="21" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="O50" s="14" t="n">
-        <v>2000</v>
+        <v>1250</v>
       </c>
       <c r="P50" s="14" t="inlineStr"/>
       <c r="Q50" s="15" t="inlineStr">
@@ -19671,19 +19993,15 @@
         </is>
       </c>
       <c r="E51" s="14" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F51" s="14" t="n"/>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>522-03.134</t>
-        </is>
-      </c>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+        </is>
+      </c>
+      <c r="H51" s="19" t="inlineStr"/>
       <c r="I51" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -19694,16 +20012,16 @@
         <v>1</v>
       </c>
       <c r="L51" s="20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="M51" s="16" t="n">
         <v>3</v>
       </c>
       <c r="N51" s="21" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="O51" s="14" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="P51" s="14" t="inlineStr"/>
       <c r="Q51" s="15" t="inlineStr">
@@ -19737,17 +20055,17 @@
         </is>
       </c>
       <c r="E52" s="14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F52" s="14" t="n"/>
       <c r="G52" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
         </is>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>521-3м-52</t>
+          <t>528-35.176</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
@@ -19760,17 +20078,15 @@
         <v>1</v>
       </c>
       <c r="L52" s="20" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M52" s="16" t="n">
         <v>3</v>
       </c>
       <c r="N52" s="21" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O52" s="14" t="n">
-        <v>2000</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="O52" s="14" t="inlineStr"/>
       <c r="P52" s="14" t="inlineStr"/>
       <c r="Q52" s="15" t="inlineStr">
         <is>
@@ -19808,12 +20124,12 @@
       <c r="F53" s="14" t="n"/>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
         </is>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>522-01.499-01</t>
+          <t>521-3м-953</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
@@ -19826,10 +20142,10 @@
         <v>1</v>
       </c>
       <c r="L53" s="20" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="M53" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N53" s="21" t="n">
         <v>0.001</v>
@@ -19874,12 +20190,12 @@
       <c r="F54" s="14" t="n"/>
       <c r="G54" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>521-01.467-03</t>
+          <t>522-03.134</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
@@ -19892,10 +20208,10 @@
         <v>1</v>
       </c>
       <c r="L54" s="20" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="M54" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N54" s="21" t="n">
         <v>0.001</v>
@@ -19940,12 +20256,12 @@
       <c r="F55" s="14" t="n"/>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
         </is>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
-          <t>Без чертежа</t>
+          <t>521-3м-52</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
@@ -19958,10 +20274,10 @@
         <v>1</v>
       </c>
       <c r="L55" s="20" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="M55" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" s="21" t="n">
         <v>0.001</v>
@@ -19977,7 +20293,7 @@
       </c>
       <c r="R55" s="14" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -20011,7 +20327,7 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>521-01.493-02</t>
+          <t>522-01.499-01</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
@@ -20024,15 +20340,17 @@
         <v>1</v>
       </c>
       <c r="L56" s="20" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="M56" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N56" s="21" t="n">
         <v>0.001</v>
       </c>
-      <c r="O56" s="14" t="inlineStr"/>
+      <c r="O56" s="14" t="n">
+        <v>2000</v>
+      </c>
       <c r="P56" s="14" t="inlineStr"/>
       <c r="Q56" s="15" t="inlineStr">
         <is>
@@ -20065,17 +20383,17 @@
         </is>
       </c>
       <c r="E57" s="14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F57" s="14" t="n"/>
       <c r="G57" s="15" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
-          <t>528-35.176</t>
+          <t>521-01.467-03</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
@@ -20088,15 +20406,17 @@
         <v>1</v>
       </c>
       <c r="L57" s="20" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M57" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N57" s="21" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O57" s="14" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="O57" s="14" t="n">
+        <v>2000</v>
+      </c>
       <c r="P57" s="14" t="inlineStr"/>
       <c r="Q57" s="15" t="inlineStr">
         <is>
@@ -20129,15 +20449,19 @@
         </is>
       </c>
       <c r="E58" s="14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F58" s="14" t="n"/>
       <c r="G58" s="15" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
-        </is>
-      </c>
-      <c r="H58" s="19" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>Без чертежа</t>
+        </is>
+      </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -20148,16 +20472,16 @@
         <v>1</v>
       </c>
       <c r="L58" s="20" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M58" s="16" t="n">
         <v>2</v>
       </c>
       <c r="N58" s="21" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="O58" s="14" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="P58" s="14" t="inlineStr"/>
       <c r="Q58" s="15" t="inlineStr">
@@ -20167,7 +20491,7 @@
       </c>
       <c r="R58" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -20190,16 +20514,18 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="E59" s="14" t="n"/>
+      <c r="E59" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="F59" s="14" t="n"/>
       <c r="G59" s="15" t="inlineStr">
         <is>
-          <t>Клапан дроссельный угловой штуцерный</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>525-35.577</t>
+          <t>521-01.469-02</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -20212,15 +20538,17 @@
         <v>1</v>
       </c>
       <c r="L59" s="20" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M59" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N59" s="21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O59" s="14" t="inlineStr"/>
+        <v>0.001</v>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>2000</v>
+      </c>
       <c r="P59" s="14" t="inlineStr"/>
       <c r="Q59" s="15" t="inlineStr">
         <is>
@@ -20229,7 +20557,7 @@
       </c>
       <c r="R59" s="14" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -20252,16 +20580,18 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="E60" s="14" t="n"/>
+      <c r="E60" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="F60" s="14" t="n"/>
       <c r="G60" s="15" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>521-03.472-01</t>
+          <t>521-01.493-02</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -20274,13 +20604,13 @@
         <v>1</v>
       </c>
       <c r="L60" s="20" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M60" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N60" s="21" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="O60" s="14" t="inlineStr"/>
       <c r="P60" s="14" t="inlineStr"/>
@@ -20306,21 +20636,21 @@
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="E61" s="14" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F61" s="14" t="n"/>
       <c r="G61" s="15" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду100 или Ду80</t>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
         </is>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
@@ -20331,24 +20661,24 @@
       </c>
       <c r="J61" s="14" t="inlineStr"/>
       <c r="K61" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M61" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="L61" s="20" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="M61" s="16" t="n">
-        <v>87</v>
-      </c>
       <c r="N61" s="21" t="n">
-        <v>0.09</v>
+        <v>0.002</v>
       </c>
       <c r="O61" s="14" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="P61" s="14" t="inlineStr"/>
       <c r="Q61" s="15" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="R61" s="14" t="inlineStr">
@@ -20368,24 +20698,26 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
-        </is>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>100</v>
-      </c>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="n"/>
       <c r="F62" s="14" t="n"/>
       <c r="G62" s="15" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
-        </is>
-      </c>
-      <c r="H62" s="19" t="inlineStr"/>
+          <t>Клапан дроссельный угловой штуцерный</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>525-35.577</t>
+        </is>
+      </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
           <t>не указано</t>
@@ -20393,53 +20725,237 @@
       </c>
       <c r="J62" s="14" t="inlineStr"/>
       <c r="K62" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" s="20" t="n">
-        <v>43.5</v>
+        <v>1.3</v>
       </c>
       <c r="M62" s="16" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="N62" s="21" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="O62" s="14" t="n">
-        <v>10000</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="O62" s="14" t="inlineStr"/>
       <c r="P62" s="14" t="inlineStr"/>
       <c r="Q62" s="15" t="inlineStr">
         <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="R62" s="14" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>Б. Добор со склада</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="n"/>
+      <c r="F63" s="14" t="n"/>
+      <c r="G63" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>521-03.472-01</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="inlineStr"/>
+      <c r="K63" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M63" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O63" s="14" t="inlineStr"/>
+      <c r="P63" s="14" t="inlineStr"/>
+      <c r="Q63" s="15" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="R63" s="14" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>Б. Добор со склада</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Ярус 4, верх</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>фильтр забортной воды</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F64" s="14" t="n"/>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>Сетка на фильтр Ду100 или Ду80</t>
+        </is>
+      </c>
+      <c r="H64" s="19" t="inlineStr"/>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="inlineStr"/>
+      <c r="K64" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" s="20" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="M64" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="N64" s="21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P64" s="14" t="inlineStr"/>
+      <c r="Q64" s="15" t="inlineStr">
+        <is>
           <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
-      <c r="R62" s="14" t="inlineStr">
+      <c r="R64" s="14" t="inlineStr">
         <is>
           <t>Склад 2</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="G63" s="3" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>Б. Добор со склада</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>Ярус 4, верх</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>фильтр забортной воды</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F65" s="14" t="n"/>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
+        </is>
+      </c>
+      <c r="H65" s="19" t="inlineStr"/>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="J65" s="14" t="inlineStr"/>
+      <c r="K65" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L65" s="20" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="M65" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="N65" s="21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O65" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P65" s="14" t="inlineStr"/>
+      <c r="Q65" s="15" t="inlineStr">
+        <is>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+        </is>
+      </c>
+      <c r="R65" s="14" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="K63" s="9">
-        <f>SUM(K5:K62)</f>
+      <c r="K66" s="9">
+        <f>SUM(K5:K65)</f>
         <v/>
       </c>
-      <c r="M63" s="9">
-        <f>SUM(M5:M62)</f>
+      <c r="M66" s="9">
+        <f>SUM(M5:M65)</f>
         <v/>
       </c>
-      <c r="N63" s="10">
-        <f>SUM(N5:N62)</f>
+      <c r="N66" s="10">
+        <f>SUM(N5:N65)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R62"/>
+  <autoFilter ref="A4:R65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/outputs/marine_equipment/Контейнер_22т_Питер.xlsx
+++ b/outputs/marine_equipment/Контейнер_22т_Питер.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Контейнер 22 т" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Остается" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Упаковка и крепление" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ящики и места" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Упаковка и крепление" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Контейнер 22 т'!$A$4:$Q$251</definedName>
@@ -133,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -186,6 +187,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -553,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1382,6 +1392,27 @@
       <c r="A49" s="17" t="inlineStr">
         <is>
           <t>— Остатки недостоверны: сверка была 16.06.2025. Количества блока Б подтверждаются только пересчетом на складе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>— 22 тонны — это предел старого двадцатифутового по ГОСТ 8477-79: брутто 24 т минус тара 2,2-2,3 т. Внутри 5867 х 2330 х 2343 мм, 33 куб. м.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>— У «тяжелого» двадцатифутового по ИСО 1СС брутто 30,48 т и тара 2,2-2,3 т, то есть под груз остается около 28 т при том же объеме 33 куб. м. Если перевозчик дает такой контейнер, в него войдет на 6 тонн больше — спросите тип при заказе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>— Объем у обоих одинаковый, 33 куб. м, и мы в него уперлись. Значит лишние тонны можно взять только более плотным грузом: задвижками, а не ящиками с мелочью.</t>
         </is>
       </c>
     </row>
@@ -20259,6 +20290,6836 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H247"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Сколько ящиков сбить и что в них класть</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ящик 1200 x 1000 x 1000 мм, на поддоне. Считаем не больше 600 кг и 0.9 куб. м на ящик: доска бэушная, рамного бруса по углам нет. Позиции одной группы стараемся не разносить по разным ящикам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Ящиков собрать</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>21 шт</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1200 x 1000 x 1000 мм, на поддоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>В ящики идет</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>11.7 т</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>193 позиций, 2387 штук</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>На настил и поддоны</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>10.0 т</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>33 позиций — задвижки и крупные клапаны, в ящики не кладем</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Поддонов под ящики</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>21 шт</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>по одному на ящик, плюс запас на бой</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Ящик №</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Что внутри</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Чертеж</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Ду</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Штук</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Вес, кг</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Объем, куб. м</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 1</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n">
+        <v>215</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>597</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>524-03.004</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n"/>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду6Ру100</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>521-01.467-02</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>522-03.149</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n"/>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>522-03,149</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>521-01.465-01</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду 15</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>521--01.468-08</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду 15 НЕРЖ</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>521-03.478-01</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr"/>
+      <c r="E18" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468-05</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>521-35.3362</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>521-01.464-02</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>522-01.500-05</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>521-03.387</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>521-03.387</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>522-01.500-04</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="n"/>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>521-01.464-01</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="n"/>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="n"/>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15Ру40</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>521-01.465-02</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Клапан невозв-запор.цапковый угловой  под дюрит Ду20Ру6</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>522-03.123</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>522-03.123</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду20 Ру100</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468-05</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>521-03.479</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="n"/>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>521-03.479</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n"/>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>521-01.465-03</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>522-35.3632</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="21" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду25</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>521--01.468-08</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду25</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>521--35.3363</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду25</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr"/>
+      <c r="E38" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" s="21" t="n">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду25 Ру 100</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>521--35.3363</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="n"/>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду25 Ру100</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468-06</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H40" s="21" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="n"/>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="inlineStr"/>
+      <c r="E41" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="H41" s="21" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="n"/>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32 Ру100</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468-07</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G42" s="16" t="n">
+        <v>63</v>
+      </c>
+      <c r="H42" s="21" t="n">
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="n"/>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468-07</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="H43" s="21" t="n">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="n"/>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>521-01.464-07</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="21" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="n"/>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>521-01.464-06</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="n"/>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>522-01.500-07</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="n"/>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>521-01.464-07</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="21" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="n"/>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>521-01.464-06</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="n"/>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>522-01.500-07</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="n"/>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468-07</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="H50" s="21" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 2</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная, Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="n"/>
+      <c r="D51" s="26" t="n"/>
+      <c r="E51" s="26" t="n"/>
+      <c r="F51" s="26" t="n">
+        <v>461</v>
+      </c>
+      <c r="G51" s="28" t="n">
+        <v>599</v>
+      </c>
+      <c r="H51" s="26" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="n"/>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468-07</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="H52" s="21" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="n"/>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>521-03.445-04</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" s="21" t="n">
+        <v>0.048</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="n"/>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Рр150/10</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>521-ц22п</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="n"/>
+      <c r="F54" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H54" s="21" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="n"/>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Рр150/10</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>521-ц22п</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="n"/>
+      <c r="F55" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H55" s="21" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="n"/>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>521-35.2754</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H56" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="n"/>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>521-35.2754</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H57" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="n"/>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>521-01.469-03</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G58" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="H58" s="21" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="n"/>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>521-01.469-02</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="n"/>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>521-01.471-01</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>409</v>
+      </c>
+      <c r="G60" s="16" t="n">
+        <v>491</v>
+      </c>
+      <c r="H60" s="21" t="n">
+        <v>0.409</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 3</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="n"/>
+      <c r="D61" s="26" t="n"/>
+      <c r="E61" s="26" t="n"/>
+      <c r="F61" s="26" t="n">
+        <v>437</v>
+      </c>
+      <c r="G61" s="28" t="n">
+        <v>598</v>
+      </c>
+      <c r="H61" s="26" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="n"/>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>521-01.471-01</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>389</v>
+      </c>
+      <c r="G62" s="16" t="n">
+        <v>467</v>
+      </c>
+      <c r="H62" s="21" t="n">
+        <v>0.389</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="n"/>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>521-35.3238</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="n"/>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>521-35.3238</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="n"/>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>521-03.420</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="n"/>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>522-01-493</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G66" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H66" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="n"/>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>522-01-493-01</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="n"/>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>528-35.176</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="n"/>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>521 3м.770</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H69" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="n"/>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>без чертежа</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F70" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="n"/>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>522-01.498</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F71" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="n"/>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>521-01.470</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F72" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="n"/>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>521. 3м.666</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F73" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H73" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="n"/>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>521-01.470.02</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F74" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="n"/>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>522-01.501-01</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F75" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="n"/>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>521-01.471-02</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F76" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H76" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="n"/>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной бессальниковый  Ду15/1</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>521-35.2608-01</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H77" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="n"/>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штущерный проходной Ду15</t>
+        </is>
+      </c>
+      <c r="D78" s="25" t="inlineStr"/>
+      <c r="E78" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F78" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G78" s="16" t="n">
+        <v>62</v>
+      </c>
+      <c r="H78" s="21" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 4</t>
+        </is>
+      </c>
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="n"/>
+      <c r="D79" s="26" t="n"/>
+      <c r="E79" s="26" t="n"/>
+      <c r="F79" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="G79" s="28" t="n">
+        <v>598</v>
+      </c>
+      <c r="H79" s="26" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="n"/>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штущерный проходной Ду15</t>
+        </is>
+      </c>
+      <c r="D80" s="25" t="inlineStr"/>
+      <c r="E80" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F80" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G80" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="H80" s="21" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="n"/>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>522-3м-9</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="n"/>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>522-03.089</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="n"/>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>522-03.089</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F83" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="n"/>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20</t>
+        </is>
+      </c>
+      <c r="D84" s="25" t="inlineStr"/>
+      <c r="E84" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F84" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G84" s="16" t="n">
+        <v>195</v>
+      </c>
+      <c r="H84" s="21" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="n"/>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>536-3м 5</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F85" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G85" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H85" s="21" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="n"/>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>536 3м .333</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="n"/>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>521-01.052</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="n"/>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>521-01.470-02</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="G88" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="H88" s="21" t="n">
+        <v>0.026</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="n"/>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>521-01.471-03</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="n"/>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>521-01.052</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F90" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" s="21" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="n"/>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>521-01.470-02</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H91" s="21" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="n"/>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>521-01.498-03</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G92" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="H92" s="21" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="n"/>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>522-01.498-02</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G93" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="H93" s="21" t="n">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="n"/>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>521-01.468-05</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F94" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H94" s="21" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="n"/>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>522-01.498.-03</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F95" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="n"/>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>425-322710</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F96" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="n"/>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>521-01464-02</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F97" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G97" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H97" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="n"/>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>521-01.470-03</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F98" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="G98" s="16" t="n">
+        <v>199</v>
+      </c>
+      <c r="H98" s="21" t="n">
+        <v>0.204</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="n"/>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>521-01464-03</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F99" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G99" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H99" s="21" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 5</t>
+        </is>
+      </c>
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная, Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C100" s="26" t="n"/>
+      <c r="D100" s="26" t="n"/>
+      <c r="E100" s="26" t="n"/>
+      <c r="F100" s="26" t="n">
+        <v>347</v>
+      </c>
+      <c r="G100" s="28" t="n">
+        <v>597</v>
+      </c>
+      <c r="H100" s="26" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="n"/>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>522-01500-05</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F101" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G101" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H101" s="21" t="n">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="n"/>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>Без чертежа</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F102" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G102" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H102" s="21" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="n"/>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>521-01474-03</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G103" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="H103" s="21" t="n">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="n"/>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>521 3м 623</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F104" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G104" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="H104" s="21" t="n">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="n"/>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>521 3м 726</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F105" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H105" s="21" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="n"/>
+      <c r="B106" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>521 3м 30</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H106" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="14" t="n"/>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>522 3м 13</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F107" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H107" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="n"/>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>522-01.501-02</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F108" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="G108" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="H108" s="21" t="n">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="14" t="n"/>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>521 3м 58</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F109" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G109" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="H109" s="21" t="n">
+        <v>0.046</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="14" t="n"/>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>522-35 240</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F110" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="n"/>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>Без чертежа</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F111" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G111" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H111" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="n"/>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16                             (Ду25Ру16 -1 шт ; Ду25Ру10 -1шт )</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>521-03.124</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F112" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="14" t="n"/>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
+        </is>
+      </c>
+      <c r="D113" s="25" t="inlineStr"/>
+      <c r="E113" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F113" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="G113" s="16" t="n">
+        <v>138</v>
+      </c>
+      <c r="H113" s="21" t="n">
+        <v>0.237</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="n"/>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>521.3м.660</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F114" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G114" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H114" s="21" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="14" t="n"/>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>Клапан для манометра штущерный  Ду3Ру400 новый</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>521-03.406</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F115" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H115" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="n"/>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>521-02.013</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="14" t="n"/>
+      <c r="B117" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C117" s="15" t="inlineStr">
+        <is>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>521-02.014</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="n"/>
+      <c r="B118" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="inlineStr">
+        <is>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>521-02.013</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F118" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="G118" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="H118" s="21" t="n">
+        <v>0.048</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="n"/>
+      <c r="B119" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C119" s="15" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>524-35.2423-01</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H119" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="14" t="n"/>
+      <c r="B120" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>524-03.188</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F120" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H120" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="14" t="n"/>
+      <c r="B121" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>524-03.174</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="14" t="n"/>
+      <c r="B122" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>524-03.173</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="14" t="n"/>
+      <c r="B123" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C123" s="15" t="inlineStr">
+        <is>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>522-03.122-04</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F123" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G123" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H123" s="21" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="n"/>
+      <c r="B124" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="inlineStr">
+        <is>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>522-03.124-04</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H124" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="14" t="n"/>
+      <c r="B125" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C125" s="15" t="inlineStr">
+        <is>
+          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>ИШТЛ 491112-003-04</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F125" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G125" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="H125" s="21" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 6</t>
+        </is>
+      </c>
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая, Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C126" s="26" t="n"/>
+      <c r="D126" s="26" t="n"/>
+      <c r="E126" s="26" t="n"/>
+      <c r="F126" s="26" t="n">
+        <v>73</v>
+      </c>
+      <c r="G126" s="28" t="n">
+        <v>559</v>
+      </c>
+      <c r="H126" s="26" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="14" t="n"/>
+      <c r="B127" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C127" s="15" t="inlineStr">
+        <is>
+          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>ИШТЛ 491112-003-04</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F127" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G127" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="H127" s="21" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="14" t="n"/>
+      <c r="B128" s="15" t="inlineStr">
+        <is>
+          <t>Штуцерная, угол или проход не указан</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="inlineStr">
+        <is>
+          <t>Клапан для манометра штуцерный сальниковый</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>521-34.3404-03</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="n"/>
+      <c r="F128" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G128" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H128" s="21" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="14" t="n"/>
+      <c r="B129" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду25</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="inlineStr">
+        <is>
+          <t>521-3М539</t>
+        </is>
+      </c>
+      <c r="E129" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F129" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="G129" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="H129" s="21" t="n">
+        <v>0.039</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="n"/>
+      <c r="B130" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду25</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>521-3М.123</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F130" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H130" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="n"/>
+      <c r="B131" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C131" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду25</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>521-3М539</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F131" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H131" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="n"/>
+      <c r="B132" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C132" s="15" t="inlineStr">
+        <is>
+          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
+        </is>
+      </c>
+      <c r="D132" s="25" t="inlineStr"/>
+      <c r="E132" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F132" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H132" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="14" t="n"/>
+      <c r="B133" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C133" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>595-03-006</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F133" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H133" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="14" t="n"/>
+      <c r="B134" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>595-01-010</t>
+        </is>
+      </c>
+      <c r="E134" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F134" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G134" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="H134" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="n"/>
+      <c r="B135" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C135" s="15" t="inlineStr">
+        <is>
+          <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
+        </is>
+      </c>
+      <c r="D135" s="25" t="inlineStr"/>
+      <c r="E135" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F135" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G135" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H135" s="21" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="n"/>
+      <c r="B136" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду40 Ру10</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>522-03.202</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F136" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H136" s="21" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="14" t="n"/>
+      <c r="B137" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C137" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду40 Ру25</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>521-01.200</t>
+        </is>
+      </c>
+      <c r="E137" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F137" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H137" s="21" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="14" t="n"/>
+      <c r="B138" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C138" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>522-35.445-19</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F138" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G138" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="H138" s="21" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="14" t="n"/>
+      <c r="B139" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C139" s="15" t="inlineStr">
+        <is>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>595-03.011</t>
+        </is>
+      </c>
+      <c r="E139" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F139" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G139" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="H139" s="21" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="14" t="n"/>
+      <c r="B140" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C140" s="15" t="inlineStr">
+        <is>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>595-03.008</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F140" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H140" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="14" t="n"/>
+      <c r="B141" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C141" s="15" t="inlineStr">
+        <is>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>без чертежа</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F141" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G141" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="H141" s="21" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="14" t="n"/>
+      <c r="B142" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
+        </is>
+      </c>
+      <c r="D142" s="25" t="inlineStr"/>
+      <c r="E142" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F142" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H142" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="14" t="n"/>
+      <c r="B143" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C143" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду50</t>
+        </is>
+      </c>
+      <c r="D143" s="25" t="inlineStr"/>
+      <c r="E143" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F143" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G143" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="H143" s="21" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="14" t="n"/>
+      <c r="B144" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C144" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>522-35.4154-02</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F144" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G144" s="16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H144" s="21" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="14" t="n"/>
+      <c r="B145" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C145" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>522-35.4154-02</t>
+        </is>
+      </c>
+      <c r="E145" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F145" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G145" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="H145" s="21" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="14" t="n"/>
+      <c r="B146" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C146" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>522-35.4201</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F146" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G146" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="H146" s="21" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="14" t="n"/>
+      <c r="B147" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C147" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>521-03.195</t>
+        </is>
+      </c>
+      <c r="E147" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F147" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H147" s="21" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 7</t>
+        </is>
+      </c>
+      <c r="B148" s="27" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C148" s="26" t="n"/>
+      <c r="D148" s="26" t="n"/>
+      <c r="E148" s="26" t="n"/>
+      <c r="F148" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="G148" s="28" t="n">
+        <v>589</v>
+      </c>
+      <c r="H148" s="26" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="14" t="n"/>
+      <c r="B149" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C149" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>521-03.195</t>
+        </is>
+      </c>
+      <c r="E149" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F149" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G149" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="H149" s="21" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="14" t="n"/>
+      <c r="B150" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду65 Ру40</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>521-03.230</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F150" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H150" s="21" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="14" t="n"/>
+      <c r="B151" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C151" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду80</t>
+        </is>
+      </c>
+      <c r="D151" s="14" t="inlineStr">
+        <is>
+          <t>522-03.197</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F151" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G151" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="H151" s="21" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 8</t>
+        </is>
+      </c>
+      <c r="B152" s="27" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная, Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C152" s="26" t="n"/>
+      <c r="D152" s="26" t="n"/>
+      <c r="E152" s="26" t="n"/>
+      <c r="F152" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="G152" s="28" t="n">
+        <v>592</v>
+      </c>
+      <c r="H152" s="26" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="14" t="n"/>
+      <c r="B153" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C153" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду80</t>
+        </is>
+      </c>
+      <c r="D153" s="14" t="inlineStr">
+        <is>
+          <t>522-03.197</t>
+        </is>
+      </c>
+      <c r="E153" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F153" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G153" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="H153" s="21" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="14" t="n"/>
+      <c r="B154" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C154" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
+        </is>
+      </c>
+      <c r="D154" s="14" t="inlineStr">
+        <is>
+          <t>521-3М.324</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F154" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G154" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="H154" s="21" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="14" t="n"/>
+      <c r="B155" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C155" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной ДУ25 ???</t>
+        </is>
+      </c>
+      <c r="D155" s="14" t="inlineStr">
+        <is>
+          <t>с камчатки</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F155" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H155" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="14" t="n"/>
+      <c r="B156" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="inlineStr">
+        <is>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
+        </is>
+      </c>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>521-03.020</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F156" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G156" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="H156" s="21" t="n">
+        <v>0.056</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="14" t="n"/>
+      <c r="B157" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C157" s="15" t="inlineStr">
+        <is>
+          <t>Клапан проходной фланцевый Ду40 - БРАК</t>
+        </is>
+      </c>
+      <c r="D157" s="25" t="inlineStr"/>
+      <c r="E157" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F157" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="G157" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="H157" s="21" t="n">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="14" t="n"/>
+      <c r="B158" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C158" s="15" t="inlineStr">
+        <is>
+          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
+        </is>
+      </c>
+      <c r="D158" s="14" t="inlineStr">
+        <is>
+          <t>595-01.002</t>
+        </is>
+      </c>
+      <c r="E158" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F158" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H158" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="14" t="n"/>
+      <c r="B159" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C159" s="15" t="inlineStr">
+        <is>
+          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
+        </is>
+      </c>
+      <c r="D159" s="25" t="inlineStr"/>
+      <c r="E159" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F159" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G159" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="H159" s="21" t="n">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="14" t="n"/>
+      <c r="B160" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C160" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду50</t>
+        </is>
+      </c>
+      <c r="D160" s="25" t="inlineStr"/>
+      <c r="E160" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F160" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G160" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="H160" s="21" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 9</t>
+        </is>
+      </c>
+      <c r="B161" s="27" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C161" s="26" t="n"/>
+      <c r="D161" s="26" t="n"/>
+      <c r="E161" s="26" t="n"/>
+      <c r="F161" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="G161" s="28" t="n">
+        <v>592</v>
+      </c>
+      <c r="H161" s="26" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="14" t="n"/>
+      <c r="B162" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C162" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду50</t>
+        </is>
+      </c>
+      <c r="D162" s="25" t="inlineStr"/>
+      <c r="E162" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F162" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G162" s="16" t="n">
+        <v>528</v>
+      </c>
+      <c r="H162" s="21" t="n">
+        <v>0.528</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="14" t="n"/>
+      <c r="B163" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C163" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду50</t>
+        </is>
+      </c>
+      <c r="D163" s="25" t="inlineStr"/>
+      <c r="E163" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F163" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G163" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="H163" s="21" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 10</t>
+        </is>
+      </c>
+      <c r="B164" s="27" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C164" s="26" t="n"/>
+      <c r="D164" s="26" t="n"/>
+      <c r="E164" s="26" t="n"/>
+      <c r="F164" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="G164" s="28" t="n">
+        <v>596</v>
+      </c>
+      <c r="H164" s="26" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="14" t="n"/>
+      <c r="B165" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C165" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду50</t>
+        </is>
+      </c>
+      <c r="D165" s="25" t="inlineStr"/>
+      <c r="E165" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F165" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G165" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="H165" s="21" t="n">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="14" t="n"/>
+      <c r="B166" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C166" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
+        </is>
+      </c>
+      <c r="D166" s="25" t="inlineStr"/>
+      <c r="E166" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F166" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G166" s="16" t="n">
+        <v>486</v>
+      </c>
+      <c r="H166" s="21" t="n">
+        <v>0.636</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 11</t>
+        </is>
+      </c>
+      <c r="B167" s="27" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C167" s="26" t="n"/>
+      <c r="D167" s="26" t="n"/>
+      <c r="E167" s="26" t="n"/>
+      <c r="F167" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="G167" s="28" t="n">
+        <v>585</v>
+      </c>
+      <c r="H167" s="26" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="14" t="n"/>
+      <c r="B168" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C168" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
+        </is>
+      </c>
+      <c r="D168" s="25" t="inlineStr"/>
+      <c r="E168" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F168" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G168" s="16" t="n">
+        <v>412</v>
+      </c>
+      <c r="H168" s="21" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="14" t="n"/>
+      <c r="B169" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C169" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
+        </is>
+      </c>
+      <c r="D169" s="25" t="inlineStr"/>
+      <c r="E169" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F169" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H169" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="14" t="n"/>
+      <c r="B170" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C170" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
+        </is>
+      </c>
+      <c r="D170" s="14" t="inlineStr">
+        <is>
+          <t>521-182.110</t>
+        </is>
+      </c>
+      <c r="E170" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F170" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G170" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H170" s="21" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="14" t="n"/>
+      <c r="B171" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C171" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
+        </is>
+      </c>
+      <c r="D171" s="14" t="inlineStr">
+        <is>
+          <t>521-182.110</t>
+        </is>
+      </c>
+      <c r="E171" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F171" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G171" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="H171" s="21" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="14" t="n"/>
+      <c r="B172" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C172" s="15" t="inlineStr">
+        <is>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
+        </is>
+      </c>
+      <c r="D172" s="14" t="inlineStr">
+        <is>
+          <t>521-03.022</t>
+        </is>
+      </c>
+      <c r="E172" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F172" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G172" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H172" s="21" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 12</t>
+        </is>
+      </c>
+      <c r="B173" s="27" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды, Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C173" s="26" t="n"/>
+      <c r="D173" s="26" t="n"/>
+      <c r="E173" s="26" t="n"/>
+      <c r="F173" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="G173" s="28" t="n">
+        <v>582</v>
+      </c>
+      <c r="H173" s="26" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="14" t="n"/>
+      <c r="B174" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C174" s="15" t="inlineStr">
+        <is>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду65 Ру6,3</t>
+        </is>
+      </c>
+      <c r="D174" s="14" t="inlineStr">
+        <is>
+          <t>521-03-022</t>
+        </is>
+      </c>
+      <c r="E174" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F174" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H174" s="21" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="14" t="n"/>
+      <c r="B175" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C175" s="15" t="inlineStr">
+        <is>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду70 Ру6,3</t>
+        </is>
+      </c>
+      <c r="D175" s="14" t="inlineStr">
+        <is>
+          <t>БЕЗ ЧЕРТЕЖА</t>
+        </is>
+      </c>
+      <c r="E175" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F175" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G175" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="H175" s="21" t="n">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="14" t="n"/>
+      <c r="B176" s="15" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C176" s="15" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
+        </is>
+      </c>
+      <c r="D176" s="14" t="inlineStr">
+        <is>
+          <t>521-182.116</t>
+        </is>
+      </c>
+      <c r="E176" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F176" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H176" s="21" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="14" t="n"/>
+      <c r="B177" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C177" s="15" t="inlineStr">
+        <is>
+          <t>Сетка на фильтр Ду20 маленькая</t>
+        </is>
+      </c>
+      <c r="D177" s="25" t="inlineStr"/>
+      <c r="E177" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F177" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="14" t="n"/>
+      <c r="B178" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C178" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду 50</t>
+        </is>
+      </c>
+      <c r="D178" s="25" t="inlineStr"/>
+      <c r="E178" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F178" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H178" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="14" t="n"/>
+      <c r="B179" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C179" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр заборной воды ДУ 80</t>
+        </is>
+      </c>
+      <c r="D179" s="25" t="inlineStr"/>
+      <c r="E179" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F179" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G179" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="H179" s="21" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="14" t="n"/>
+      <c r="B180" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C180" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду 100</t>
+        </is>
+      </c>
+      <c r="D180" s="25" t="inlineStr"/>
+      <c r="E180" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F180" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="H180" s="21" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="14" t="n"/>
+      <c r="B181" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C181" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
+        </is>
+      </c>
+      <c r="D181" s="14" t="inlineStr">
+        <is>
+          <t>427-03-109-2</t>
+        </is>
+      </c>
+      <c r="E181" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F181" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G181" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="H181" s="21" t="n">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="14" t="n"/>
+      <c r="B182" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C182" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр заборной воды ДУ 150</t>
+        </is>
+      </c>
+      <c r="D182" s="25" t="inlineStr"/>
+      <c r="E182" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="F182" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G182" s="16" t="n">
+        <v>192</v>
+      </c>
+      <c r="H182" s="21" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 13</t>
+        </is>
+      </c>
+      <c r="B183" s="27" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C183" s="26" t="n"/>
+      <c r="D183" s="26" t="n"/>
+      <c r="E183" s="26" t="n"/>
+      <c r="F183" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G183" s="28" t="n">
+        <v>572</v>
+      </c>
+      <c r="H183" s="26" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="14" t="n"/>
+      <c r="B184" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C184" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр заборной воды ДУ 150</t>
+        </is>
+      </c>
+      <c r="D184" s="25" t="inlineStr"/>
+      <c r="E184" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="F184" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G184" s="16" t="n">
+        <v>128</v>
+      </c>
+      <c r="H184" s="21" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="14" t="n"/>
+      <c r="B185" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C185" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду200</t>
+        </is>
+      </c>
+      <c r="D185" s="25" t="inlineStr"/>
+      <c r="E185" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="F185" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G185" s="16" t="n">
+        <v>444</v>
+      </c>
+      <c r="H185" s="21" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 14</t>
+        </is>
+      </c>
+      <c r="B186" s="27" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C186" s="26" t="n"/>
+      <c r="D186" s="26" t="n"/>
+      <c r="E186" s="26" t="n"/>
+      <c r="F186" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G186" s="28" t="n">
+        <v>592</v>
+      </c>
+      <c r="H186" s="26" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="14" t="n"/>
+      <c r="B187" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C187" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду200</t>
+        </is>
+      </c>
+      <c r="D187" s="25" t="inlineStr"/>
+      <c r="E187" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="F187" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G187" s="16" t="n">
+        <v>592</v>
+      </c>
+      <c r="H187" s="21" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 15</t>
+        </is>
+      </c>
+      <c r="B188" s="27" t="inlineStr">
+        <is>
+          <t>Головки вентиляционные, Кингстоны, Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C188" s="26" t="n"/>
+      <c r="D188" s="26" t="n"/>
+      <c r="E188" s="26" t="n"/>
+      <c r="F188" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="G188" s="28" t="n">
+        <v>515</v>
+      </c>
+      <c r="H188" s="26" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="14" t="n"/>
+      <c r="B189" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C189" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду200</t>
+        </is>
+      </c>
+      <c r="D189" s="25" t="inlineStr"/>
+      <c r="E189" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="F189" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="16" t="n">
+        <v>148</v>
+      </c>
+      <c r="H189" s="21" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="14" t="n"/>
+      <c r="B190" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C190" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду 300</t>
+        </is>
+      </c>
+      <c r="D190" s="25" t="inlineStr"/>
+      <c r="E190" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="F190" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="16" t="n">
+        <v>172</v>
+      </c>
+      <c r="H190" s="21" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="14" t="n"/>
+      <c r="B191" s="15" t="inlineStr">
+        <is>
+          <t>Кингстоны</t>
+        </is>
+      </c>
+      <c r="C191" s="15" t="inlineStr">
+        <is>
+          <t>Кингстон донный фланцевый Ду32Ру2,5</t>
+        </is>
+      </c>
+      <c r="D191" s="14" t="inlineStr">
+        <is>
+          <t>527-03.014</t>
+        </is>
+      </c>
+      <c r="E191" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F191" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="H191" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="14" t="n"/>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>Кингстоны</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr">
+        <is>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+        </is>
+      </c>
+      <c r="D192" s="14" t="inlineStr">
+        <is>
+          <t>527-03.054</t>
+        </is>
+      </c>
+      <c r="E192" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F192" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="H192" s="21" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="14" t="n"/>
+      <c r="B193" s="15" t="inlineStr">
+        <is>
+          <t>Кингстоны</t>
+        </is>
+      </c>
+      <c r="C193" s="15" t="inlineStr">
+        <is>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+        </is>
+      </c>
+      <c r="D193" s="14" t="inlineStr">
+        <is>
+          <t>без чертежа(527-35.1165)</t>
+        </is>
+      </c>
+      <c r="E193" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F193" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H193" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="14" t="n"/>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>Кингстоны</t>
+        </is>
+      </c>
+      <c r="C194" s="15" t="inlineStr">
+        <is>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+        </is>
+      </c>
+      <c r="D194" s="14" t="inlineStr">
+        <is>
+          <t>527-03.055</t>
+        </is>
+      </c>
+      <c r="E194" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F194" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G194" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="H194" s="21" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="14" t="n"/>
+      <c r="B195" s="15" t="inlineStr">
+        <is>
+          <t>Кингстоны</t>
+        </is>
+      </c>
+      <c r="C195" s="15" t="inlineStr">
+        <is>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+        </is>
+      </c>
+      <c r="D195" s="14" t="inlineStr">
+        <is>
+          <t>527-03.055</t>
+        </is>
+      </c>
+      <c r="E195" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F195" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="H195" s="21" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="14" t="n"/>
+      <c r="B196" s="15" t="inlineStr">
+        <is>
+          <t>Головки вентиляционные</t>
+        </is>
+      </c>
+      <c r="C196" s="15" t="inlineStr">
+        <is>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
+        </is>
+      </c>
+      <c r="D196" s="14" t="inlineStr">
+        <is>
+          <t>(541-03.232)</t>
+        </is>
+      </c>
+      <c r="E196" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F196" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G196" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H196" s="21" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="14" t="n"/>
+      <c r="B197" s="15" t="inlineStr">
+        <is>
+          <t>Головки вентиляционные</t>
+        </is>
+      </c>
+      <c r="C197" s="15" t="inlineStr">
+        <is>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
+        </is>
+      </c>
+      <c r="D197" s="14" t="inlineStr">
+        <is>
+          <t>541-03.224</t>
+        </is>
+      </c>
+      <c r="E197" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F197" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G197" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H197" s="21" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="14" t="n"/>
+      <c r="B198" s="15" t="inlineStr">
+        <is>
+          <t>Головки вентиляционные</t>
+        </is>
+      </c>
+      <c r="C198" s="15" t="inlineStr">
+        <is>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
+        </is>
+      </c>
+      <c r="D198" s="14" t="inlineStr">
+        <is>
+          <t>(541-03.218)</t>
+        </is>
+      </c>
+      <c r="E198" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F198" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G198" s="16" t="n">
+        <v>78</v>
+      </c>
+      <c r="H198" s="21" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 16</t>
+        </is>
+      </c>
+      <c r="B199" s="27" t="inlineStr">
+        <is>
+          <t>Головки вентиляционные, Захлопки, Колонка смотровая, Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C199" s="26" t="n"/>
+      <c r="D199" s="26" t="n"/>
+      <c r="E199" s="26" t="n"/>
+      <c r="F199" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="G199" s="28" t="n">
+        <v>573</v>
+      </c>
+      <c r="H199" s="26" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="14" t="n"/>
+      <c r="B200" s="15" t="inlineStr">
+        <is>
+          <t>Головки вентиляционные</t>
+        </is>
+      </c>
+      <c r="C200" s="15" t="inlineStr">
+        <is>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
+        </is>
+      </c>
+      <c r="D200" s="14" t="inlineStr">
+        <is>
+          <t>(541-03.218)</t>
+        </is>
+      </c>
+      <c r="E200" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F200" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G200" s="16" t="n">
+        <v>134</v>
+      </c>
+      <c r="H200" s="21" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="14" t="n"/>
+      <c r="B201" s="15" t="inlineStr">
+        <is>
+          <t>Колонка смотровая</t>
+        </is>
+      </c>
+      <c r="C201" s="15" t="inlineStr">
+        <is>
+          <t>Клапан для колонки указательной Ду10 Ру16</t>
+        </is>
+      </c>
+      <c r="D201" s="14" t="inlineStr">
+        <is>
+          <t>598-03.022-06</t>
+        </is>
+      </c>
+      <c r="E201" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F201" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G201" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H201" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="14" t="n"/>
+      <c r="B202" s="15" t="inlineStr">
+        <is>
+          <t>Захлопки</t>
+        </is>
+      </c>
+      <c r="C202" s="15" t="inlineStr">
+        <is>
+          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
+        </is>
+      </c>
+      <c r="D202" s="14" t="inlineStr">
+        <is>
+          <t>529-35.1400-01</t>
+        </is>
+      </c>
+      <c r="E202" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F202" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H202" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="14" t="n"/>
+      <c r="B203" s="15" t="inlineStr">
+        <is>
+          <t>Захлопки</t>
+        </is>
+      </c>
+      <c r="C203" s="15" t="inlineStr">
+        <is>
+          <t>Захлопка фланцевая горизонтальная Ду50</t>
+        </is>
+      </c>
+      <c r="D203" s="14" t="inlineStr">
+        <is>
+          <t>529-03.011</t>
+        </is>
+      </c>
+      <c r="E203" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F203" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="H203" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="14" t="n"/>
+      <c r="B204" s="15" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C204" s="15" t="inlineStr">
+        <is>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+        </is>
+      </c>
+      <c r="D204" s="25" t="inlineStr"/>
+      <c r="E204" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F204" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H204" s="21" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="14" t="n"/>
+      <c r="B205" s="15" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C205" s="15" t="inlineStr">
+        <is>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
+        </is>
+      </c>
+      <c r="D205" s="25" t="inlineStr"/>
+      <c r="E205" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F205" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G205" s="16" t="n">
+        <v>205</v>
+      </c>
+      <c r="H205" s="21" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="14" t="n"/>
+      <c r="B206" s="15" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C206" s="15" t="inlineStr">
+        <is>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+        </is>
+      </c>
+      <c r="D206" s="25" t="inlineStr"/>
+      <c r="E206" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F206" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G206" s="16" t="n">
+        <v>143</v>
+      </c>
+      <c r="H206" s="21" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 17</t>
+        </is>
+      </c>
+      <c r="B207" s="27" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C207" s="26" t="n"/>
+      <c r="D207" s="26" t="n"/>
+      <c r="E207" s="26" t="n"/>
+      <c r="F207" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="G207" s="28" t="n">
+        <v>571</v>
+      </c>
+      <c r="H207" s="26" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="14" t="n"/>
+      <c r="B208" s="15" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C208" s="15" t="inlineStr">
+        <is>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+        </is>
+      </c>
+      <c r="D208" s="25" t="inlineStr"/>
+      <c r="E208" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F208" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G208" s="16" t="n">
+        <v>571</v>
+      </c>
+      <c r="H208" s="21" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 18</t>
+        </is>
+      </c>
+      <c r="B209" s="27" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C209" s="26" t="n"/>
+      <c r="D209" s="26" t="n"/>
+      <c r="E209" s="26" t="n"/>
+      <c r="F209" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G209" s="28" t="n">
+        <v>544</v>
+      </c>
+      <c r="H209" s="26" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="14" t="n"/>
+      <c r="B210" s="15" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C210" s="15" t="inlineStr">
+        <is>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
+        </is>
+      </c>
+      <c r="D210" s="25" t="inlineStr"/>
+      <c r="E210" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F210" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G210" s="16" t="n">
+        <v>544</v>
+      </c>
+      <c r="H210" s="21" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 19</t>
+        </is>
+      </c>
+      <c r="B211" s="27" t="inlineStr">
+        <is>
+          <t>Коробки клапанные, Краны, Пусковые клапаны, Редукционные клапаны, Стаканы переборочные</t>
+        </is>
+      </c>
+      <c r="C211" s="26" t="n"/>
+      <c r="D211" s="26" t="n"/>
+      <c r="E211" s="26" t="n"/>
+      <c r="F211" s="26" t="n">
+        <v>112</v>
+      </c>
+      <c r="G211" s="28" t="n">
+        <v>588</v>
+      </c>
+      <c r="H211" s="26" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="14" t="n"/>
+      <c r="B212" s="15" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C212" s="15" t="inlineStr">
+        <is>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
+        </is>
+      </c>
+      <c r="D212" s="25" t="inlineStr"/>
+      <c r="E212" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F212" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G212" s="16" t="n">
+        <v>272</v>
+      </c>
+      <c r="H212" s="21" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="14" t="n"/>
+      <c r="B213" s="15" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C213" s="15" t="inlineStr">
+        <is>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
+        </is>
+      </c>
+      <c r="D213" s="25" t="inlineStr"/>
+      <c r="E213" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F213" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G213" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H213" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="14" t="n"/>
+      <c r="B214" s="15" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C214" s="15" t="inlineStr">
+        <is>
+          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
+        </is>
+      </c>
+      <c r="D214" s="14" t="inlineStr">
+        <is>
+          <t>536-3М5</t>
+        </is>
+      </c>
+      <c r="E214" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F214" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G214" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H214" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="14" t="n"/>
+      <c r="B215" s="15" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C215" s="15" t="inlineStr">
+        <is>
+          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
+        </is>
+      </c>
+      <c r="D215" s="14" t="inlineStr">
+        <is>
+          <t>536-35.695</t>
+        </is>
+      </c>
+      <c r="E215" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F215" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G215" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H215" s="21" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="14" t="n"/>
+      <c r="B216" s="15" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C216" s="15" t="inlineStr">
+        <is>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
+        </is>
+      </c>
+      <c r="D216" s="14" t="inlineStr">
+        <is>
+          <t>528-3М129</t>
+        </is>
+      </c>
+      <c r="E216" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F216" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G216" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="H216" s="21" t="n">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="14" t="n"/>
+      <c r="B217" s="15" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C217" s="15" t="inlineStr">
+        <is>
+          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
+        </is>
+      </c>
+      <c r="D217" s="14" t="inlineStr">
+        <is>
+          <t>536-3М.72</t>
+        </is>
+      </c>
+      <c r="E217" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F217" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H217" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="14" t="n"/>
+      <c r="B218" s="15" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C218" s="15" t="inlineStr">
+        <is>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+        </is>
+      </c>
+      <c r="D218" s="14" t="inlineStr">
+        <is>
+          <t>536-35.696</t>
+        </is>
+      </c>
+      <c r="E218" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F218" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G218" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H218" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="14" t="n"/>
+      <c r="B219" s="15" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C219" s="15" t="inlineStr">
+        <is>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+        </is>
+      </c>
+      <c r="D219" s="14" t="inlineStr">
+        <is>
+          <t>536-35.696</t>
+        </is>
+      </c>
+      <c r="E219" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F219" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H219" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="14" t="n"/>
+      <c r="B220" s="15" t="inlineStr">
+        <is>
+          <t>Стаканы переборочные</t>
+        </is>
+      </c>
+      <c r="C220" s="15" t="inlineStr">
+        <is>
+          <t>Стакан переборочный Ду10Ру100</t>
+        </is>
+      </c>
+      <c r="D220" s="14" t="inlineStr">
+        <is>
+          <t>554-35.265</t>
+        </is>
+      </c>
+      <c r="E220" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F220" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G220" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H220" s="21" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="14" t="n"/>
+      <c r="B221" s="15" t="inlineStr">
+        <is>
+          <t>Стаканы переборочные</t>
+        </is>
+      </c>
+      <c r="C221" s="15" t="inlineStr">
+        <is>
+          <t>Стакан переборочный Ду20Ру100</t>
+        </is>
+      </c>
+      <c r="D221" s="14" t="inlineStr">
+        <is>
+          <t>554-03.909-03</t>
+        </is>
+      </c>
+      <c r="E221" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F221" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G221" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H221" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="14" t="n"/>
+      <c r="B222" s="15" t="inlineStr">
+        <is>
+          <t>Стаканы переборочные</t>
+        </is>
+      </c>
+      <c r="C222" s="15" t="inlineStr">
+        <is>
+          <t>Стакан переборочный Ду20Ру100</t>
+        </is>
+      </c>
+      <c r="D222" s="14" t="inlineStr">
+        <is>
+          <t>554-03.905-06</t>
+        </is>
+      </c>
+      <c r="E222" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F222" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G222" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="H222" s="21" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="14" t="n"/>
+      <c r="B223" s="15" t="inlineStr">
+        <is>
+          <t>Стаканы переборочные</t>
+        </is>
+      </c>
+      <c r="C223" s="15" t="inlineStr">
+        <is>
+          <t>Стакан переборочный Ду25Ру100</t>
+        </is>
+      </c>
+      <c r="D223" s="14" t="inlineStr">
+        <is>
+          <t>554-35.156</t>
+        </is>
+      </c>
+      <c r="E223" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F223" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H223" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="14" t="n"/>
+      <c r="B224" s="15" t="inlineStr">
+        <is>
+          <t>Пусковые клапаны</t>
+        </is>
+      </c>
+      <c r="C224" s="15" t="inlineStr">
+        <is>
+          <t>Клапан пусковой Ду20Ру125</t>
+        </is>
+      </c>
+      <c r="D224" s="14" t="inlineStr">
+        <is>
+          <t>587-03.080</t>
+        </is>
+      </c>
+      <c r="E224" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F224" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G224" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="H224" s="21" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="14" t="n"/>
+      <c r="B225" s="15" t="inlineStr">
+        <is>
+          <t>Пусковые клапаны</t>
+        </is>
+      </c>
+      <c r="C225" s="15" t="inlineStr">
+        <is>
+          <t>Клапан пусковой Ду32Ру125</t>
+        </is>
+      </c>
+      <c r="D225" s="14" t="inlineStr">
+        <is>
+          <t>587-03.082</t>
+        </is>
+      </c>
+      <c r="E225" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F225" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G225" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="H225" s="21" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="14" t="n"/>
+      <c r="B226" s="15" t="inlineStr">
+        <is>
+          <t>Редукционные клапаны</t>
+        </is>
+      </c>
+      <c r="C226" s="15" t="inlineStr">
+        <is>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+        </is>
+      </c>
+      <c r="D226" s="14" t="inlineStr">
+        <is>
+          <t>525-35.2634</t>
+        </is>
+      </c>
+      <c r="E226" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F226" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H226" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="14" t="n"/>
+      <c r="B227" s="15" t="inlineStr">
+        <is>
+          <t>Редукционные клапаны</t>
+        </is>
+      </c>
+      <c r="C227" s="15" t="inlineStr">
+        <is>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+        </is>
+      </c>
+      <c r="D227" s="14" t="inlineStr">
+        <is>
+          <t>525-35.2634-04</t>
+        </is>
+      </c>
+      <c r="E227" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F227" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H227" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="14" t="n"/>
+      <c r="B228" s="15" t="inlineStr">
+        <is>
+          <t>Редукционные клапаны</t>
+        </is>
+      </c>
+      <c r="C228" s="15" t="inlineStr">
+        <is>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+        </is>
+      </c>
+      <c r="D228" s="14" t="inlineStr">
+        <is>
+          <t>525-03.044</t>
+        </is>
+      </c>
+      <c r="E228" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F228" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="H228" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 20</t>
+        </is>
+      </c>
+      <c r="B229" s="27" t="inlineStr">
+        <is>
+          <t>Паровые клапаны, Педальные клапаны, Редукционные клапаны, Электромагнитные клапаны</t>
+        </is>
+      </c>
+      <c r="C229" s="26" t="n"/>
+      <c r="D229" s="26" t="n"/>
+      <c r="E229" s="26" t="n"/>
+      <c r="F229" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="G229" s="28" t="n">
+        <v>597</v>
+      </c>
+      <c r="H229" s="26" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="14" t="n"/>
+      <c r="B230" s="15" t="inlineStr">
+        <is>
+          <t>Редукционные клапаны</t>
+        </is>
+      </c>
+      <c r="C230" s="15" t="inlineStr">
+        <is>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+        </is>
+      </c>
+      <c r="D230" s="14" t="inlineStr">
+        <is>
+          <t>525-03.044</t>
+        </is>
+      </c>
+      <c r="E230" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F230" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G230" s="16" t="n">
+        <v>216</v>
+      </c>
+      <c r="H230" s="21" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="14" t="n"/>
+      <c r="B231" s="15" t="inlineStr">
+        <is>
+          <t>Паровые клапаны</t>
+        </is>
+      </c>
+      <c r="C231" s="15" t="inlineStr">
+        <is>
+          <t>Клапан паровой Ду65Ру10</t>
+        </is>
+      </c>
+      <c r="D231" s="14" t="inlineStr">
+        <is>
+          <t>581-03.034</t>
+        </is>
+      </c>
+      <c r="E231" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F231" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="H231" s="21" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="14" t="n"/>
+      <c r="B232" s="15" t="inlineStr">
+        <is>
+          <t>Электромагнитные клапаны</t>
+        </is>
+      </c>
+      <c r="C232" s="15" t="inlineStr">
+        <is>
+          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
+        </is>
+      </c>
+      <c r="D232" s="14" t="inlineStr">
+        <is>
+          <t>587-35.8490-04</t>
+        </is>
+      </c>
+      <c r="E232" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F232" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H232" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="14" t="n"/>
+      <c r="B233" s="15" t="inlineStr">
+        <is>
+          <t>Электромагнитные клапаны</t>
+        </is>
+      </c>
+      <c r="C233" s="15" t="inlineStr">
+        <is>
+          <t>Клапан с электромагнитным ручным управлением</t>
+        </is>
+      </c>
+      <c r="D233" s="14" t="inlineStr">
+        <is>
+          <t>587-182.126</t>
+        </is>
+      </c>
+      <c r="E233" s="14" t="n"/>
+      <c r="F233" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H233" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="14" t="n"/>
+      <c r="B234" s="15" t="inlineStr">
+        <is>
+          <t>Педальные клапаны</t>
+        </is>
+      </c>
+      <c r="C234" s="15" t="inlineStr">
+        <is>
+          <t>Клапан педальный Ду25</t>
+        </is>
+      </c>
+      <c r="D234" s="14" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
+      <c r="E234" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F234" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H234" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="14" t="n"/>
+      <c r="B235" s="15" t="inlineStr">
+        <is>
+          <t>Педальные клапаны</t>
+        </is>
+      </c>
+      <c r="C235" s="15" t="inlineStr">
+        <is>
+          <t>Клапан педальный Ду25 новый приход</t>
+        </is>
+      </c>
+      <c r="D235" s="14" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
+      <c r="E235" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F235" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="G235" s="16" t="n">
+        <v>319</v>
+      </c>
+      <c r="H235" s="21" t="n">
+        <v>0.174</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 21</t>
+        </is>
+      </c>
+      <c r="B236" s="27" t="inlineStr">
+        <is>
+          <t>Без описания — уточнить, Педальные клапаны, Эжекторы</t>
+        </is>
+      </c>
+      <c r="C236" s="26" t="n"/>
+      <c r="D236" s="26" t="n"/>
+      <c r="E236" s="26" t="n"/>
+      <c r="F236" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="G236" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="H236" s="26" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="14" t="n"/>
+      <c r="B237" s="15" t="inlineStr">
+        <is>
+          <t>Педальные клапаны</t>
+        </is>
+      </c>
+      <c r="C237" s="15" t="inlineStr">
+        <is>
+          <t>Клапан педальный Ду25 новый приход</t>
+        </is>
+      </c>
+      <c r="D237" s="14" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
+      <c r="E237" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F237" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G237" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="H237" s="21" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="14" t="n"/>
+      <c r="B238" s="15" t="inlineStr">
+        <is>
+          <t>Эжекторы</t>
+        </is>
+      </c>
+      <c r="C238" s="15" t="inlineStr">
+        <is>
+          <t>Эжектор ВЭЖ 6,3</t>
+        </is>
+      </c>
+      <c r="D238" s="25" t="inlineStr"/>
+      <c r="E238" s="14" t="n"/>
+      <c r="F238" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H238" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="14" t="n"/>
+      <c r="B239" s="15" t="inlineStr">
+        <is>
+          <t>Без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="C239" s="15" t="inlineStr">
+        <is>
+          <t>Клапан Ду20/10</t>
+        </is>
+      </c>
+      <c r="D239" s="14" t="inlineStr">
+        <is>
+          <t>581-С6.73</t>
+        </is>
+      </c>
+      <c r="E239" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F239" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G239" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H239" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="14" t="n"/>
+      <c r="B240" s="15" t="inlineStr">
+        <is>
+          <t>Без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="C240" s="15" t="inlineStr">
+        <is>
+          <t>Кланан Рр18-2 45/25</t>
+        </is>
+      </c>
+      <c r="D240" s="14" t="inlineStr">
+        <is>
+          <t>2619802505</t>
+        </is>
+      </c>
+      <c r="E240" s="14" t="n"/>
+      <c r="F240" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H240" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>Что учесть по таре</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="30" customHeight="1">
+      <c r="A243" s="17" t="inlineStr">
+        <is>
+          <t>— Ящик из бэушной доски на 600 кг держит только при брусе 50х50 по четырем углам и по верху. Без него стенка сложится при первом же ударе на маневрировании.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="30" customHeight="1">
+      <c r="A244" s="17" t="inlineStr">
+        <is>
+          <t>— Дно ящика набиваем доской вплотную, без щелей шире ладони: мелкий клапан проваливается и бьет соседей.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="30" customHeight="1">
+      <c r="A245" s="17" t="inlineStr">
+        <is>
+          <t>— На каждый ящик — бирка: номер, группа, вес, строки реестра и стрелки «верх». Принимать груз будут по упаковочному листу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="30" customHeight="1">
+      <c r="A246" s="17" t="inlineStr">
+        <is>
+          <t>— Задвижки и крупные фланцевые клапаны в ящики не кладем: они встают прямо на настил, с прокладкой доской между рядами и креплением к рымам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="30" customHeight="1">
+      <c r="A247" s="17" t="inlineStr">
+        <is>
+          <t>— Фильтры идут верхним ярусом на ящиках, поэтому ящики под ними должны быть самыми крепкими — туда ставим те, что с брусом.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/outputs/marine_equipment/Контейнер_22т_Питер.xlsx
+++ b/outputs/marine_equipment/Контейнер_22т_Питер.xlsx
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Задвижки и клинкеты Ду200, 250, 300, 350</t>
+          <t>Клинкеты Ду200, 250, 300, 350 — один слой</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Необрезная доска 25 мм поперек, на всю ширину, шаг 300-400 мм</t>
+          <t>Необрезная доска 25 мм сплошным настилом поверх слоя</t>
         </is>
       </c>
       <c r="D39" s="16" t="n">
@@ -1292,12 +1292,12 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Остальные клинкеты, задвижки и арматура Ду100-150</t>
+          <t>Клапанные коробки и тяжелая арматура от Ду100</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -1306,27 +1306,27 @@
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>3626</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Ящики с мелкой арматурой до Ду80</t>
+          <t>Ящики с мелкой арматурой, включая клинкеты до Ду150</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Сплошной настил доской по верху ящиков, под верхний ярус</t>
+          <t>Два яруса ящиков высотой не больше 0,91 м каждый</t>
         </is>
       </c>
       <c r="D41" s="16" t="n">
-        <v>9636</v>
+        <v>9796</v>
       </c>
     </row>
     <row r="42">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N6" s="15" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N7" s="15" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N8" s="15" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N9" s="15" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N10" s="15" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N11" s="15" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N12" s="15" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="M13" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N13" s="15" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N14" s="15" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="M15" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N15" s="15" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N16" s="15" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="M17" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N17" s="15" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N18" s="15" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="M19" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N19" s="15" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N20" s="15" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N21" s="15" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N22" s="15" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="M23" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N23" s="15" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N24" s="15" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="M25" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N25" s="15" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N26" s="15" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="M27" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N27" s="15" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N28" s="15" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N29" s="15" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N30" s="15" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="M31" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N31" s="15" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N32" s="15" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N33" s="15" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N34" s="15" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N35" s="15" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N36" s="15" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="M37" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N37" s="15" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N38" s="15" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="M39" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N39" s="15" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N40" s="15" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="M41" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N41" s="15" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N42" s="15" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N43" s="15" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N44" s="15" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="M45" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N45" s="15" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N46" s="15" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="M47" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N47" s="15" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N48" s="15" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N50" s="15" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="M51" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N51" s="15" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N52" s="15" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="M53" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N53" s="15" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N54" s="15" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="M55" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N55" s="15" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N56" s="15" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="M57" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N57" s="15" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N58" s="15" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="M59" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N59" s="15" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N60" s="15" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="M61" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N61" s="15" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N62" s="15" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="M63" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N63" s="15" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N64" s="15" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="M65" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N65" s="15" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N66" s="15" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M67" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N67" s="15" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N68" s="15" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="M69" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N69" s="15" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N70" s="15" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="M71" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N71" s="15" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N72" s="15" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="M73" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N73" s="15" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N74" s="15" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="M75" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N75" s="15" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N76" s="15" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="M77" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N77" s="15" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N78" s="15" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="M79" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N79" s="15" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N80" s="15" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="M81" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N81" s="15" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N82" s="15" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="M83" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N83" s="15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N84" s="15" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M85" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N85" s="15" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N86" s="15" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="M87" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N87" s="15" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N88" s="15" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="M89" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N89" s="15" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N90" s="15" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="M91" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N91" s="15" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N92" s="15" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="M93" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N93" s="15" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N94" s="15" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="M95" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N95" s="15" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N96" s="15" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="M97" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N97" s="15" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N98" s="15" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="M99" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N99" s="15" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N100" s="15" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="M101" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N101" s="15" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N102" s="15" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="M103" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N103" s="15" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="M105" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N105" s="15" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N106" s="15" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="M107" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N107" s="15" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N108" s="15" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="M109" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N109" s="15" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N110" s="15" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="M111" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N111" s="15" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N112" s="15" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="M113" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N113" s="15" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N114" s="15" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="M115" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N115" s="15" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N116" s="15" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N118" s="15" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="M119" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N119" s="15" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N120" s="15" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="M121" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N121" s="15" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N122" s="15" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="M123" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N123" s="15" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N124" s="15" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M125" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N125" s="15" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N126" s="15" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="M127" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N127" s="15" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N128" s="15" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M129" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N129" s="15" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N130" s="15" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N131" s="15" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="M132" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N132" s="15" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="M133" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N133" s="15" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N134" s="15" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="M135" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N135" s="15" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N136" s="15" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="M137" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N137" s="15" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M138" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N138" s="15" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="M139" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N139" s="15" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="M140" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N140" s="15" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="M141" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N141" s="15" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="M143" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N143" s="15" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="M144" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N144" s="15" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="M145" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N145" s="15" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="M146" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N146" s="15" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="M147" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N147" s="15" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="M148" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N148" s="15" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="M149" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N149" s="15" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="M150" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N150" s="15" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="M151" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N151" s="15" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="M152" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N152" s="15" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="M155" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N155" s="15" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M156" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N156" s="15" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="M157" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N157" s="15" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="M159" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N159" s="15" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="M160" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N160" s="15" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="M161" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N161" s="15" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="M162" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N162" s="15" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="M164" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N164" s="15" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="M165" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N165" s="15" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="M166" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N166" s="15" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="M167" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N167" s="15" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="M168" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N168" s="15" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="M169" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N169" s="15" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="M170" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N170" s="15" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N171" s="15" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="M172" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N172" s="15" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="M173" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N173" s="15" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="M174" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N174" s="15" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="M175" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N175" s="15" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="M176" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N176" s="15" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="M191" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N191" s="15" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="M192" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N192" s="15" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="M193" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N193" s="15" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="M194" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N194" s="15" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="M195" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N195" s="15" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="M197" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N197" s="15" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="M198" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N198" s="15" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="M199" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N199" s="15" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="M200" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N200" s="15" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="M201" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N201" s="15" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="M202" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N202" s="15" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="M203" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N203" s="15" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="M205" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N205" s="15" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="M207" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N207" s="15" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="M208" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N208" s="15" t="inlineStr">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="M209" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N209" s="15" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="M210" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N210" s="15" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="M211" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N211" s="15" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="M212" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N212" s="15" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="M214" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N214" s="15" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="M215" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N215" s="15" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="M216" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N216" s="15" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="M217" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N217" s="15" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="M218" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N218" s="15" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="M220" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N220" s="15" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="M221" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N221" s="15" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="M222" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N222" s="15" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="M223" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N223" s="15" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="M224" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N224" s="15" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="M225" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N225" s="15" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="M226" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N226" s="15" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="M228" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N228" s="15" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="M229" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N229" s="15" t="inlineStr">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="M230" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N230" s="15" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="M231" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N231" s="15" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="M233" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N233" s="15" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M234" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N234" s="15" t="inlineStr">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="M236" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N236" s="15" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="M237" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N237" s="15" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="M238" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N238" s="15" t="inlineStr">
@@ -15732,7 +15732,7 @@
       </c>
       <c r="M240" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N240" s="15" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="M242" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N242" s="15" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="M243" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N243" s="15" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="M245" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N245" s="15" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="M246" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N246" s="15" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="M248" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N248" s="15" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="M250" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N250" s="15" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="M251" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N251" s="15" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N6" s="15" t="inlineStr">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N7" s="15" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N8" s="15" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N9" s="15" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N10" s="15" t="inlineStr">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N12" s="15" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="M13" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N13" s="15" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N14" s="15" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="M15" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N15" s="15" t="inlineStr">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N16" s="15" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="M17" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N17" s="15" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N18" s="15" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="M19" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N19" s="15" t="inlineStr">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N20" s="15" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N21" s="15" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N22" s="15" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="M23" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N23" s="15" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N24" s="15" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M25" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N25" s="15" t="inlineStr">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="M27" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N27" s="15" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N28" s="15" t="inlineStr">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N29" s="15" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="M31" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N31" s="15" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N32" s="15" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N33" s="15" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N34" s="15" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N35" s="15" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N36" s="15" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="M37" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N37" s="15" t="inlineStr">
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N38" s="15" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="M39" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N39" s="15" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N40" s="15" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="M41" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N41" s="15" t="inlineStr">
@@ -18559,7 +18559,7 @@
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N42" s="15" t="inlineStr">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N43" s="15" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N44" s="15" t="inlineStr">
@@ -18751,7 +18751,7 @@
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N46" s="15" t="inlineStr">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="M47" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N47" s="15" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N48" s="15" t="inlineStr">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N50" s="15" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="M51" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N51" s="15" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="M55" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N55" s="15" t="inlineStr">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N56" s="15" t="inlineStr">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="M61" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N61" s="15" t="inlineStr">
@@ -19584,7 +19584,7 @@
       </c>
       <c r="M63" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N63" s="15" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N64" s="15" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="M65" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N65" s="15" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N66" s="15" t="inlineStr">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="M67" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N67" s="15" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N68" s="15" t="inlineStr">
@@ -19941,7 +19941,7 @@
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N70" s="15" t="inlineStr">
@@ -19994,7 +19994,7 @@
       </c>
       <c r="M71" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N71" s="15" t="inlineStr">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="M73" s="14" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N73" s="15" t="inlineStr">
@@ -20131,7 +20131,7 @@
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N74" s="15" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="M75" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N75" s="15" t="inlineStr">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N76" s="15" t="inlineStr">
@@ -20290,7 +20290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H247"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>21 шт</t>
+          <t>23 шт</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -20342,12 +20342,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>11.7 т</t>
+          <t>11.8 т</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>193 позиций, 2387 штук</t>
+          <t>202 позиций, 2496 штук</t>
         </is>
       </c>
     </row>
@@ -20359,12 +20359,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10.0 т</t>
+          <t>9.9 т</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33 позиций — задвижки и крупные клапаны, в ящики не кладем</t>
+          <t>24 позиций — задвижки и крупные клапаны, в ящики не кладем</t>
         </is>
       </c>
     </row>
@@ -20376,7 +20376,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>21 шт</t>
+          <t>23 шт</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -25173,20 +25173,20 @@
       </c>
       <c r="B173" s="27" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды, Фланцевая проходная</t>
+          <t>Клинкеты, Фланцевая проходная</t>
         </is>
       </c>
       <c r="C173" s="26" t="n"/>
       <c r="D173" s="26" t="n"/>
       <c r="E173" s="26" t="n"/>
       <c r="F173" s="26" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G173" s="28" t="n">
-        <v>582</v>
+        <v>389</v>
       </c>
       <c r="H173" s="26" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="174">
@@ -25283,236 +25283,232 @@
       <c r="A177" s="14" t="n"/>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C177" s="15" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду20 маленькая</t>
+          <t>Задвижка клинкетная Ду 50, без клиньев</t>
         </is>
       </c>
       <c r="D177" s="25" t="inlineStr"/>
       <c r="E177" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F177" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G177" s="16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H177" s="21" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="14" t="n"/>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 50</t>
+          <t>Задвижка клинкетная Ду60</t>
         </is>
       </c>
       <c r="D178" s="25" t="inlineStr"/>
       <c r="E178" s="14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F178" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G178" s="16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H178" s="21" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="14" t="n"/>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C179" s="15" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 80</t>
+          <t>Задвижка клинкетная Ду60</t>
         </is>
       </c>
       <c r="D179" s="25" t="inlineStr"/>
       <c r="E179" s="14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F179" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G179" s="16" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H179" s="21" t="n">
-        <v>0.15</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="14" t="n"/>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 100</t>
+          <t>Задвижка клинкетная Ду65</t>
         </is>
       </c>
       <c r="D180" s="25" t="inlineStr"/>
       <c r="E180" s="14" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="F180" s="14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G180" s="16" t="n">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="H180" s="21" t="n">
-        <v>0.045</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="14" t="n"/>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C181" s="15" t="inlineStr">
         <is>
-          <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
-        </is>
-      </c>
-      <c r="D181" s="14" t="inlineStr">
-        <is>
-          <t>427-03-109-2</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
+        </is>
+      </c>
+      <c r="D181" s="25" t="inlineStr"/>
       <c r="E181" s="14" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F181" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G181" s="16" t="n">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="H181" s="21" t="n">
-        <v>0.135</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="14" t="n"/>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 150</t>
+          <t>Задвижка клинкетная ДУ 80, сталь</t>
         </is>
       </c>
       <c r="D182" s="25" t="inlineStr"/>
       <c r="E182" s="14" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="F182" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G182" s="16" t="n">
-        <v>192</v>
+        <v>12</v>
       </c>
       <c r="H182" s="21" t="n">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="26" t="inlineStr">
+      <c r="A183" s="14" t="n"/>
+      <c r="B183" s="15" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C183" s="15" t="inlineStr">
+        <is>
+          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
+        </is>
+      </c>
+      <c r="D183" s="25" t="inlineStr"/>
+      <c r="E183" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F183" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G183" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="H183" s="21" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="26" t="inlineStr">
         <is>
           <t>ЯЩИК 13</t>
         </is>
       </c>
-      <c r="B183" s="27" t="inlineStr">
-        <is>
-          <t>Фильтры забортной воды</t>
-        </is>
-      </c>
-      <c r="C183" s="26" t="n"/>
-      <c r="D183" s="26" t="n"/>
-      <c r="E183" s="26" t="n"/>
-      <c r="F183" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G183" s="28" t="n">
-        <v>572</v>
-      </c>
-      <c r="H183" s="26" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="14" t="n"/>
-      <c r="B184" s="15" t="inlineStr">
-        <is>
-          <t>Фильтры забортной воды</t>
-        </is>
-      </c>
-      <c r="C184" s="15" t="inlineStr">
-        <is>
-          <t>Фильтр заборной воды ДУ 150</t>
-        </is>
-      </c>
-      <c r="D184" s="25" t="inlineStr"/>
-      <c r="E184" s="14" t="n">
-        <v>150</v>
-      </c>
-      <c r="F184" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G184" s="16" t="n">
-        <v>128</v>
-      </c>
-      <c r="H184" s="21" t="n">
-        <v>0.2</v>
+      <c r="B184" s="27" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C184" s="26" t="n"/>
+      <c r="D184" s="26" t="n"/>
+      <c r="E184" s="26" t="n"/>
+      <c r="F184" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="G184" s="28" t="n">
+        <v>352</v>
+      </c>
+      <c r="H184" s="26" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="14" t="n"/>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C185" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду200</t>
+          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
         </is>
       </c>
       <c r="D185" s="25" t="inlineStr"/>
       <c r="E185" s="14" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F185" s="14" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G185" s="16" t="n">
-        <v>444</v>
+        <v>352</v>
       </c>
       <c r="H185" s="21" t="n">
-        <v>0.48</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="186">
@@ -25523,263 +25519,243 @@
       </c>
       <c r="B186" s="27" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C186" s="26" t="n"/>
       <c r="D186" s="26" t="n"/>
       <c r="E186" s="26" t="n"/>
       <c r="F186" s="26" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G186" s="28" t="n">
-        <v>592</v>
+        <v>336</v>
       </c>
       <c r="H186" s="26" t="n">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="14" t="n"/>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C187" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду200</t>
+          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
         </is>
       </c>
       <c r="D187" s="25" t="inlineStr"/>
       <c r="E187" s="14" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F187" s="14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G187" s="16" t="n">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="H187" s="21" t="n">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="26" t="inlineStr">
-        <is>
-          <t>ЯЩИК 15</t>
-        </is>
-      </c>
-      <c r="B188" s="27" t="inlineStr">
-        <is>
-          <t>Головки вентиляционные, Кингстоны, Фильтры забортной воды</t>
-        </is>
-      </c>
-      <c r="C188" s="26" t="n"/>
-      <c r="D188" s="26" t="n"/>
-      <c r="E188" s="26" t="n"/>
-      <c r="F188" s="26" t="n">
-        <v>27</v>
-      </c>
-      <c r="G188" s="28" t="n">
-        <v>515</v>
-      </c>
-      <c r="H188" s="26" t="n">
-        <v>0.89</v>
+      <c r="A188" s="14" t="n"/>
+      <c r="B188" s="15" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C188" s="15" t="inlineStr">
+        <is>
+          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
+        </is>
+      </c>
+      <c r="D188" s="25" t="inlineStr"/>
+      <c r="E188" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F188" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G188" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="H188" s="21" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="14" t="n"/>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C189" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду200</t>
+          <t>Задвижка клинкетная фланцевая Ду80 Ру6</t>
         </is>
       </c>
       <c r="D189" s="25" t="inlineStr"/>
       <c r="E189" s="14" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F189" s="14" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G189" s="16" t="n">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="H189" s="21" t="n">
-        <v>0.16</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="n"/>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 300</t>
+          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
         </is>
       </c>
       <c r="D190" s="25" t="inlineStr"/>
       <c r="E190" s="14" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F190" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G190" s="16" t="n">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="H190" s="21" t="n">
-        <v>0.35</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="14" t="n"/>
-      <c r="B191" s="15" t="inlineStr">
-        <is>
-          <t>Кингстоны</t>
-        </is>
-      </c>
-      <c r="C191" s="15" t="inlineStr">
-        <is>
-          <t>Кингстон донный фланцевый Ду32Ру2,5</t>
-        </is>
-      </c>
-      <c r="D191" s="14" t="inlineStr">
-        <is>
-          <t>527-03.014</t>
-        </is>
-      </c>
-      <c r="E191" s="14" t="n">
-        <v>32</v>
-      </c>
-      <c r="F191" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G191" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="H191" s="21" t="n">
-        <v>0.005</v>
+      <c r="A191" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 15</t>
+        </is>
+      </c>
+      <c r="B191" s="27" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C191" s="26" t="n"/>
+      <c r="D191" s="26" t="n"/>
+      <c r="E191" s="26" t="n"/>
+      <c r="F191" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="G191" s="28" t="n">
+        <v>383</v>
+      </c>
+      <c r="H191" s="26" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="14" t="n"/>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Кингстоны</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C192" s="15" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
-        </is>
-      </c>
-      <c r="D192" s="14" t="inlineStr">
-        <is>
-          <t>527-03.054</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
+        </is>
+      </c>
+      <c r="D192" s="25" t="inlineStr"/>
       <c r="E192" s="14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F192" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G192" s="16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H192" s="21" t="n">
-        <v>0.024</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="14" t="n"/>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Кингстоны</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C193" s="15" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
-        </is>
-      </c>
-      <c r="D193" s="14" t="inlineStr">
-        <is>
-          <t>без чертежа(527-35.1165)</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду100</t>
+        </is>
+      </c>
+      <c r="D193" s="25" t="inlineStr"/>
       <c r="E193" s="14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F193" s="14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G193" s="16" t="n">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="H193" s="21" t="n">
-        <v>0.012</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="14" t="n"/>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Кингстоны</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C194" s="15" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="D194" s="14" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду100</t>
+        </is>
+      </c>
+      <c r="D194" s="25" t="inlineStr"/>
       <c r="E194" s="14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F194" s="14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G194" s="16" t="n">
-        <v>38</v>
+        <v>230</v>
       </c>
       <c r="H194" s="21" t="n">
-        <v>0.06</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="14" t="n"/>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Кингстоны</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C195" s="15" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="D195" s="14" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду100</t>
+        </is>
+      </c>
+      <c r="D195" s="25" t="inlineStr"/>
       <c r="E195" s="14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F195" s="14" t="n">
         <v>1</v>
@@ -25788,200 +25764,174 @@
         <v>19</v>
       </c>
       <c r="H195" s="21" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="14" t="n"/>
-      <c r="B196" s="15" t="inlineStr">
-        <is>
-          <t>Головки вентиляционные</t>
-        </is>
-      </c>
-      <c r="C196" s="15" t="inlineStr">
-        <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
-        </is>
-      </c>
-      <c r="D196" s="14" t="inlineStr">
-        <is>
-          <t>(541-03.232)</t>
-        </is>
-      </c>
-      <c r="E196" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="F196" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G196" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="H196" s="21" t="n">
-        <v>0.024</v>
+      <c r="A196" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 16</t>
+        </is>
+      </c>
+      <c r="B196" s="27" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C196" s="26" t="n"/>
+      <c r="D196" s="26" t="n"/>
+      <c r="E196" s="26" t="n"/>
+      <c r="F196" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="G196" s="28" t="n">
+        <v>383</v>
+      </c>
+      <c r="H196" s="26" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="14" t="n"/>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C197" s="15" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
-        </is>
-      </c>
-      <c r="D197" s="14" t="inlineStr">
-        <is>
-          <t>541-03.224</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду100</t>
+        </is>
+      </c>
+      <c r="D197" s="25" t="inlineStr"/>
       <c r="E197" s="14" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G197" s="16" t="n">
-        <v>4</v>
+        <v>383</v>
       </c>
       <c r="H197" s="21" t="n">
-        <v>0.015</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="14" t="n"/>
-      <c r="B198" s="15" t="inlineStr">
-        <is>
-          <t>Головки вентиляционные</t>
-        </is>
-      </c>
-      <c r="C198" s="15" t="inlineStr">
-        <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
-        </is>
-      </c>
-      <c r="D198" s="14" t="inlineStr">
-        <is>
-          <t>(541-03.218)</t>
-        </is>
-      </c>
-      <c r="E198" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="F198" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G198" s="16" t="n">
-        <v>78</v>
-      </c>
-      <c r="H198" s="21" t="n">
-        <v>0.21</v>
+      <c r="A198" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 17</t>
+        </is>
+      </c>
+      <c r="B198" s="27" t="inlineStr">
+        <is>
+          <t>Клинкеты, Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C198" s="26" t="n"/>
+      <c r="D198" s="26" t="n"/>
+      <c r="E198" s="26" t="n"/>
+      <c r="F198" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="G198" s="28" t="n">
+        <v>502</v>
+      </c>
+      <c r="H198" s="26" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="26" t="inlineStr">
-        <is>
-          <t>ЯЩИК 16</t>
-        </is>
-      </c>
-      <c r="B199" s="27" t="inlineStr">
-        <is>
-          <t>Головки вентиляционные, Захлопки, Колонка смотровая, Коробки клапанные</t>
-        </is>
-      </c>
-      <c r="C199" s="26" t="n"/>
-      <c r="D199" s="26" t="n"/>
-      <c r="E199" s="26" t="n"/>
-      <c r="F199" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="G199" s="28" t="n">
-        <v>573</v>
-      </c>
-      <c r="H199" s="26" t="n">
-        <v>0.5600000000000001</v>
+      <c r="A199" s="14" t="n"/>
+      <c r="B199" s="15" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C199" s="15" t="inlineStr">
+        <is>
+          <t>Задвижка клинкетная Ду100</t>
+        </is>
+      </c>
+      <c r="D199" s="25" t="inlineStr"/>
+      <c r="E199" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F199" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G199" s="16" t="n">
+        <v>192</v>
+      </c>
+      <c r="H199" s="21" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="14" t="n"/>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="C200" s="15" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
-        </is>
-      </c>
-      <c r="D200" s="14" t="inlineStr">
-        <is>
-          <t>(541-03.218)</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+        </is>
+      </c>
+      <c r="D200" s="25" t="inlineStr"/>
       <c r="E200" s="14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F200" s="14" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G200" s="16" t="n">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="H200" s="21" t="n">
-        <v>0.36</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="14" t="n"/>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Колонка смотровая</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C201" s="15" t="inlineStr">
         <is>
-          <t>Клапан для колонки указательной Ду10 Ру16</t>
-        </is>
-      </c>
-      <c r="D201" s="14" t="inlineStr">
-        <is>
-          <t>598-03.022-06</t>
-        </is>
-      </c>
+          <t>Сетка на фильтр Ду20 маленькая</t>
+        </is>
+      </c>
+      <c r="D201" s="25" t="inlineStr"/>
       <c r="E201" s="14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F201" s="14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G201" s="16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H201" s="21" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n"/>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C202" s="15" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
-        </is>
-      </c>
-      <c r="D202" s="14" t="inlineStr">
-        <is>
-          <t>529-35.1400-01</t>
-        </is>
-      </c>
+          <t>Фильтр забортной воды Ду 50</t>
+        </is>
+      </c>
+      <c r="D202" s="25" t="inlineStr"/>
       <c r="E202" s="14" t="n">
         <v>50</v>
       </c>
@@ -25989,7 +25939,7 @@
         <v>1</v>
       </c>
       <c r="G202" s="16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H202" s="21" t="n">
         <v>0.012</v>
@@ -25999,873 +25949,865 @@
       <c r="A203" s="14" t="n"/>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C203" s="15" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизонтальная Ду50</t>
-        </is>
-      </c>
-      <c r="D203" s="14" t="inlineStr">
-        <is>
-          <t>529-03.011</t>
-        </is>
-      </c>
+          <t>Фильтр заборной воды ДУ 80</t>
+        </is>
+      </c>
+      <c r="D203" s="25" t="inlineStr"/>
       <c r="E203" s="14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F203" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G203" s="16" t="n">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="H203" s="21" t="n">
-        <v>0.012</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="14" t="n"/>
       <c r="B204" s="15" t="inlineStr">
         <is>
-          <t>Коробки клапанные</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C204" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+          <t>Фильтр забортной воды Ду 100</t>
         </is>
       </c>
       <c r="D204" s="25" t="inlineStr"/>
       <c r="E204" s="14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F204" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G204" s="16" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H204" s="21" t="n">
-        <v>0.024</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="14" t="n"/>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>Коробки клапанные</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C205" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду50</t>
-        </is>
-      </c>
-      <c r="D205" s="25" t="inlineStr"/>
+          <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
+        </is>
+      </c>
+      <c r="D205" s="14" t="inlineStr">
+        <is>
+          <t>427-03-109-2</t>
+        </is>
+      </c>
       <c r="E205" s="14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F205" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G205" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="H205" s="21" t="n">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 18</t>
+        </is>
+      </c>
+      <c r="B206" s="27" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C206" s="26" t="n"/>
+      <c r="D206" s="26" t="n"/>
+      <c r="E206" s="26" t="n"/>
+      <c r="F206" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="G206" s="28" t="n">
+        <v>468</v>
+      </c>
+      <c r="H206" s="26" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="14" t="n"/>
+      <c r="B207" s="15" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C207" s="15" t="inlineStr">
+        <is>
+          <t>Фильтр заборной воды ДУ 150</t>
+        </is>
+      </c>
+      <c r="D207" s="25" t="inlineStr"/>
+      <c r="E207" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="F207" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G205" s="16" t="n">
-        <v>205</v>
-      </c>
-      <c r="H205" s="21" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="14" t="n"/>
-      <c r="B206" s="15" t="inlineStr">
-        <is>
-          <t>Коробки клапанные</t>
-        </is>
-      </c>
-      <c r="C206" s="15" t="inlineStr">
-        <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
-        </is>
-      </c>
-      <c r="D206" s="25" t="inlineStr"/>
-      <c r="E206" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="F206" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G206" s="16" t="n">
-        <v>143</v>
-      </c>
-      <c r="H206" s="21" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="26" t="inlineStr">
-        <is>
-          <t>ЯЩИК 17</t>
-        </is>
-      </c>
-      <c r="B207" s="27" t="inlineStr">
-        <is>
-          <t>Коробки клапанные</t>
-        </is>
-      </c>
-      <c r="C207" s="26" t="n"/>
-      <c r="D207" s="26" t="n"/>
-      <c r="E207" s="26" t="n"/>
-      <c r="F207" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="G207" s="28" t="n">
-        <v>571</v>
-      </c>
-      <c r="H207" s="26" t="n">
-        <v>0.36</v>
+      <c r="G207" s="16" t="n">
+        <v>320</v>
+      </c>
+      <c r="H207" s="21" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="14" t="n"/>
       <c r="B208" s="15" t="inlineStr">
         <is>
-          <t>Коробки клапанные</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C208" s="15" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Фильтр забортной воды Ду200</t>
         </is>
       </c>
       <c r="D208" s="25" t="inlineStr"/>
       <c r="E208" s="14" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="F208" s="14" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G208" s="16" t="n">
-        <v>571</v>
+        <v>148</v>
       </c>
       <c r="H208" s="21" t="n">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="26" t="inlineStr">
         <is>
-          <t>ЯЩИК 18</t>
+          <t>ЯЩИК 19</t>
         </is>
       </c>
       <c r="B209" s="27" t="inlineStr">
         <is>
-          <t>Коробки клапанные</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C209" s="26" t="n"/>
       <c r="D209" s="26" t="n"/>
       <c r="E209" s="26" t="n"/>
       <c r="F209" s="26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G209" s="28" t="n">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="H209" s="26" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="14" t="n"/>
       <c r="B210" s="15" t="inlineStr">
         <is>
-          <t>Коробки клапанные</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C210" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Фильтр забортной воды Ду200</t>
         </is>
       </c>
       <c r="D210" s="25" t="inlineStr"/>
       <c r="E210" s="14" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="F210" s="14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G210" s="16" t="n">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="H210" s="21" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="26" t="inlineStr">
         <is>
-          <t>ЯЩИК 19</t>
+          <t>ЯЩИК 20</t>
         </is>
       </c>
       <c r="B211" s="27" t="inlineStr">
         <is>
-          <t>Коробки клапанные, Краны, Пусковые клапаны, Редукционные клапаны, Стаканы переборочные</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C211" s="26" t="n"/>
       <c r="D211" s="26" t="n"/>
       <c r="E211" s="26" t="n"/>
       <c r="F211" s="26" t="n">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="G211" s="28" t="n">
-        <v>588</v>
+        <v>444</v>
       </c>
       <c r="H211" s="26" t="n">
-        <v>0.37</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="14" t="n"/>
       <c r="B212" s="15" t="inlineStr">
         <is>
-          <t>Коробки клапанные</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C212" s="15" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Фильтр забортной воды Ду200</t>
         </is>
       </c>
       <c r="D212" s="25" t="inlineStr"/>
       <c r="E212" s="14" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="F212" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G212" s="16" t="n">
-        <v>272</v>
+        <v>444</v>
       </c>
       <c r="H212" s="21" t="n">
-        <v>0.12</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="14" t="n"/>
-      <c r="B213" s="15" t="inlineStr">
-        <is>
-          <t>Краны</t>
-        </is>
-      </c>
-      <c r="C213" s="15" t="inlineStr">
-        <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
-        </is>
-      </c>
-      <c r="D213" s="25" t="inlineStr"/>
-      <c r="E213" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="F213" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G213" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H213" s="21" t="n">
-        <v>0.006</v>
+      <c r="A213" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 21</t>
+        </is>
+      </c>
+      <c r="B213" s="27" t="inlineStr">
+        <is>
+          <t>Головки вентиляционные, Кингстоны, Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C213" s="26" t="n"/>
+      <c r="D213" s="26" t="n"/>
+      <c r="E213" s="26" t="n"/>
+      <c r="F213" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="G213" s="28" t="n">
+        <v>423</v>
+      </c>
+      <c r="H213" s="26" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="14" t="n"/>
       <c r="B214" s="15" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="C214" s="15" t="inlineStr">
         <is>
-          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
-        </is>
-      </c>
-      <c r="D214" s="14" t="inlineStr">
-        <is>
-          <t>536-3М5</t>
-        </is>
-      </c>
+          <t>Фильтр забортной воды Ду 300</t>
+        </is>
+      </c>
+      <c r="D214" s="25" t="inlineStr"/>
       <c r="E214" s="14" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F214" s="14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G214" s="16" t="n">
-        <v>7</v>
+        <v>172</v>
       </c>
       <c r="H214" s="21" t="n">
-        <v>0.012</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="14" t="n"/>
       <c r="B215" s="15" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="C215" s="15" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
+          <t>Кингстон донный фланцевый Ду32Ру2,5</t>
         </is>
       </c>
       <c r="D215" s="14" t="inlineStr">
         <is>
-          <t>536-35.695</t>
+          <t>527-03.014</t>
         </is>
       </c>
       <c r="E215" s="14" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F215" s="14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G215" s="16" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H215" s="21" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="14" t="n"/>
       <c r="B216" s="15" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="C216" s="15" t="inlineStr">
         <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="D216" s="14" t="inlineStr">
         <is>
-          <t>528-3М129</t>
+          <t>527-03.054</t>
         </is>
       </c>
       <c r="E216" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F216" s="14" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G216" s="16" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="H216" s="21" t="n">
-        <v>0.066</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="14" t="n"/>
       <c r="B217" s="15" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="C217" s="15" t="inlineStr">
         <is>
-          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="D217" s="14" t="inlineStr">
         <is>
-          <t>536-3М.72</t>
+          <t>без чертежа(527-35.1165)</t>
         </is>
       </c>
       <c r="E217" s="14" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F217" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G217" s="16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H217" s="21" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="14" t="n"/>
       <c r="B218" s="15" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="C218" s="15" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="D218" s="14" t="inlineStr">
         <is>
-          <t>536-35.696</t>
+          <t>527-03.055</t>
         </is>
       </c>
       <c r="E218" s="14" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="F218" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G218" s="16" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H218" s="21" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="14" t="n"/>
       <c r="B219" s="15" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="C219" s="15" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="D219" s="14" t="inlineStr">
         <is>
-          <t>536-35.696</t>
+          <t>527-03.055</t>
         </is>
       </c>
       <c r="E219" s="14" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="F219" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G219" s="16" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H219" s="21" t="n">
-        <v>0.005</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="14" t="n"/>
       <c r="B220" s="15" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="C220" s="15" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду10Ру100</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
         </is>
       </c>
       <c r="D220" s="14" t="inlineStr">
         <is>
-          <t>554-35.265</t>
+          <t>(541-03.232)</t>
         </is>
       </c>
       <c r="E220" s="14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F220" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G220" s="16" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H220" s="21" t="n">
-        <v>0.005</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="14" t="n"/>
       <c r="B221" s="15" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="C221" s="15" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
         </is>
       </c>
       <c r="D221" s="14" t="inlineStr">
         <is>
-          <t>554-03.909-03</t>
+          <t>541-03.224</t>
         </is>
       </c>
       <c r="E221" s="14" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F221" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G221" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H221" s="21" t="n">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="14" t="n"/>
       <c r="B222" s="15" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="C222" s="15" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
         </is>
       </c>
       <c r="D222" s="14" t="inlineStr">
         <is>
-          <t>554-03.905-06</t>
+          <t>(541-03.218)</t>
         </is>
       </c>
       <c r="E222" s="14" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F222" s="14" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G222" s="16" t="n">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="H222" s="21" t="n">
-        <v>0.052</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="14" t="n"/>
-      <c r="B223" s="15" t="inlineStr">
-        <is>
-          <t>Стаканы переборочные</t>
-        </is>
-      </c>
-      <c r="C223" s="15" t="inlineStr">
-        <is>
-          <t>Стакан переборочный Ду25Ру100</t>
-        </is>
-      </c>
-      <c r="D223" s="14" t="inlineStr">
-        <is>
-          <t>554-35.156</t>
-        </is>
-      </c>
-      <c r="E223" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="F223" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G223" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H223" s="21" t="n">
-        <v>0.006</v>
+      <c r="A223" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 22</t>
+        </is>
+      </c>
+      <c r="B223" s="27" t="inlineStr">
+        <is>
+          <t>Головки вентиляционные, Захлопки, Колонка смотровая, Краны, Пусковые клапаны, Редукционные клапаны, Стаканы переборочные</t>
+        </is>
+      </c>
+      <c r="C223" s="26" t="n"/>
+      <c r="D223" s="26" t="n"/>
+      <c r="E223" s="26" t="n"/>
+      <c r="F223" s="26" t="n">
+        <v>129</v>
+      </c>
+      <c r="G223" s="28" t="n">
+        <v>587</v>
+      </c>
+      <c r="H223" s="26" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="14" t="n"/>
       <c r="B224" s="15" t="inlineStr">
         <is>
-          <t>Пусковые клапаны</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="C224" s="15" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду20Ру125</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
         </is>
       </c>
       <c r="D224" s="14" t="inlineStr">
         <is>
-          <t>587-03.080</t>
+          <t>(541-03.218)</t>
         </is>
       </c>
       <c r="E224" s="14" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F224" s="14" t="n">
         <v>7</v>
       </c>
       <c r="G224" s="16" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H224" s="21" t="n">
-        <v>0.014</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="14" t="n"/>
       <c r="B225" s="15" t="inlineStr">
         <is>
-          <t>Пусковые клапаны</t>
+          <t>Колонка смотровая</t>
         </is>
       </c>
       <c r="C225" s="15" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду32Ру125</t>
+          <t>Клапан для колонки указательной Ду10 Ру16</t>
         </is>
       </c>
       <c r="D225" s="14" t="inlineStr">
         <is>
-          <t>587-03.082</t>
+          <t>598-03.022-06</t>
         </is>
       </c>
       <c r="E225" s="14" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F225" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G225" s="16" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="H225" s="21" t="n">
-        <v>0.04</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="14" t="n"/>
       <c r="B226" s="15" t="inlineStr">
         <is>
-          <t>Редукционные клапаны</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="C226" s="15" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
         </is>
       </c>
       <c r="D226" s="14" t="inlineStr">
         <is>
-          <t>525-35.2634</t>
+          <t>529-35.1400-01</t>
         </is>
       </c>
       <c r="E226" s="14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F226" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G226" s="16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H226" s="21" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="14" t="n"/>
       <c r="B227" s="15" t="inlineStr">
         <is>
-          <t>Редукционные клапаны</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="C227" s="15" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Захлопка фланцевая горизонтальная Ду50</t>
         </is>
       </c>
       <c r="D227" s="14" t="inlineStr">
         <is>
-          <t>525-35.2634-04</t>
+          <t>529-03.011</t>
         </is>
       </c>
       <c r="E227" s="14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F227" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G227" s="16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H227" s="21" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="14" t="n"/>
       <c r="B228" s="15" t="inlineStr">
         <is>
-          <t>Редукционные клапаны</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="C228" s="15" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
-        </is>
-      </c>
-      <c r="D228" s="14" t="inlineStr">
-        <is>
-          <t>525-03.044</t>
-        </is>
-      </c>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
+        </is>
+      </c>
+      <c r="D228" s="25" t="inlineStr"/>
       <c r="E228" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F228" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G228" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H228" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="14" t="n"/>
+      <c r="B229" s="15" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C229" s="15" t="inlineStr">
+        <is>
+          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
+        </is>
+      </c>
+      <c r="D229" s="14" t="inlineStr">
+        <is>
+          <t>536-3М5</t>
+        </is>
+      </c>
+      <c r="E229" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="F228" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G228" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="H228" s="21" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="26" t="inlineStr">
-        <is>
-          <t>ЯЩИК 20</t>
-        </is>
-      </c>
-      <c r="B229" s="27" t="inlineStr">
-        <is>
-          <t>Паровые клапаны, Педальные клапаны, Редукционные клапаны, Электромагнитные клапаны</t>
-        </is>
-      </c>
-      <c r="C229" s="26" t="n"/>
-      <c r="D229" s="26" t="n"/>
-      <c r="E229" s="26" t="n"/>
-      <c r="F229" s="26" t="n">
-        <v>70</v>
-      </c>
-      <c r="G229" s="28" t="n">
-        <v>597</v>
-      </c>
-      <c r="H229" s="26" t="n">
-        <v>0.23</v>
+      <c r="F229" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G229" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H229" s="21" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="14" t="n"/>
       <c r="B230" s="15" t="inlineStr">
         <is>
-          <t>Редукционные клапаны</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="C230" s="15" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="D230" s="14" t="inlineStr">
         <is>
-          <t>525-03.044</t>
+          <t>536-35.695</t>
         </is>
       </c>
       <c r="E230" s="14" t="n">
         <v>20</v>
       </c>
       <c r="F230" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G230" s="16" t="n">
-        <v>216</v>
+        <v>20</v>
       </c>
       <c r="H230" s="21" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="14" t="n"/>
       <c r="B231" s="15" t="inlineStr">
         <is>
-          <t>Паровые клапаны</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="C231" s="15" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
         </is>
       </c>
       <c r="D231" s="14" t="inlineStr">
         <is>
-          <t>581-03.034</t>
+          <t>528-3М129</t>
         </is>
       </c>
       <c r="E231" s="14" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F231" s="14" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G231" s="16" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="H231" s="21" t="n">
-        <v>0.02</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="14" t="n"/>
       <c r="B232" s="15" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="C232" s="15" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
+          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
         </is>
       </c>
       <c r="D232" s="14" t="inlineStr">
         <is>
-          <t>587-35.8490-04</t>
+          <t>536-3М.72</t>
         </is>
       </c>
       <c r="E232" s="14" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F232" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G232" s="16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H232" s="21" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="14" t="n"/>
       <c r="B233" s="15" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="C233" s="15" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением</t>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
       <c r="D233" s="14" t="inlineStr">
         <is>
-          <t>587-182.126</t>
-        </is>
-      </c>
-      <c r="E233" s="14" t="n"/>
+          <t>536-35.696</t>
+        </is>
+      </c>
+      <c r="E233" s="14" t="n">
+        <v>32</v>
+      </c>
       <c r="F233" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G233" s="16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H233" s="21" t="n">
         <v>0.01</v>
@@ -26875,235 +26817,623 @@
       <c r="A234" s="14" t="n"/>
       <c r="B234" s="15" t="inlineStr">
         <is>
-          <t>Педальные клапаны</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="C234" s="15" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25</t>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
       <c r="D234" s="14" t="inlineStr">
         <is>
-          <t>М528-03.001</t>
+          <t>536-35.696</t>
         </is>
       </c>
       <c r="E234" s="14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F234" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G234" s="16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H234" s="21" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="14" t="n"/>
       <c r="B235" s="15" t="inlineStr">
         <is>
-          <t>Педальные клапаны</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="C235" s="15" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25 новый приход</t>
+          <t>Стакан переборочный Ду10Ру100</t>
         </is>
       </c>
       <c r="D235" s="14" t="inlineStr">
         <is>
-          <t>М528-03.001</t>
+          <t>554-35.265</t>
         </is>
       </c>
       <c r="E235" s="14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F235" s="14" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="G235" s="16" t="n">
-        <v>319</v>
+        <v>3</v>
       </c>
       <c r="H235" s="21" t="n">
-        <v>0.174</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="26" t="inlineStr">
-        <is>
-          <t>ЯЩИК 21</t>
-        </is>
-      </c>
-      <c r="B236" s="27" t="inlineStr">
-        <is>
-          <t>Без описания — уточнить, Педальные клапаны, Эжекторы</t>
-        </is>
-      </c>
-      <c r="C236" s="26" t="n"/>
-      <c r="D236" s="26" t="n"/>
-      <c r="E236" s="26" t="n"/>
-      <c r="F236" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="G236" s="28" t="n">
-        <v>40</v>
-      </c>
-      <c r="H236" s="26" t="n">
-        <v>0.04</v>
+      <c r="A236" s="14" t="n"/>
+      <c r="B236" s="15" t="inlineStr">
+        <is>
+          <t>Стаканы переборочные</t>
+        </is>
+      </c>
+      <c r="C236" s="15" t="inlineStr">
+        <is>
+          <t>Стакан переборочный Ду20Ру100</t>
+        </is>
+      </c>
+      <c r="D236" s="14" t="inlineStr">
+        <is>
+          <t>554-03.909-03</t>
+        </is>
+      </c>
+      <c r="E236" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F236" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G236" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H236" s="21" t="n">
+        <v>0.006</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="14" t="n"/>
       <c r="B237" s="15" t="inlineStr">
         <is>
-          <t>Педальные клапаны</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="C237" s="15" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25 новый приход</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="D237" s="14" t="inlineStr">
         <is>
-          <t>М528-03.001</t>
+          <t>554-03.905-06</t>
         </is>
       </c>
       <c r="E237" s="14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F237" s="14" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="G237" s="16" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H237" s="21" t="n">
-        <v>0.012</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="14" t="n"/>
       <c r="B238" s="15" t="inlineStr">
         <is>
-          <t>Эжекторы</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="C238" s="15" t="inlineStr">
         <is>
-          <t>Эжектор ВЭЖ 6,3</t>
-        </is>
-      </c>
-      <c r="D238" s="25" t="inlineStr"/>
-      <c r="E238" s="14" t="n"/>
+          <t>Стакан переборочный Ду25Ру100</t>
+        </is>
+      </c>
+      <c r="D238" s="14" t="inlineStr">
+        <is>
+          <t>554-35.156</t>
+        </is>
+      </c>
+      <c r="E238" s="14" t="n">
+        <v>25</v>
+      </c>
       <c r="F238" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G238" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H238" s="21" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="14" t="n"/>
       <c r="B239" s="15" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Пусковые клапаны</t>
         </is>
       </c>
       <c r="C239" s="15" t="inlineStr">
         <is>
-          <t>Клапан Ду20/10</t>
+          <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
       <c r="D239" s="14" t="inlineStr">
         <is>
-          <t>581-С6.73</t>
+          <t>587-03.080</t>
         </is>
       </c>
       <c r="E239" s="14" t="n">
         <v>20</v>
       </c>
       <c r="F239" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G239" s="16" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H239" s="21" t="n">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="14" t="n"/>
       <c r="B240" s="15" t="inlineStr">
         <is>
+          <t>Пусковые клапаны</t>
+        </is>
+      </c>
+      <c r="C240" s="15" t="inlineStr">
+        <is>
+          <t>Клапан пусковой Ду32Ру125</t>
+        </is>
+      </c>
+      <c r="D240" s="14" t="inlineStr">
+        <is>
+          <t>587-03.082</t>
+        </is>
+      </c>
+      <c r="E240" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F240" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G240" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="H240" s="21" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="14" t="n"/>
+      <c r="B241" s="15" t="inlineStr">
+        <is>
+          <t>Редукционные клапаны</t>
+        </is>
+      </c>
+      <c r="C241" s="15" t="inlineStr">
+        <is>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+        </is>
+      </c>
+      <c r="D241" s="14" t="inlineStr">
+        <is>
+          <t>525-35.2634</t>
+        </is>
+      </c>
+      <c r="E241" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F241" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H241" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="14" t="n"/>
+      <c r="B242" s="15" t="inlineStr">
+        <is>
+          <t>Редукционные клапаны</t>
+        </is>
+      </c>
+      <c r="C242" s="15" t="inlineStr">
+        <is>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+        </is>
+      </c>
+      <c r="D242" s="14" t="inlineStr">
+        <is>
+          <t>525-35.2634-04</t>
+        </is>
+      </c>
+      <c r="E242" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F242" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H242" s="21" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="14" t="n"/>
+      <c r="B243" s="15" t="inlineStr">
+        <is>
+          <t>Редукционные клапаны</t>
+        </is>
+      </c>
+      <c r="C243" s="15" t="inlineStr">
+        <is>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+        </is>
+      </c>
+      <c r="D243" s="14" t="inlineStr">
+        <is>
+          <t>525-03.044</t>
+        </is>
+      </c>
+      <c r="E243" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F243" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G243" s="16" t="n">
+        <v>189</v>
+      </c>
+      <c r="H243" s="21" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="26" t="inlineStr">
+        <is>
+          <t>ЯЩИК 23</t>
+        </is>
+      </c>
+      <c r="B244" s="27" t="inlineStr">
+        <is>
+          <t>Без описания — уточнить, Паровые клапаны, Педальные клапаны, Редукционные клапаны, Эжекторы, Электромагнитные клапаны</t>
+        </is>
+      </c>
+      <c r="C244" s="26" t="n"/>
+      <c r="D244" s="26" t="n"/>
+      <c r="E244" s="26" t="n"/>
+      <c r="F244" s="26" t="n">
+        <v>73</v>
+      </c>
+      <c r="G244" s="28" t="n">
+        <v>475</v>
+      </c>
+      <c r="H244" s="26" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="14" t="n"/>
+      <c r="B245" s="15" t="inlineStr">
+        <is>
+          <t>Редукционные клапаны</t>
+        </is>
+      </c>
+      <c r="C245" s="15" t="inlineStr">
+        <is>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+        </is>
+      </c>
+      <c r="D245" s="14" t="inlineStr">
+        <is>
+          <t>525-03.044</t>
+        </is>
+      </c>
+      <c r="E245" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F245" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G245" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="H245" s="21" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="14" t="n"/>
+      <c r="B246" s="15" t="inlineStr">
+        <is>
+          <t>Паровые клапаны</t>
+        </is>
+      </c>
+      <c r="C246" s="15" t="inlineStr">
+        <is>
+          <t>Клапан паровой Ду65Ру10</t>
+        </is>
+      </c>
+      <c r="D246" s="14" t="inlineStr">
+        <is>
+          <t>581-03.034</t>
+        </is>
+      </c>
+      <c r="E246" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F246" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="H246" s="21" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="14" t="n"/>
+      <c r="B247" s="15" t="inlineStr">
+        <is>
+          <t>Электромагнитные клапаны</t>
+        </is>
+      </c>
+      <c r="C247" s="15" t="inlineStr">
+        <is>
+          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
+        </is>
+      </c>
+      <c r="D247" s="14" t="inlineStr">
+        <is>
+          <t>587-35.8490-04</t>
+        </is>
+      </c>
+      <c r="E247" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F247" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H247" s="21" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="14" t="n"/>
+      <c r="B248" s="15" t="inlineStr">
+        <is>
+          <t>Электромагнитные клапаны</t>
+        </is>
+      </c>
+      <c r="C248" s="15" t="inlineStr">
+        <is>
+          <t>Клапан с электромагнитным ручным управлением</t>
+        </is>
+      </c>
+      <c r="D248" s="14" t="inlineStr">
+        <is>
+          <t>587-182.126</t>
+        </is>
+      </c>
+      <c r="E248" s="14" t="n"/>
+      <c r="F248" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H248" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="14" t="n"/>
+      <c r="B249" s="15" t="inlineStr">
+        <is>
+          <t>Педальные клапаны</t>
+        </is>
+      </c>
+      <c r="C249" s="15" t="inlineStr">
+        <is>
+          <t>Клапан педальный Ду25</t>
+        </is>
+      </c>
+      <c r="D249" s="14" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
+      <c r="E249" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F249" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H249" s="21" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="14" t="n"/>
+      <c r="B250" s="15" t="inlineStr">
+        <is>
+          <t>Педальные клапаны</t>
+        </is>
+      </c>
+      <c r="C250" s="15" t="inlineStr">
+        <is>
+          <t>Клапан педальный Ду25 новый приход</t>
+        </is>
+      </c>
+      <c r="D250" s="14" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
+      <c r="E250" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F250" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="G250" s="16" t="n">
+        <v>341</v>
+      </c>
+      <c r="H250" s="21" t="n">
+        <v>0.186</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="14" t="n"/>
+      <c r="B251" s="15" t="inlineStr">
+        <is>
+          <t>Эжекторы</t>
+        </is>
+      </c>
+      <c r="C251" s="15" t="inlineStr">
+        <is>
+          <t>Эжектор ВЭЖ 6,3</t>
+        </is>
+      </c>
+      <c r="D251" s="25" t="inlineStr"/>
+      <c r="E251" s="14" t="n"/>
+      <c r="F251" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G251" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H251" s="21" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="14" t="n"/>
+      <c r="B252" s="15" t="inlineStr">
+        <is>
           <t>Без описания — уточнить</t>
         </is>
       </c>
-      <c r="C240" s="15" t="inlineStr">
+      <c r="C252" s="15" t="inlineStr">
+        <is>
+          <t>Клапан Ду20/10</t>
+        </is>
+      </c>
+      <c r="D252" s="14" t="inlineStr">
+        <is>
+          <t>581-С6.73</t>
+        </is>
+      </c>
+      <c r="E252" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F252" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G252" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H252" s="21" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="14" t="n"/>
+      <c r="B253" s="15" t="inlineStr">
+        <is>
+          <t>Без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="C253" s="15" t="inlineStr">
         <is>
           <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
-      <c r="D240" s="14" t="inlineStr">
+      <c r="D253" s="14" t="inlineStr">
         <is>
           <t>2619802505</t>
         </is>
       </c>
-      <c r="E240" s="14" t="n"/>
-      <c r="F240" s="14" t="n">
+      <c r="E253" s="14" t="n"/>
+      <c r="F253" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G240" s="16" t="n">
+      <c r="G253" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="H240" s="21" t="n">
+      <c r="H253" s="21" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="4" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
         <is>
           <t>Что учесть по таре</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="30" customHeight="1">
-      <c r="A243" s="17" t="inlineStr">
+    <row r="256" ht="30" customHeight="1">
+      <c r="A256" s="17" t="inlineStr">
         <is>
           <t>— Ящик из бэушной доски на 600 кг держит только при брусе 50х50 по четырем углам и по верху. Без него стенка сложится при первом же ударе на маневрировании.</t>
         </is>
       </c>
     </row>
-    <row r="244" ht="30" customHeight="1">
-      <c r="A244" s="17" t="inlineStr">
+    <row r="257" ht="30" customHeight="1">
+      <c r="A257" s="17" t="inlineStr">
         <is>
           <t>— Дно ящика набиваем доской вплотную, без щелей шире ладони: мелкий клапан проваливается и бьет соседей.</t>
         </is>
       </c>
     </row>
-    <row r="245" ht="30" customHeight="1">
-      <c r="A245" s="17" t="inlineStr">
+    <row r="258" ht="30" customHeight="1">
+      <c r="A258" s="17" t="inlineStr">
         <is>
           <t>— На каждый ящик — бирка: номер, группа, вес, строки реестра и стрелки «верх». Принимать груз будут по упаковочному листу.</t>
         </is>
       </c>
     </row>
-    <row r="246" ht="30" customHeight="1">
-      <c r="A246" s="17" t="inlineStr">
+    <row r="259" ht="30" customHeight="1">
+      <c r="A259" s="17" t="inlineStr">
         <is>
           <t>— Задвижки и крупные фланцевые клапаны в ящики не кладем: они встают прямо на настил, с прокладкой доской между рядами и креплением к рымам.</t>
         </is>
       </c>
     </row>
-    <row r="247" ht="30" customHeight="1">
-      <c r="A247" s="17" t="inlineStr">
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="17" t="inlineStr">
         <is>
           <t>— Фильтры идут верхним ярусом на ящиках, поэтому ящики под ними должны быть самыми крепкими — туда ставим те, что с брусом.</t>
         </is>
